--- a/model/ABNB_margin_line_build.xlsx
+++ b/model/ABNB_margin_line_build.xlsx
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.19</v>
+        <v>0.215</v>
       </c>
       <c r="D11" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calibrated on 1H26: line cost per booking -5.1% y/y (WS02) while mgmt's metric fell -10% (1Q26) and -16% (2Q26) and bookings grew 11%; v solves 0.19 x (-13%) + 0.81 x (8% - 11.2%) = -5.1%. Consistent with the metric being third-party contact cost (13,000 contingent workers, FY25 10-K), not the whole line.</t>
+          <t>Calibrated on 1H26 with the rule itself: ops 1H26/1H25 = 624/591 = 1.056 = v x (1 - 0.13) x 1.112 (bookings) + (1 - v) x 1.08 -&gt; v = 0.215; mgmt's metric fell -10% (1Q26) and -16% (2Q26). Consistent with the metric being third-party contact cost (13,000 contingent workers, FY25 10-K), not the whole line.</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>etr_fy26</t>
+          <t>etr_2h26</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% applied to 2H26 forecast quarters (1H26 printed 17.1%)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2267,40 +2267,40 @@
         <v>28.96</v>
       </c>
       <c r="J2" t="n">
-        <v>99.89400000000001</v>
+        <v>100.208</v>
       </c>
       <c r="K2" t="n">
         <v>52.853</v>
       </c>
       <c r="L2" t="n">
-        <v>640.47</v>
+        <v>640.784</v>
       </c>
       <c r="M2" t="n">
         <v>1.763</v>
       </c>
       <c r="N2" t="n">
-        <v>62.433</v>
+        <v>70.648</v>
       </c>
       <c r="O2" t="n">
-        <v>300.056</v>
+        <v>290.795</v>
       </c>
       <c r="P2" t="n">
-        <v>362.489</v>
+        <v>361.443</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.012</v>
+        <v>8.986000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>359.095</v>
       </c>
       <c r="S2" t="n">
-        <v>539.938</v>
+        <v>540.671</v>
       </c>
       <c r="T2" t="n">
         <v>237.645</v>
       </c>
       <c r="U2" t="n">
-        <v>777.5839999999999</v>
+        <v>778.316</v>
       </c>
       <c r="V2" t="n">
         <v>265.389</v>
@@ -2324,7 +2324,7 @@
         <v>50.367</v>
       </c>
       <c r="AC2" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD2" t="n">
         <v>451.579</v>
@@ -2333,7 +2333,7 @@
         <v>1947.429</v>
       </c>
       <c r="AF2" t="n">
-        <v>162.889</v>
+        <v>183.549</v>
       </c>
       <c r="AG2" t="n">
         <v>37</v>
@@ -2342,34 +2342,34 @@
         <v>3.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>2077.019</v>
+        <v>2097.678</v>
       </c>
       <c r="AJ2" t="n">
-        <v>373.863</v>
+        <v>377.582</v>
       </c>
       <c r="AK2" t="n">
         <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>1703.155</v>
+        <v>1720.096</v>
       </c>
       <c r="AM2" t="n">
         <v>591.676</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.879</v>
+        <v>2.907</v>
       </c>
       <c r="AO2" t="n">
-        <v>16.661</v>
+        <v>16.718</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.332</v>
+        <v>13.338</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.682</v>
+        <v>5.377</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.546</v>
+        <v>7.524</v>
       </c>
       <c r="AS2" t="n">
         <v>7.836</v>
@@ -2378,10 +2378,10 @@
         <v>7.475</v>
       </c>
       <c r="AU2" t="n">
-        <v>32.92</v>
+        <v>33.045</v>
       </c>
       <c r="AV2" t="n">
-        <v>16.186</v>
+        <v>16.201</v>
       </c>
       <c r="AW2" t="n">
         <v>1.682</v>
@@ -2402,7 +2402,7 @@
         <v>50.367</v>
       </c>
       <c r="BC2" t="n">
-        <v>30.25</v>
+        <v>31.546</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -2445,28 +2445,28 @@
         <v>25.999</v>
       </c>
       <c r="J3" t="n">
-        <v>99.89400000000001</v>
+        <v>100.208</v>
       </c>
       <c r="K3" t="n">
         <v>47.447</v>
       </c>
       <c r="L3" t="n">
-        <v>577.726</v>
+        <v>578.039</v>
       </c>
       <c r="M3" t="n">
         <v>1.759</v>
       </c>
       <c r="N3" t="n">
-        <v>54.264</v>
+        <v>61.404</v>
       </c>
       <c r="O3" t="n">
-        <v>265.064</v>
+        <v>256.883</v>
       </c>
       <c r="P3" t="n">
-        <v>319.328</v>
+        <v>318.287</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.843</v>
+        <v>8.815</v>
       </c>
       <c r="R3" t="n">
         <v>369.025</v>
@@ -2490,28 +2490,28 @@
         <v>276.411</v>
       </c>
       <c r="Y3" t="n">
-        <v>2300.597</v>
+        <v>2299.87</v>
       </c>
       <c r="Z3" t="n">
         <v>20.634</v>
       </c>
       <c r="AA3" t="n">
-        <v>898.144</v>
+        <v>898.872</v>
       </c>
       <c r="AB3" t="n">
-        <v>28.26</v>
+        <v>28.283</v>
       </c>
       <c r="AC3" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD3" t="n">
         <v>465.161</v>
       </c>
       <c r="AE3" t="n">
-        <v>412.35</v>
+        <v>413.077</v>
       </c>
       <c r="AF3" t="n">
-        <v>160.409</v>
+        <v>165.495</v>
       </c>
       <c r="AG3" t="n">
         <v>37</v>
@@ -2520,34 +2520,34 @@
         <v>3.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>539.4589999999999</v>
+        <v>545.273</v>
       </c>
       <c r="AJ3" t="n">
-        <v>97.10299999999999</v>
+        <v>98.149</v>
       </c>
       <c r="AK3" t="n">
         <v>18</v>
       </c>
       <c r="AL3" t="n">
-        <v>442.356</v>
+        <v>447.124</v>
       </c>
       <c r="AM3" t="n">
         <v>586.352</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.754</v>
+        <v>0.763</v>
       </c>
       <c r="AO3" t="n">
-        <v>18.629</v>
+        <v>18.694</v>
       </c>
       <c r="AP3" t="n">
-        <v>18.178</v>
+        <v>18.188</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.389</v>
+        <v>5.045</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.048</v>
+        <v>10.015</v>
       </c>
       <c r="AS3" t="n">
         <v>10.157</v>
@@ -2568,19 +2568,19 @@
         <v>8.696999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.657</v>
+        <v>9.622</v>
       </c>
       <c r="AZ3" t="n">
-        <v>72.389</v>
+        <v>72.366</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.268</v>
+        <v>14.36</v>
       </c>
       <c r="BB3" t="n">
-        <v>28.26</v>
+        <v>28.283</v>
       </c>
       <c r="BC3" t="n">
-        <v>34.718</v>
+        <v>36.17</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -2623,40 +2623,40 @@
         <v>33.804</v>
       </c>
       <c r="J4" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K4" t="n">
         <v>60.846</v>
       </c>
       <c r="L4" t="n">
-        <v>705.6900000000001</v>
+        <v>706.004</v>
       </c>
       <c r="M4" t="n">
         <v>1.533</v>
       </c>
       <c r="N4" t="n">
-        <v>56.468</v>
+        <v>63.898</v>
       </c>
       <c r="O4" t="n">
-        <v>263.315</v>
+        <v>255.188</v>
       </c>
       <c r="P4" t="n">
-        <v>319.783</v>
+        <v>319.086</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.811</v>
+        <v>6.796</v>
       </c>
       <c r="R4" t="n">
         <v>414.124</v>
       </c>
       <c r="S4" t="n">
-        <v>583.8680000000001</v>
+        <v>584.0700000000001</v>
       </c>
       <c r="T4" t="n">
         <v>245.202</v>
       </c>
       <c r="U4" t="n">
-        <v>829.0700000000001</v>
+        <v>829.272</v>
       </c>
       <c r="V4" t="n">
         <v>249.227</v>
@@ -2668,28 +2668,28 @@
         <v>249.227</v>
       </c>
       <c r="Y4" t="n">
-        <v>2517.894</v>
+        <v>2517.713</v>
       </c>
       <c r="Z4" t="n">
         <v>20.634</v>
       </c>
       <c r="AA4" t="n">
-        <v>555.87</v>
+        <v>556.051</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.207</v>
+        <v>18.212</v>
       </c>
       <c r="AC4" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD4" t="n">
         <v>464.029</v>
       </c>
       <c r="AE4" t="n">
-        <v>71.20699999999999</v>
+        <v>71.38800000000001</v>
       </c>
       <c r="AF4" t="n">
-        <v>191.42</v>
+        <v>180.262</v>
       </c>
       <c r="AG4" t="n">
         <v>37</v>
@@ -2698,34 +2698,34 @@
         <v>3.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>229.326</v>
+        <v>218.35</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40.132</v>
+        <v>38.211</v>
       </c>
       <c r="AK4" t="n">
         <v>17.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>189.194</v>
+        <v>180.139</v>
       </c>
       <c r="AM4" t="n">
         <v>581.027</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.326</v>
+        <v>0.31</v>
       </c>
       <c r="AO4" t="n">
-        <v>21.461</v>
+        <v>21.515</v>
       </c>
       <c r="AP4" t="n">
-        <v>23.114</v>
+        <v>23.124</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.24</v>
+        <v>6.009</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.474</v>
+        <v>10.451</v>
       </c>
       <c r="AS4" t="n">
         <v>10.433</v>
@@ -2734,10 +2734,10 @@
         <v>13.564</v>
       </c>
       <c r="AU4" t="n">
-        <v>19.119</v>
+        <v>19.148</v>
       </c>
       <c r="AV4" t="n">
-        <v>27.155</v>
+        <v>27.161</v>
       </c>
       <c r="AW4" t="n">
         <v>8.833</v>
@@ -2746,19 +2746,19 @@
         <v>8.163</v>
       </c>
       <c r="AY4" t="n">
-        <v>15.394</v>
+        <v>15.386</v>
       </c>
       <c r="AZ4" t="n">
-        <v>82.46899999999999</v>
+        <v>82.46299999999999</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.104</v>
+        <v>7.139</v>
       </c>
       <c r="BB4" t="n">
-        <v>18.207</v>
+        <v>18.212</v>
       </c>
       <c r="BC4" t="n">
-        <v>25.239</v>
+        <v>19.244</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2801,40 +2801,40 @@
         <v>31.42</v>
       </c>
       <c r="J5" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K5" t="n">
         <v>56.556</v>
       </c>
       <c r="L5" t="n">
-        <v>726.986</v>
+        <v>727.3</v>
       </c>
       <c r="M5" t="n">
         <v>1.78</v>
       </c>
       <c r="N5" t="n">
-        <v>59.323</v>
+        <v>67.129</v>
       </c>
       <c r="O5" t="n">
-        <v>282.56</v>
+        <v>273.839</v>
       </c>
       <c r="P5" t="n">
-        <v>341.884</v>
+        <v>340.968</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.834</v>
+        <v>7.813</v>
       </c>
       <c r="R5" t="n">
         <v>400.796</v>
       </c>
       <c r="S5" t="n">
-        <v>658.404</v>
+        <v>658.6319999999999</v>
       </c>
       <c r="T5" t="n">
         <v>276.504</v>
       </c>
       <c r="U5" t="n">
-        <v>934.909</v>
+        <v>935.136</v>
       </c>
       <c r="V5" t="n">
         <v>271.58</v>
@@ -2846,28 +2846,28 @@
         <v>271.58</v>
       </c>
       <c r="Y5" t="n">
-        <v>2676.155</v>
+        <v>2675.781</v>
       </c>
       <c r="Z5" t="n">
         <v>20.634</v>
       </c>
       <c r="AA5" t="n">
-        <v>1373.46</v>
+        <v>1373.834</v>
       </c>
       <c r="AB5" t="n">
-        <v>34.09</v>
+        <v>34.099</v>
       </c>
       <c r="AC5" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD5" t="n">
         <v>551.176</v>
       </c>
       <c r="AE5" t="n">
-        <v>801.65</v>
+        <v>802.024</v>
       </c>
       <c r="AF5" t="n">
-        <v>204.684</v>
+        <v>202.848</v>
       </c>
       <c r="AG5" t="n">
         <v>37</v>
@@ -2876,34 +2876,34 @@
         <v>3.7</v>
       </c>
       <c r="AI5" t="n">
-        <v>973.034</v>
+        <v>971.572</v>
       </c>
       <c r="AJ5" t="n">
-        <v>170.281</v>
+        <v>170.025</v>
       </c>
       <c r="AK5" t="n">
         <v>17.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>802.753</v>
+        <v>801.547</v>
       </c>
       <c r="AM5" t="n">
         <v>575.703</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.394</v>
+        <v>1.392</v>
       </c>
       <c r="AO5" t="n">
-        <v>14.848</v>
+        <v>14.897</v>
       </c>
       <c r="AP5" t="n">
-        <v>18.044</v>
+        <v>18.052</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.846</v>
+        <v>5.563</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.486000000000001</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="AS5" t="n">
         <v>7.165</v>
@@ -2912,10 +2912,10 @@
         <v>9.948</v>
       </c>
       <c r="AU5" t="n">
-        <v>15.707</v>
+        <v>15.735</v>
       </c>
       <c r="AV5" t="n">
-        <v>23.205</v>
+        <v>23.21</v>
       </c>
       <c r="AW5" t="n">
         <v>20.702</v>
@@ -2924,19 +2924,19 @@
         <v>6.741</v>
       </c>
       <c r="AY5" t="n">
-        <v>13.252</v>
+        <v>13.237</v>
       </c>
       <c r="AZ5" t="n">
-        <v>66.423</v>
+        <v>66.413</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.917999999999999</v>
+        <v>8.948</v>
       </c>
       <c r="BB5" t="n">
-        <v>34.09</v>
+        <v>34.099</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.78</v>
+        <v>1.627</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2979,40 +2979,40 @@
         <v>31.192</v>
       </c>
       <c r="J6" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K6" t="n">
         <v>56.145</v>
       </c>
       <c r="L6" t="n">
-        <v>699.14</v>
+        <v>699.454</v>
       </c>
       <c r="M6" t="n">
         <v>1.763</v>
       </c>
       <c r="N6" t="n">
-        <v>66.761</v>
+        <v>75.328</v>
       </c>
       <c r="O6" t="n">
-        <v>317.106</v>
+        <v>306.431</v>
       </c>
       <c r="P6" t="n">
-        <v>383.867</v>
+        <v>381.759</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.861000000000001</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="R6" t="n">
         <v>399.659</v>
       </c>
       <c r="S6" t="n">
-        <v>577.2910000000001</v>
+        <v>577.491</v>
       </c>
       <c r="T6" t="n">
         <v>242.44</v>
       </c>
       <c r="U6" t="n">
-        <v>819.731</v>
+        <v>819.931</v>
       </c>
       <c r="V6" t="n">
         <v>256.539</v>
@@ -3024,28 +3024,28 @@
         <v>256.539</v>
       </c>
       <c r="Y6" t="n">
-        <v>2558.936</v>
+        <v>2557.341</v>
       </c>
       <c r="Z6" t="n">
         <v>20.634</v>
       </c>
       <c r="AA6" t="n">
-        <v>2742.431</v>
+        <v>2744.025</v>
       </c>
       <c r="AB6" t="n">
-        <v>51.933</v>
+        <v>51.963</v>
       </c>
       <c r="AC6" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD6" t="n">
         <v>511.087</v>
       </c>
       <c r="AE6" t="n">
-        <v>2210.71</v>
+        <v>2212.304</v>
       </c>
       <c r="AF6" t="n">
-        <v>170.01</v>
+        <v>191.145</v>
       </c>
       <c r="AG6" t="n">
         <v>37</v>
@@ -3054,34 +3054,34 @@
         <v>3.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>2347.42</v>
+        <v>2370.149</v>
       </c>
       <c r="AJ6" t="n">
-        <v>410.798</v>
+        <v>414.776</v>
       </c>
       <c r="AK6" t="n">
         <v>17.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>1936.621</v>
+        <v>1955.373</v>
       </c>
       <c r="AM6" t="n">
         <v>570.379</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.395</v>
+        <v>3.428</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.16</v>
+        <v>9.156000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>13.239</v>
+        <v>13.245</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.897</v>
+        <v>5.621</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.269</v>
+        <v>7.229</v>
       </c>
       <c r="AS6" t="n">
         <v>11.296</v>
@@ -3090,10 +3090,10 @@
         <v>7.568</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.42</v>
+        <v>5.347</v>
       </c>
       <c r="AV6" t="n">
-        <v>15.523</v>
+        <v>15.527</v>
       </c>
       <c r="AW6" t="n">
         <v>-3.335</v>
@@ -3102,19 +3102,19 @@
         <v>4.858</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.399</v>
+        <v>6.333</v>
       </c>
       <c r="AZ6" t="n">
-        <v>48.458</v>
+        <v>48.428</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.34</v>
+        <v>13.406</v>
       </c>
       <c r="BB6" t="n">
-        <v>51.933</v>
+        <v>51.963</v>
       </c>
       <c r="BC6" t="n">
-        <v>17.953</v>
+        <v>17.923</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -3157,40 +3157,40 @@
         <v>27.953</v>
       </c>
       <c r="J7" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K7" t="n">
         <v>50.316</v>
       </c>
       <c r="L7" t="n">
-        <v>626.538</v>
+        <v>626.852</v>
       </c>
       <c r="M7" t="n">
         <v>1.759</v>
       </c>
       <c r="N7" t="n">
-        <v>58.71</v>
+        <v>66.21899999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>279.348</v>
+        <v>269.844</v>
       </c>
       <c r="P7" t="n">
-        <v>338.058</v>
+        <v>336.062</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.708</v>
+        <v>8.656000000000001</v>
       </c>
       <c r="R7" t="n">
         <v>410.711</v>
       </c>
       <c r="S7" t="n">
-        <v>616.264</v>
+        <v>616.477</v>
       </c>
       <c r="T7" t="n">
         <v>258.807</v>
       </c>
       <c r="U7" t="n">
-        <v>875.072</v>
+        <v>875.285</v>
       </c>
       <c r="V7" t="n">
         <v>267.193</v>
@@ -3202,28 +3202,28 @@
         <v>267.193</v>
       </c>
       <c r="Y7" t="n">
-        <v>2517.573</v>
+        <v>2516.104</v>
       </c>
       <c r="Z7" t="n">
         <v>20.634</v>
       </c>
       <c r="AA7" t="n">
-        <v>968.825</v>
+        <v>970.295</v>
       </c>
       <c r="AB7" t="n">
-        <v>27.954</v>
+        <v>27.997</v>
       </c>
       <c r="AC7" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD7" t="n">
         <v>526.458</v>
       </c>
       <c r="AE7" t="n">
-        <v>421.733</v>
+        <v>423.202</v>
       </c>
       <c r="AF7" t="n">
-        <v>166.64</v>
+        <v>171.155</v>
       </c>
       <c r="AG7" t="n">
         <v>37</v>
@@ -3232,34 +3232,34 @@
         <v>3.7</v>
       </c>
       <c r="AI7" t="n">
-        <v>555.074</v>
+        <v>561.057</v>
       </c>
       <c r="AJ7" t="n">
-        <v>97.13800000000001</v>
+        <v>98.185</v>
       </c>
       <c r="AK7" t="n">
         <v>17.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>457.936</v>
+        <v>462.872</v>
       </c>
       <c r="AM7" t="n">
         <v>565.0549999999999</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="AO7" t="n">
-        <v>8.449</v>
+        <v>8.445</v>
       </c>
       <c r="AP7" t="n">
-        <v>18.078</v>
+        <v>18.087</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.866</v>
+        <v>5.585</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.754</v>
+        <v>9.696999999999999</v>
       </c>
       <c r="AS7" t="n">
         <v>11.296</v>
@@ -3268,10 +3268,10 @@
         <v>11.851</v>
       </c>
       <c r="AU7" t="n">
-        <v>15.428</v>
+        <v>15.457</v>
       </c>
       <c r="AV7" t="n">
-        <v>25.249</v>
+        <v>25.255</v>
       </c>
       <c r="AW7" t="n">
         <v>-3.335</v>
@@ -3280,16 +3280,16 @@
         <v>7.71</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.430999999999999</v>
+        <v>9.401999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>72.64100000000001</v>
+        <v>72.599</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.87</v>
+        <v>7.946</v>
       </c>
       <c r="BB7" t="n">
-        <v>27.954</v>
+        <v>27.997</v>
       </c>
       <c r="BC7" t="n">
         <v>7.424</v>
@@ -3347,16 +3347,16 @@
         <v>1.763</v>
       </c>
       <c r="N8" t="n">
-        <v>62.433</v>
+        <v>70.648</v>
       </c>
       <c r="O8" t="n">
-        <v>300.056</v>
+        <v>290.795</v>
       </c>
       <c r="P8" t="n">
-        <v>362.489</v>
+        <v>361.443</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.012</v>
+        <v>8.986000000000001</v>
       </c>
       <c r="R8" t="n">
         <v>359.095</v>
@@ -3380,16 +3380,16 @@
         <v>265.389</v>
       </c>
       <c r="Y8" t="n">
-        <v>2308.713</v>
+        <v>2307.667</v>
       </c>
       <c r="Z8" t="n">
         <v>20.634</v>
       </c>
       <c r="AA8" t="n">
-        <v>2515.956</v>
+        <v>2517.002</v>
       </c>
       <c r="AB8" t="n">
-        <v>52.372</v>
+        <v>52.393</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -3398,10 +3398,10 @@
         <v>451.579</v>
       </c>
       <c r="AE8" t="n">
-        <v>2043.743</v>
+        <v>2044.789</v>
       </c>
       <c r="AF8" t="n">
-        <v>162.889</v>
+        <v>183.549</v>
       </c>
       <c r="AG8" t="n">
         <v>37</v>
@@ -3410,22 +3410,22 @@
         <v>3.7</v>
       </c>
       <c r="AI8" t="n">
-        <v>2173.332</v>
+        <v>2195.038</v>
       </c>
       <c r="AJ8" t="n">
-        <v>391.2</v>
+        <v>395.107</v>
       </c>
       <c r="AK8" t="n">
         <v>18</v>
       </c>
       <c r="AL8" t="n">
-        <v>1782.133</v>
+        <v>1799.931</v>
       </c>
       <c r="AM8" t="n">
         <v>591.676</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.012</v>
+        <v>3.042</v>
       </c>
       <c r="AO8" t="n">
         <v>11.398</v>
@@ -3434,10 +3434,10 @@
         <v>12.73</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.682</v>
+        <v>5.377</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.546</v>
+        <v>7.524</v>
       </c>
       <c r="AS8" t="n">
         <v>7.836</v>
@@ -3458,19 +3458,19 @@
         <v>5.524</v>
       </c>
       <c r="AY8" t="n">
-        <v>11.478</v>
+        <v>11.428</v>
       </c>
       <c r="AZ8" t="n">
-        <v>48.058</v>
+        <v>48.036</v>
       </c>
       <c r="BA8" t="n">
-        <v>22.67</v>
+        <v>22.721</v>
       </c>
       <c r="BB8" t="n">
-        <v>52.372</v>
+        <v>52.393</v>
       </c>
       <c r="BC8" t="n">
-        <v>36.29</v>
+        <v>37.651</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3525,16 +3525,16 @@
         <v>1.759</v>
       </c>
       <c r="N9" t="n">
-        <v>54.264</v>
+        <v>61.404</v>
       </c>
       <c r="O9" t="n">
-        <v>265.064</v>
+        <v>256.883</v>
       </c>
       <c r="P9" t="n">
-        <v>319.328</v>
+        <v>318.287</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.843</v>
+        <v>8.815</v>
       </c>
       <c r="R9" t="n">
         <v>369.025</v>
@@ -3558,16 +3558,16 @@
         <v>276.411</v>
       </c>
       <c r="Y9" t="n">
-        <v>2271.703</v>
+        <v>2270.662</v>
       </c>
       <c r="Z9" t="n">
         <v>20.634</v>
       </c>
       <c r="AA9" t="n">
-        <v>927.039</v>
+        <v>928.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>29.17</v>
+        <v>29.202</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3576,10 +3576,10 @@
         <v>465.161</v>
       </c>
       <c r="AE9" t="n">
-        <v>441.244</v>
+        <v>442.285</v>
       </c>
       <c r="AF9" t="n">
-        <v>160.409</v>
+        <v>165.495</v>
       </c>
       <c r="AG9" t="n">
         <v>37</v>
@@ -3588,22 +3588,22 @@
         <v>3.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>568.353</v>
+        <v>574.481</v>
       </c>
       <c r="AJ9" t="n">
-        <v>102.304</v>
+        <v>103.406</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>466.05</v>
+        <v>471.074</v>
       </c>
       <c r="AM9" t="n">
         <v>586.352</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.795</v>
+        <v>0.803</v>
       </c>
       <c r="AO9" t="n">
         <v>12.696</v>
@@ -3612,10 +3612,10 @@
         <v>17.269</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.389</v>
+        <v>5.045</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.048</v>
+        <v>10.015</v>
       </c>
       <c r="AS9" t="n">
         <v>10.157</v>
@@ -3636,19 +3636,19 @@
         <v>8.696999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.279</v>
+        <v>8.23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>71.48</v>
+        <v>71.447</v>
       </c>
       <c r="BA9" t="n">
-        <v>17.944</v>
+        <v>18.076</v>
       </c>
       <c r="BB9" t="n">
-        <v>29.17</v>
+        <v>29.202</v>
       </c>
       <c r="BC9" t="n">
-        <v>41.934</v>
+        <v>43.464</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         <v>1.533</v>
       </c>
       <c r="N10" t="n">
-        <v>56.468</v>
+        <v>63.898</v>
       </c>
       <c r="O10" t="n">
-        <v>263.315</v>
+        <v>255.188</v>
       </c>
       <c r="P10" t="n">
-        <v>319.783</v>
+        <v>319.086</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.811</v>
+        <v>6.796</v>
       </c>
       <c r="R10" t="n">
         <v>414.124</v>
@@ -3736,16 +3736,16 @@
         <v>249.227</v>
       </c>
       <c r="Y10" t="n">
-        <v>2470.415</v>
+        <v>2469.718</v>
       </c>
       <c r="Z10" t="n">
         <v>20.634</v>
       </c>
       <c r="AA10" t="n">
-        <v>603.348</v>
+        <v>604.045</v>
       </c>
       <c r="AB10" t="n">
-        <v>19.762</v>
+        <v>19.784</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3754,10 +3754,10 @@
         <v>464.029</v>
       </c>
       <c r="AE10" t="n">
-        <v>118.685</v>
+        <v>119.382</v>
       </c>
       <c r="AF10" t="n">
-        <v>191.42</v>
+        <v>180.262</v>
       </c>
       <c r="AG10" t="n">
         <v>37</v>
@@ -3766,22 +3766,22 @@
         <v>3.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>276.805</v>
+        <v>266.345</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48.441</v>
+        <v>46.61</v>
       </c>
       <c r="AK10" t="n">
         <v>17.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>228.364</v>
+        <v>219.734</v>
       </c>
       <c r="AM10" t="n">
         <v>581.027</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.393</v>
+        <v>0.378</v>
       </c>
       <c r="AO10" t="n">
         <v>16.488</v>
@@ -3790,10 +3790,10 @@
         <v>22.167</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.24</v>
+        <v>6.009</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.474</v>
+        <v>10.451</v>
       </c>
       <c r="AS10" t="n">
         <v>10.433</v>
@@ -3814,19 +3814,19 @@
         <v>8.163</v>
       </c>
       <c r="AY10" t="n">
-        <v>13.218</v>
+        <v>13.186</v>
       </c>
       <c r="AZ10" t="n">
-        <v>80.914</v>
+        <v>80.89100000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>16.252</v>
+        <v>16.386</v>
       </c>
       <c r="BB10" t="n">
-        <v>19.762</v>
+        <v>19.784</v>
       </c>
       <c r="BC10" t="n">
-        <v>51.167</v>
+        <v>45.455</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -3881,16 +3881,16 @@
         <v>1.78</v>
       </c>
       <c r="N11" t="n">
-        <v>59.323</v>
+        <v>67.129</v>
       </c>
       <c r="O11" t="n">
-        <v>282.56</v>
+        <v>273.839</v>
       </c>
       <c r="P11" t="n">
-        <v>341.884</v>
+        <v>340.968</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.834</v>
+        <v>7.813</v>
       </c>
       <c r="R11" t="n">
         <v>400.796</v>
@@ -3914,16 +3914,16 @@
         <v>271.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>2626.304</v>
+        <v>2625.388</v>
       </c>
       <c r="Z11" t="n">
         <v>20.634</v>
       </c>
       <c r="AA11" t="n">
-        <v>1423.311</v>
+        <v>1424.226</v>
       </c>
       <c r="AB11" t="n">
-        <v>35.327</v>
+        <v>35.35</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3932,10 +3932,10 @@
         <v>551.176</v>
       </c>
       <c r="AE11" t="n">
-        <v>851.502</v>
+        <v>852.417</v>
       </c>
       <c r="AF11" t="n">
-        <v>204.684</v>
+        <v>202.848</v>
       </c>
       <c r="AG11" t="n">
         <v>37</v>
@@ -3944,22 +3944,22 @@
         <v>3.7</v>
       </c>
       <c r="AI11" t="n">
-        <v>1022.885</v>
+        <v>1021.965</v>
       </c>
       <c r="AJ11" t="n">
-        <v>179.005</v>
+        <v>178.844</v>
       </c>
       <c r="AK11" t="n">
         <v>17.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>843.88</v>
+        <v>843.121</v>
       </c>
       <c r="AM11" t="n">
         <v>575.703</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.466</v>
+        <v>1.465</v>
       </c>
       <c r="AO11" t="n">
         <v>10.283</v>
@@ -3968,10 +3968,10 @@
         <v>17.327</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.846</v>
+        <v>5.563</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.486000000000001</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="AS11" t="n">
         <v>7.165</v>
@@ -3992,19 +3992,19 @@
         <v>6.741</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.143</v>
+        <v>11.104</v>
       </c>
       <c r="AZ11" t="n">
-        <v>65.185</v>
+        <v>65.163</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.872</v>
+        <v>12.944</v>
       </c>
       <c r="BB11" t="n">
-        <v>35.327</v>
+        <v>35.35</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.995</v>
+        <v>6.898</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
         <v>1.763</v>
       </c>
       <c r="N12" t="n">
-        <v>66.761</v>
+        <v>75.328</v>
       </c>
       <c r="O12" t="n">
-        <v>317.106</v>
+        <v>306.431</v>
       </c>
       <c r="P12" t="n">
-        <v>383.867</v>
+        <v>381.759</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.861000000000001</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>399.659</v>
@@ -4092,16 +4092,16 @@
         <v>256.539</v>
       </c>
       <c r="Y12" t="n">
-        <v>2511.666</v>
+        <v>2509.559</v>
       </c>
       <c r="Z12" t="n">
         <v>20.634</v>
       </c>
       <c r="AA12" t="n">
-        <v>2789.7</v>
+        <v>2791.808</v>
       </c>
       <c r="AB12" t="n">
-        <v>52.828</v>
+        <v>52.868</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4110,10 +4110,10 @@
         <v>511.087</v>
       </c>
       <c r="AE12" t="n">
-        <v>2257.979</v>
+        <v>2260.087</v>
       </c>
       <c r="AF12" t="n">
-        <v>170.01</v>
+        <v>191.145</v>
       </c>
       <c r="AG12" t="n">
         <v>37</v>
@@ -4122,22 +4122,22 @@
         <v>3.7</v>
       </c>
       <c r="AI12" t="n">
-        <v>2394.689</v>
+        <v>2417.932</v>
       </c>
       <c r="AJ12" t="n">
-        <v>419.071</v>
+        <v>423.138</v>
       </c>
       <c r="AK12" t="n">
         <v>17.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>1975.619</v>
+        <v>1994.794</v>
       </c>
       <c r="AM12" t="n">
         <v>570.379</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.464</v>
+        <v>3.497</v>
       </c>
       <c r="AO12" t="n">
         <v>9.593</v>
@@ -4146,10 +4146,10 @@
         <v>12.692</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.897</v>
+        <v>5.621</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.269</v>
+        <v>7.229</v>
       </c>
       <c r="AS12" t="n">
         <v>11.296</v>
@@ -4170,19 +4170,19 @@
         <v>4.858</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.791</v>
+        <v>8.749000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>47.563</v>
+        <v>47.523</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.88</v>
+        <v>10.918</v>
       </c>
       <c r="BB12" t="n">
-        <v>52.828</v>
+        <v>52.868</v>
       </c>
       <c r="BC12" t="n">
-        <v>14.996</v>
+        <v>14.964</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -4237,16 +4237,16 @@
         <v>1.759</v>
       </c>
       <c r="N13" t="n">
-        <v>58.71</v>
+        <v>66.21899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>279.348</v>
+        <v>269.844</v>
       </c>
       <c r="P13" t="n">
-        <v>338.058</v>
+        <v>336.062</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.708</v>
+        <v>8.656000000000001</v>
       </c>
       <c r="R13" t="n">
         <v>410.711</v>
@@ -4270,16 +4270,16 @@
         <v>267.193</v>
       </c>
       <c r="Y13" t="n">
-        <v>2469.063</v>
+        <v>2467.067</v>
       </c>
       <c r="Z13" t="n">
         <v>20.634</v>
       </c>
       <c r="AA13" t="n">
-        <v>1017.335</v>
+        <v>1019.331</v>
       </c>
       <c r="AB13" t="n">
-        <v>29.354</v>
+        <v>29.411</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4288,10 +4288,10 @@
         <v>526.458</v>
       </c>
       <c r="AE13" t="n">
-        <v>470.243</v>
+        <v>472.239</v>
       </c>
       <c r="AF13" t="n">
-        <v>166.64</v>
+        <v>171.155</v>
       </c>
       <c r="AG13" t="n">
         <v>37</v>
@@ -4300,22 +4300,22 @@
         <v>3.7</v>
       </c>
       <c r="AI13" t="n">
-        <v>603.583</v>
+        <v>610.0940000000001</v>
       </c>
       <c r="AJ13" t="n">
-        <v>105.627</v>
+        <v>106.766</v>
       </c>
       <c r="AK13" t="n">
         <v>17.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>497.956</v>
+        <v>503.328</v>
       </c>
       <c r="AM13" t="n">
         <v>565.0549999999999</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.881</v>
+        <v>0.891</v>
       </c>
       <c r="AO13" t="n">
         <v>8.894</v>
@@ -4324,10 +4324,10 @@
         <v>17.244</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.866</v>
+        <v>5.585</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.754</v>
+        <v>9.696999999999999</v>
       </c>
       <c r="AS13" t="n">
         <v>11.296</v>
@@ -4348,19 +4348,19 @@
         <v>7.71</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.688000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="AZ13" t="n">
-        <v>71.242</v>
+        <v>71.184</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.74</v>
+        <v>9.832000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>29.354</v>
+        <v>29.411</v>
       </c>
       <c r="BC13" t="n">
-        <v>10.873</v>
+        <v>10.874</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -4403,40 +4403,40 @@
         <v>28.594</v>
       </c>
       <c r="J14" t="n">
-        <v>99.89400000000001</v>
+        <v>100.208</v>
       </c>
       <c r="K14" t="n">
         <v>52.184</v>
       </c>
       <c r="L14" t="n">
-        <v>627.501</v>
+        <v>627.8150000000001</v>
       </c>
       <c r="M14" t="n">
         <v>1.763</v>
       </c>
       <c r="N14" t="n">
-        <v>61.643</v>
+        <v>69.754</v>
       </c>
       <c r="O14" t="n">
-        <v>300.056</v>
+        <v>290.795</v>
       </c>
       <c r="P14" t="n">
-        <v>361.7</v>
+        <v>360.549</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.108000000000001</v>
+        <v>9.079000000000001</v>
       </c>
       <c r="R14" t="n">
         <v>359.095</v>
       </c>
       <c r="S14" t="n">
-        <v>539.938</v>
+        <v>540.671</v>
       </c>
       <c r="T14" t="n">
         <v>237.645</v>
       </c>
       <c r="U14" t="n">
-        <v>777.5839999999999</v>
+        <v>778.316</v>
       </c>
       <c r="V14" t="n">
         <v>265.389</v>
@@ -4448,28 +4448,28 @@
         <v>265.389</v>
       </c>
       <c r="Y14" t="n">
-        <v>2391.268</v>
+        <v>2391.164</v>
       </c>
       <c r="Z14" t="n">
         <v>20.634</v>
       </c>
       <c r="AA14" t="n">
-        <v>2384.366</v>
+        <v>2384.47</v>
       </c>
       <c r="AB14" t="n">
-        <v>50.144</v>
+        <v>50.147</v>
       </c>
       <c r="AC14" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD14" t="n">
         <v>451.579</v>
       </c>
       <c r="AE14" t="n">
-        <v>1912.153</v>
+        <v>1912.257</v>
       </c>
       <c r="AF14" t="n">
-        <v>162.011</v>
+        <v>182.671</v>
       </c>
       <c r="AG14" t="n">
         <v>37</v>
@@ -4478,34 +4478,34 @@
         <v>3.7</v>
       </c>
       <c r="AI14" t="n">
-        <v>2040.864</v>
+        <v>2061.628</v>
       </c>
       <c r="AJ14" t="n">
-        <v>367.356</v>
+        <v>371.093</v>
       </c>
       <c r="AK14" t="n">
         <v>18</v>
       </c>
       <c r="AL14" t="n">
-        <v>1673.509</v>
+        <v>1690.535</v>
       </c>
       <c r="AM14" t="n">
         <v>591.676</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.828</v>
+        <v>2.857</v>
       </c>
       <c r="AO14" t="n">
-        <v>14.299</v>
+        <v>14.356</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.197</v>
+        <v>13.203</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.452</v>
+        <v>5.116</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.607</v>
+        <v>7.583</v>
       </c>
       <c r="AS14" t="n">
         <v>7.836</v>
@@ -4514,10 +4514,10 @@
         <v>7.552</v>
       </c>
       <c r="AU14" t="n">
-        <v>32.92</v>
+        <v>33.045</v>
       </c>
       <c r="AV14" t="n">
-        <v>16.353</v>
+        <v>16.368</v>
       </c>
       <c r="AW14" t="n">
         <v>1.682</v>
@@ -4526,19 +4526,19 @@
         <v>5.581</v>
       </c>
       <c r="AY14" t="n">
-        <v>15.464</v>
+        <v>15.459</v>
       </c>
       <c r="AZ14" t="n">
-        <v>50.29</v>
+        <v>50.287</v>
       </c>
       <c r="BA14" t="n">
-        <v>16.254</v>
+        <v>16.259</v>
       </c>
       <c r="BB14" t="n">
-        <v>50.144</v>
+        <v>50.147</v>
       </c>
       <c r="BC14" t="n">
-        <v>27.983</v>
+        <v>29.285</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -4581,28 +4581,28 @@
         <v>25.97</v>
       </c>
       <c r="J15" t="n">
-        <v>99.89400000000001</v>
+        <v>100.208</v>
       </c>
       <c r="K15" t="n">
         <v>47.395</v>
       </c>
       <c r="L15" t="n">
-        <v>571.575</v>
+        <v>571.889</v>
       </c>
       <c r="M15" t="n">
         <v>1.759</v>
       </c>
       <c r="N15" t="n">
-        <v>54.203</v>
+        <v>61.336</v>
       </c>
       <c r="O15" t="n">
-        <v>265.064</v>
+        <v>256.883</v>
       </c>
       <c r="P15" t="n">
-        <v>319.268</v>
+        <v>318.219</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.852</v>
+        <v>8.821999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>369.025</v>
@@ -4626,28 +4626,28 @@
         <v>276.411</v>
       </c>
       <c r="Y15" t="n">
-        <v>2294.386</v>
+        <v>2293.651</v>
       </c>
       <c r="Z15" t="n">
         <v>20.634</v>
       </c>
       <c r="AA15" t="n">
-        <v>850.0549999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>27.212</v>
+        <v>27.236</v>
       </c>
       <c r="AC15" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD15" t="n">
         <v>465.161</v>
       </c>
       <c r="AE15" t="n">
-        <v>364.26</v>
+        <v>364.995</v>
       </c>
       <c r="AF15" t="n">
-        <v>159.924</v>
+        <v>164.133</v>
       </c>
       <c r="AG15" t="n">
         <v>37</v>
@@ -4656,34 +4656,34 @@
         <v>3.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>490.884</v>
+        <v>495.828</v>
       </c>
       <c r="AJ15" t="n">
-        <v>88.35899999999999</v>
+        <v>89.249</v>
       </c>
       <c r="AK15" t="n">
         <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>402.525</v>
+        <v>406.579</v>
       </c>
       <c r="AM15" t="n">
         <v>586.352</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AO15" t="n">
-        <v>17.367</v>
+        <v>17.431</v>
       </c>
       <c r="AP15" t="n">
-        <v>18.297</v>
+        <v>18.307</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.369</v>
+        <v>5.023</v>
       </c>
       <c r="AR15" t="n">
-        <v>10.22</v>
+        <v>10.187</v>
       </c>
       <c r="AS15" t="n">
         <v>10.157</v>
@@ -4704,19 +4704,19 @@
         <v>8.849</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.361000000000001</v>
+        <v>9.326000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>73.44799999999999</v>
+        <v>73.425</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.148999999999999</v>
+        <v>8.243</v>
       </c>
       <c r="BB15" t="n">
-        <v>27.212</v>
+        <v>27.236</v>
       </c>
       <c r="BC15" t="n">
-        <v>22.588</v>
+        <v>23.822</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -4759,40 +4759,40 @@
         <v>32.71</v>
       </c>
       <c r="J16" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K16" t="n">
         <v>58.879</v>
       </c>
       <c r="L16" t="n">
-        <v>667.489</v>
+        <v>667.803</v>
       </c>
       <c r="M16" t="n">
         <v>1.533</v>
       </c>
       <c r="N16" t="n">
-        <v>54.642</v>
+        <v>61.832</v>
       </c>
       <c r="O16" t="n">
-        <v>263.315</v>
+        <v>255.188</v>
       </c>
       <c r="P16" t="n">
-        <v>317.957</v>
+        <v>317.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.999</v>
+        <v>6.978</v>
       </c>
       <c r="R16" t="n">
         <v>414.124</v>
       </c>
       <c r="S16" t="n">
-        <v>583.8680000000001</v>
+        <v>584.0700000000001</v>
       </c>
       <c r="T16" t="n">
         <v>245.202</v>
       </c>
       <c r="U16" t="n">
-        <v>829.0700000000001</v>
+        <v>829.272</v>
       </c>
       <c r="V16" t="n">
         <v>249.227</v>
@@ -4804,28 +4804,28 @@
         <v>249.227</v>
       </c>
       <c r="Y16" t="n">
-        <v>2477.867</v>
+        <v>2477.446</v>
       </c>
       <c r="Z16" t="n">
         <v>20.634</v>
       </c>
       <c r="AA16" t="n">
-        <v>537.929</v>
+        <v>538.351</v>
       </c>
       <c r="AB16" t="n">
-        <v>17.96</v>
+        <v>17.974</v>
       </c>
       <c r="AC16" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD16" t="n">
         <v>464.029</v>
       </c>
       <c r="AE16" t="n">
-        <v>53.267</v>
+        <v>53.688</v>
       </c>
       <c r="AF16" t="n">
-        <v>188.007</v>
+        <v>176.365</v>
       </c>
       <c r="AG16" t="n">
         <v>37</v>
@@ -4834,34 +4834,34 @@
         <v>3.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>207.974</v>
+        <v>196.753</v>
       </c>
       <c r="AJ16" t="n">
-        <v>36.395</v>
+        <v>34.432</v>
       </c>
       <c r="AK16" t="n">
         <v>17.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>171.578</v>
+        <v>162.321</v>
       </c>
       <c r="AM16" t="n">
         <v>581.027</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.295</v>
+        <v>0.279</v>
       </c>
       <c r="AO16" t="n">
-        <v>14.886</v>
+        <v>14.94</v>
       </c>
       <c r="AP16" t="n">
-        <v>22.286</v>
+        <v>22.296</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.634</v>
+        <v>5.322</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.616</v>
+        <v>10.584</v>
       </c>
       <c r="AS16" t="n">
         <v>10.433</v>
@@ -4870,10 +4870,10 @@
         <v>13.826</v>
       </c>
       <c r="AU16" t="n">
-        <v>19.119</v>
+        <v>19.148</v>
       </c>
       <c r="AV16" t="n">
-        <v>27.68</v>
+        <v>27.687</v>
       </c>
       <c r="AW16" t="n">
         <v>8.833</v>
@@ -4882,19 +4882,19 @@
         <v>8.321</v>
       </c>
       <c r="AY16" t="n">
-        <v>13.559</v>
+        <v>13.54</v>
       </c>
       <c r="AZ16" t="n">
-        <v>82.729</v>
+        <v>82.715</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.647</v>
+        <v>3.729</v>
       </c>
       <c r="BB16" t="n">
-        <v>17.96</v>
+        <v>17.974</v>
       </c>
       <c r="BC16" t="n">
-        <v>13.578</v>
+        <v>7.45</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -4937,40 +4937,40 @@
         <v>30.558</v>
       </c>
       <c r="J17" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K17" t="n">
         <v>55.004</v>
       </c>
       <c r="L17" t="n">
-        <v>691.675</v>
+        <v>691.989</v>
       </c>
       <c r="M17" t="n">
         <v>1.78</v>
       </c>
       <c r="N17" t="n">
-        <v>57.695</v>
+        <v>65.286</v>
       </c>
       <c r="O17" t="n">
-        <v>282.56</v>
+        <v>273.839</v>
       </c>
       <c r="P17" t="n">
-        <v>340.255</v>
+        <v>339.126</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.016999999999999</v>
+        <v>7.991</v>
       </c>
       <c r="R17" t="n">
         <v>400.796</v>
       </c>
       <c r="S17" t="n">
-        <v>658.404</v>
+        <v>658.6319999999999</v>
       </c>
       <c r="T17" t="n">
         <v>276.504</v>
       </c>
       <c r="U17" t="n">
-        <v>934.909</v>
+        <v>935.136</v>
       </c>
       <c r="V17" t="n">
         <v>271.58</v>
@@ -4982,28 +4982,28 @@
         <v>271.58</v>
       </c>
       <c r="Y17" t="n">
-        <v>2639.215</v>
+        <v>2638.627</v>
       </c>
       <c r="Z17" t="n">
         <v>20.634</v>
       </c>
       <c r="AA17" t="n">
-        <v>1185.143</v>
+        <v>1185.731</v>
       </c>
       <c r="AB17" t="n">
-        <v>31.157</v>
+        <v>31.173</v>
       </c>
       <c r="AC17" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD17" t="n">
         <v>551.176</v>
       </c>
       <c r="AE17" t="n">
-        <v>613.333</v>
+        <v>613.921</v>
       </c>
       <c r="AF17" t="n">
-        <v>201.262</v>
+        <v>196.013</v>
       </c>
       <c r="AG17" t="n">
         <v>37</v>
@@ -5012,34 +5012,34 @@
         <v>3.7</v>
       </c>
       <c r="AI17" t="n">
-        <v>781.295</v>
+        <v>776.634</v>
       </c>
       <c r="AJ17" t="n">
-        <v>136.727</v>
+        <v>135.911</v>
       </c>
       <c r="AK17" t="n">
         <v>17.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>644.568</v>
+        <v>640.723</v>
       </c>
       <c r="AM17" t="n">
         <v>575.703</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.12</v>
+        <v>1.113</v>
       </c>
       <c r="AO17" t="n">
-        <v>9.269</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="AP17" t="n">
-        <v>18.184</v>
+        <v>18.192</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.342</v>
+        <v>4.992</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.945</v>
+        <v>8.916</v>
       </c>
       <c r="AS17" t="n">
         <v>7.165</v>
@@ -5048,10 +5048,10 @@
         <v>10.537</v>
       </c>
       <c r="AU17" t="n">
-        <v>15.707</v>
+        <v>15.735</v>
       </c>
       <c r="AV17" t="n">
-        <v>24.579</v>
+        <v>24.585</v>
       </c>
       <c r="AW17" t="n">
         <v>20.702</v>
@@ -5060,19 +5060,19 @@
         <v>7.14</v>
       </c>
       <c r="AY17" t="n">
-        <v>11.689</v>
+        <v>11.664</v>
       </c>
       <c r="AZ17" t="n">
-        <v>69.38500000000001</v>
+        <v>69.37</v>
       </c>
       <c r="BA17" t="n">
-        <v>-6.016</v>
+        <v>-5.969</v>
       </c>
       <c r="BB17" t="n">
-        <v>31.157</v>
+        <v>31.173</v>
       </c>
       <c r="BC17" t="n">
-        <v>-18.276</v>
+        <v>-18.764</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -5115,40 +5115,40 @@
         <v>29.978</v>
       </c>
       <c r="J18" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K18" t="n">
         <v>53.961</v>
       </c>
       <c r="L18" t="n">
-        <v>656.462</v>
+        <v>656.776</v>
       </c>
       <c r="M18" t="n">
         <v>1.763</v>
       </c>
       <c r="N18" t="n">
-        <v>64.845</v>
+        <v>73.14400000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>316.415</v>
+        <v>305.674</v>
       </c>
       <c r="P18" t="n">
-        <v>381.26</v>
+        <v>378.818</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.157</v>
+        <v>9.098000000000001</v>
       </c>
       <c r="R18" t="n">
         <v>399.659</v>
       </c>
       <c r="S18" t="n">
-        <v>577.2910000000001</v>
+        <v>577.491</v>
       </c>
       <c r="T18" t="n">
         <v>242.44</v>
       </c>
       <c r="U18" t="n">
-        <v>819.731</v>
+        <v>819.931</v>
       </c>
       <c r="V18" t="n">
         <v>256.539</v>
@@ -5160,28 +5160,28 @@
         <v>256.539</v>
       </c>
       <c r="Y18" t="n">
-        <v>2513.651</v>
+        <v>2511.722</v>
       </c>
       <c r="Z18" t="n">
         <v>20.634</v>
       </c>
       <c r="AA18" t="n">
-        <v>2443.521</v>
+        <v>2445.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>49.499</v>
+        <v>49.538</v>
       </c>
       <c r="AC18" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD18" t="n">
         <v>511.087</v>
       </c>
       <c r="AE18" t="n">
-        <v>1911.8</v>
+        <v>1913.729</v>
       </c>
       <c r="AF18" t="n">
-        <v>166.242</v>
+        <v>184.833</v>
       </c>
       <c r="AG18" t="n">
         <v>37</v>
@@ -5190,34 +5190,34 @@
         <v>3.7</v>
       </c>
       <c r="AI18" t="n">
-        <v>2044.742</v>
+        <v>2065.261</v>
       </c>
       <c r="AJ18" t="n">
-        <v>357.83</v>
+        <v>361.421</v>
       </c>
       <c r="AK18" t="n">
         <v>17.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>1686.912</v>
+        <v>1703.841</v>
       </c>
       <c r="AM18" t="n">
         <v>570.379</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.958</v>
+        <v>2.987</v>
       </c>
       <c r="AO18" t="n">
-        <v>4.615</v>
+        <v>4.613</v>
       </c>
       <c r="AP18" t="n">
-        <v>13.298</v>
+        <v>13.304</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.408</v>
+        <v>5.067</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.723</v>
+        <v>7.674</v>
       </c>
       <c r="AS18" t="n">
         <v>11.296</v>
@@ -5226,10 +5226,10 @@
         <v>8.096</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.42</v>
+        <v>5.347</v>
       </c>
       <c r="AV18" t="n">
-        <v>16.605</v>
+        <v>16.609</v>
       </c>
       <c r="AW18" t="n">
         <v>-3.335</v>
@@ -5238,19 +5238,19 @@
         <v>5.197</v>
       </c>
       <c r="AY18" t="n">
-        <v>5.118</v>
+        <v>5.042</v>
       </c>
       <c r="AZ18" t="n">
-        <v>50.919</v>
+        <v>50.88</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.481</v>
+        <v>2.557</v>
       </c>
       <c r="BB18" t="n">
-        <v>49.499</v>
+        <v>49.538</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.565</v>
+        <v>4.55</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -5293,40 +5293,40 @@
         <v>27.206</v>
       </c>
       <c r="J19" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K19" t="n">
         <v>48.972</v>
       </c>
       <c r="L19" t="n">
-        <v>602.115</v>
+        <v>602.429</v>
       </c>
       <c r="M19" t="n">
         <v>1.759</v>
       </c>
       <c r="N19" t="n">
-        <v>57.195</v>
+        <v>64.508</v>
       </c>
       <c r="O19" t="n">
-        <v>279.296</v>
+        <v>269.786</v>
       </c>
       <c r="P19" t="n">
-        <v>336.49</v>
+        <v>334.294</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.904999999999999</v>
+        <v>8.847</v>
       </c>
       <c r="R19" t="n">
         <v>410.711</v>
       </c>
       <c r="S19" t="n">
-        <v>616.264</v>
+        <v>616.477</v>
       </c>
       <c r="T19" t="n">
         <v>258.807</v>
       </c>
       <c r="U19" t="n">
-        <v>875.072</v>
+        <v>875.285</v>
       </c>
       <c r="V19" t="n">
         <v>267.193</v>
@@ -5338,28 +5338,28 @@
         <v>267.193</v>
       </c>
       <c r="Y19" t="n">
-        <v>2491.581</v>
+        <v>2489.911</v>
       </c>
       <c r="Z19" t="n">
         <v>20.634</v>
       </c>
       <c r="AA19" t="n">
-        <v>741.962</v>
+        <v>743.6319999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>23.093</v>
+        <v>23.145</v>
       </c>
       <c r="AC19" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD19" t="n">
         <v>526.458</v>
       </c>
       <c r="AE19" t="n">
-        <v>194.87</v>
+        <v>196.54</v>
       </c>
       <c r="AF19" t="n">
-        <v>164.372</v>
+        <v>166.481</v>
       </c>
       <c r="AG19" t="n">
         <v>37</v>
@@ -5368,34 +5368,34 @@
         <v>3.7</v>
       </c>
       <c r="AI19" t="n">
-        <v>325.941</v>
+        <v>329.72</v>
       </c>
       <c r="AJ19" t="n">
-        <v>57.04</v>
+        <v>57.701</v>
       </c>
       <c r="AK19" t="n">
         <v>17.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>268.902</v>
+        <v>272.019</v>
       </c>
       <c r="AM19" t="n">
         <v>565.0549999999999</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.476</v>
+        <v>0.481</v>
       </c>
       <c r="AO19" t="n">
-        <v>5.343</v>
+        <v>5.34</v>
       </c>
       <c r="AP19" t="n">
-        <v>18.74</v>
+        <v>18.75</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.394</v>
+        <v>5.051</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.473</v>
+        <v>10.405</v>
       </c>
       <c r="AS19" t="n">
         <v>11.296</v>
@@ -5404,10 +5404,10 @@
         <v>12.783</v>
       </c>
       <c r="AU19" t="n">
-        <v>15.428</v>
+        <v>15.457</v>
       </c>
       <c r="AV19" t="n">
-        <v>27.236</v>
+        <v>27.243</v>
       </c>
       <c r="AW19" t="n">
         <v>-3.335</v>
@@ -5416,19 +5416,19 @@
         <v>8.316000000000001</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.595000000000001</v>
+        <v>8.557</v>
       </c>
       <c r="AZ19" t="n">
-        <v>77.54900000000001</v>
+        <v>77.497</v>
       </c>
       <c r="BA19" t="n">
-        <v>-12.716</v>
+        <v>-12.595</v>
       </c>
       <c r="BB19" t="n">
-        <v>23.093</v>
+        <v>23.145</v>
       </c>
       <c r="BC19" t="n">
-        <v>-30.678</v>
+        <v>-30.574</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -5471,40 +5471,40 @@
         <v>29.253</v>
       </c>
       <c r="J20" t="n">
-        <v>99.89400000000001</v>
+        <v>100.208</v>
       </c>
       <c r="K20" t="n">
         <v>53.387</v>
       </c>
       <c r="L20" t="n">
-        <v>652.248</v>
+        <v>652.561</v>
       </c>
       <c r="M20" t="n">
         <v>1.763</v>
       </c>
       <c r="N20" t="n">
-        <v>63.063</v>
+        <v>71.361</v>
       </c>
       <c r="O20" t="n">
-        <v>300.056</v>
+        <v>290.795</v>
       </c>
       <c r="P20" t="n">
-        <v>363.12</v>
+        <v>362.157</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.936999999999999</v>
+        <v>8.914</v>
       </c>
       <c r="R20" t="n">
         <v>359.095</v>
       </c>
       <c r="S20" t="n">
-        <v>539.938</v>
+        <v>540.671</v>
       </c>
       <c r="T20" t="n">
         <v>237.645</v>
       </c>
       <c r="U20" t="n">
-        <v>777.5839999999999</v>
+        <v>778.316</v>
       </c>
       <c r="V20" t="n">
         <v>265.389</v>
@@ -5516,28 +5516,28 @@
         <v>265.389</v>
       </c>
       <c r="Y20" t="n">
-        <v>2417.435</v>
+        <v>2417.518</v>
       </c>
       <c r="Z20" t="n">
         <v>20.634</v>
       </c>
       <c r="AA20" t="n">
-        <v>2481.199</v>
+        <v>2481.116</v>
       </c>
       <c r="AB20" t="n">
-        <v>50.865</v>
+        <v>50.863</v>
       </c>
       <c r="AC20" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD20" t="n">
         <v>451.579</v>
       </c>
       <c r="AE20" t="n">
-        <v>2008.986</v>
+        <v>2008.903</v>
       </c>
       <c r="AF20" t="n">
-        <v>163.695</v>
+        <v>184.355</v>
       </c>
       <c r="AG20" t="n">
         <v>37</v>
@@ -5546,34 +5546,34 @@
         <v>3.7</v>
       </c>
       <c r="AI20" t="n">
-        <v>2139.381</v>
+        <v>2159.958</v>
       </c>
       <c r="AJ20" t="n">
-        <v>385.089</v>
+        <v>388.792</v>
       </c>
       <c r="AK20" t="n">
         <v>18</v>
       </c>
       <c r="AL20" t="n">
-        <v>1754.292</v>
+        <v>1771.165</v>
       </c>
       <c r="AM20" t="n">
         <v>591.676</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.965</v>
+        <v>2.993</v>
       </c>
       <c r="AO20" t="n">
-        <v>18.806</v>
+        <v>18.864</v>
       </c>
       <c r="AP20" t="n">
-        <v>13.371</v>
+        <v>13.378</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.866</v>
+        <v>5.585</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.444</v>
+        <v>7.424</v>
       </c>
       <c r="AS20" t="n">
         <v>7.836</v>
@@ -5582,10 +5582,10 @@
         <v>7.362</v>
       </c>
       <c r="AU20" t="n">
-        <v>32.92</v>
+        <v>33.045</v>
       </c>
       <c r="AV20" t="n">
-        <v>15.941</v>
+        <v>15.956</v>
       </c>
       <c r="AW20" t="n">
         <v>1.682</v>
@@ -5594,19 +5594,19 @@
         <v>5.441</v>
       </c>
       <c r="AY20" t="n">
-        <v>16.728</v>
+        <v>16.732</v>
       </c>
       <c r="AZ20" t="n">
-        <v>49.558</v>
+        <v>49.56</v>
       </c>
       <c r="BA20" t="n">
-        <v>20.975</v>
+        <v>20.971</v>
       </c>
       <c r="BB20" t="n">
-        <v>50.865</v>
+        <v>50.863</v>
       </c>
       <c r="BC20" t="n">
-        <v>34.161</v>
+        <v>35.451</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -5649,28 +5649,28 @@
         <v>26.176</v>
       </c>
       <c r="J21" t="n">
-        <v>99.89400000000001</v>
+        <v>100.208</v>
       </c>
       <c r="K21" t="n">
         <v>47.772</v>
       </c>
       <c r="L21" t="n">
-        <v>586.621</v>
+        <v>586.9349999999999</v>
       </c>
       <c r="M21" t="n">
         <v>1.759</v>
       </c>
       <c r="N21" t="n">
-        <v>54.635</v>
+        <v>61.824</v>
       </c>
       <c r="O21" t="n">
-        <v>265.064</v>
+        <v>256.883</v>
       </c>
       <c r="P21" t="n">
-        <v>319.699</v>
+        <v>318.707</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.794</v>
+        <v>8.766</v>
       </c>
       <c r="R21" t="n">
         <v>369.025</v>
@@ -5694,28 +5694,28 @@
         <v>276.411</v>
       </c>
       <c r="Y21" t="n">
-        <v>2309.864</v>
+        <v>2309.186</v>
       </c>
       <c r="Z21" t="n">
         <v>20.634</v>
       </c>
       <c r="AA21" t="n">
-        <v>938.706</v>
+        <v>939.385</v>
       </c>
       <c r="AB21" t="n">
-        <v>29.081</v>
+        <v>29.102</v>
       </c>
       <c r="AC21" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD21" t="n">
         <v>465.161</v>
       </c>
       <c r="AE21" t="n">
-        <v>452.912</v>
+        <v>453.59</v>
       </c>
       <c r="AF21" t="n">
-        <v>161.08</v>
+        <v>166.972</v>
       </c>
       <c r="AG21" t="n">
         <v>37</v>
@@ -5724,34 +5724,34 @@
         <v>3.7</v>
       </c>
       <c r="AI21" t="n">
-        <v>580.691</v>
+        <v>587.2619999999999</v>
       </c>
       <c r="AJ21" t="n">
-        <v>104.524</v>
+        <v>105.707</v>
       </c>
       <c r="AK21" t="n">
         <v>18</v>
       </c>
       <c r="AL21" t="n">
-        <v>476.167</v>
+        <v>481.555</v>
       </c>
       <c r="AM21" t="n">
         <v>586.352</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.821</v>
       </c>
       <c r="AO21" t="n">
-        <v>20.456</v>
+        <v>20.521</v>
       </c>
       <c r="AP21" t="n">
-        <v>18.173</v>
+        <v>18.183</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.511</v>
+        <v>5.184</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.904</v>
+        <v>9.872999999999999</v>
       </c>
       <c r="AS21" t="n">
         <v>10.157</v>
@@ -5772,19 +5772,19 @@
         <v>8.563000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>10.098</v>
+        <v>10.066</v>
       </c>
       <c r="AZ21" t="n">
-        <v>71.559</v>
+        <v>71.538</v>
       </c>
       <c r="BA21" t="n">
-        <v>19.428</v>
+        <v>19.515</v>
       </c>
       <c r="BB21" t="n">
-        <v>29.081</v>
+        <v>29.102</v>
       </c>
       <c r="BC21" t="n">
-        <v>45.015</v>
+        <v>46.656</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -5827,40 +5827,40 @@
         <v>34.528</v>
       </c>
       <c r="J22" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K22" t="n">
         <v>62.15</v>
       </c>
       <c r="L22" t="n">
-        <v>731.0549999999999</v>
+        <v>731.369</v>
       </c>
       <c r="M22" t="n">
         <v>1.533</v>
       </c>
       <c r="N22" t="n">
-        <v>57.678</v>
+        <v>65.267</v>
       </c>
       <c r="O22" t="n">
-        <v>263.315</v>
+        <v>255.188</v>
       </c>
       <c r="P22" t="n">
-        <v>320.993</v>
+        <v>320.455</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.694</v>
+        <v>6.682</v>
       </c>
       <c r="R22" t="n">
         <v>414.124</v>
       </c>
       <c r="S22" t="n">
-        <v>583.8680000000001</v>
+        <v>584.0700000000001</v>
       </c>
       <c r="T22" t="n">
         <v>245.202</v>
       </c>
       <c r="U22" t="n">
-        <v>829.0700000000001</v>
+        <v>829.272</v>
       </c>
       <c r="V22" t="n">
         <v>249.227</v>
@@ -5872,28 +5872,28 @@
         <v>249.227</v>
       </c>
       <c r="Y22" t="n">
-        <v>2544.469</v>
+        <v>2544.447</v>
       </c>
       <c r="Z22" t="n">
         <v>20.634</v>
       </c>
       <c r="AA22" t="n">
-        <v>596.103</v>
+        <v>596.125</v>
       </c>
       <c r="AB22" t="n">
-        <v>19.106</v>
+        <v>19.107</v>
       </c>
       <c r="AC22" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD22" t="n">
         <v>464.029</v>
       </c>
       <c r="AE22" t="n">
-        <v>111.44</v>
+        <v>111.462</v>
       </c>
       <c r="AF22" t="n">
-        <v>193.686</v>
+        <v>183.199</v>
       </c>
       <c r="AG22" t="n">
         <v>37</v>
@@ -5902,34 +5902,34 @@
         <v>3.7</v>
       </c>
       <c r="AI22" t="n">
-        <v>271.826</v>
+        <v>261.361</v>
       </c>
       <c r="AJ22" t="n">
-        <v>47.57</v>
+        <v>45.738</v>
       </c>
       <c r="AK22" t="n">
         <v>17.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>224.256</v>
+        <v>215.623</v>
       </c>
       <c r="AM22" t="n">
         <v>581.027</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.386</v>
+        <v>0.371</v>
       </c>
       <c r="AO22" t="n">
-        <v>25.827</v>
+        <v>25.881</v>
       </c>
       <c r="AP22" t="n">
-        <v>23.432</v>
+        <v>23.442</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.642</v>
+        <v>6.463</v>
       </c>
       <c r="AR22" t="n">
-        <v>10.288</v>
+        <v>10.271</v>
       </c>
       <c r="AS22" t="n">
         <v>10.433</v>
@@ -5938,10 +5938,10 @@
         <v>13.273</v>
       </c>
       <c r="AU22" t="n">
-        <v>19.119</v>
+        <v>19.148</v>
       </c>
       <c r="AV22" t="n">
-        <v>26.573</v>
+        <v>26.58</v>
       </c>
       <c r="AW22" t="n">
         <v>8.833</v>
@@ -5950,19 +5950,19 @@
         <v>7.988</v>
       </c>
       <c r="AY22" t="n">
-        <v>16.612</v>
+        <v>16.611</v>
       </c>
       <c r="AZ22" t="n">
-        <v>81.55500000000001</v>
+        <v>81.554</v>
       </c>
       <c r="BA22" t="n">
-        <v>14.856</v>
+        <v>14.86</v>
       </c>
       <c r="BB22" t="n">
-        <v>19.106</v>
+        <v>19.107</v>
       </c>
       <c r="BC22" t="n">
-        <v>48.448</v>
+        <v>42.733</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -6005,40 +6005,40 @@
         <v>32.276</v>
       </c>
       <c r="J23" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K23" t="n">
         <v>58.097</v>
       </c>
       <c r="L23" t="n">
-        <v>759.0700000000001</v>
+        <v>759.384</v>
       </c>
       <c r="M23" t="n">
         <v>1.78</v>
       </c>
       <c r="N23" t="n">
-        <v>60.939</v>
+        <v>68.958</v>
       </c>
       <c r="O23" t="n">
-        <v>282.56</v>
+        <v>273.839</v>
       </c>
       <c r="P23" t="n">
-        <v>343.5</v>
+        <v>342.797</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.663</v>
+        <v>7.647</v>
       </c>
       <c r="R23" t="n">
         <v>400.796</v>
       </c>
       <c r="S23" t="n">
-        <v>658.404</v>
+        <v>658.6319999999999</v>
       </c>
       <c r="T23" t="n">
         <v>276.504</v>
       </c>
       <c r="U23" t="n">
-        <v>934.909</v>
+        <v>935.136</v>
       </c>
       <c r="V23" t="n">
         <v>271.58</v>
@@ -6050,28 +6050,28 @@
         <v>271.58</v>
       </c>
       <c r="Y23" t="n">
-        <v>2709.855</v>
+        <v>2709.694</v>
       </c>
       <c r="Z23" t="n">
         <v>20.634</v>
       </c>
       <c r="AA23" t="n">
-        <v>1500.684</v>
+        <v>1500.845</v>
       </c>
       <c r="AB23" t="n">
-        <v>35.817</v>
+        <v>35.821</v>
       </c>
       <c r="AC23" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD23" t="n">
         <v>551.176</v>
       </c>
       <c r="AE23" t="n">
-        <v>928.875</v>
+        <v>929.0359999999999</v>
       </c>
       <c r="AF23" t="n">
-        <v>207.772</v>
+        <v>208.203</v>
       </c>
       <c r="AG23" t="n">
         <v>37</v>
@@ -6080,34 +6080,34 @@
         <v>3.7</v>
       </c>
       <c r="AI23" t="n">
-        <v>1103.347</v>
+        <v>1103.938</v>
       </c>
       <c r="AJ23" t="n">
-        <v>193.086</v>
+        <v>193.189</v>
       </c>
       <c r="AK23" t="n">
         <v>17.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>910.261</v>
+        <v>910.749</v>
       </c>
       <c r="AM23" t="n">
         <v>575.703</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.581</v>
+        <v>1.582</v>
       </c>
       <c r="AO23" t="n">
-        <v>19.916</v>
+        <v>19.966</v>
       </c>
       <c r="AP23" t="n">
-        <v>18.117</v>
+        <v>18.124</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.347</v>
+        <v>6.129</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.198</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="AS23" t="n">
         <v>7.165</v>
@@ -6116,10 +6116,10 @@
         <v>9.566000000000001</v>
       </c>
       <c r="AU23" t="n">
-        <v>15.707</v>
+        <v>15.735</v>
       </c>
       <c r="AV23" t="n">
-        <v>22.313</v>
+        <v>22.319</v>
       </c>
       <c r="AW23" t="n">
         <v>20.702</v>
@@ -6128,19 +6128,19 @@
         <v>6.482</v>
       </c>
       <c r="AY23" t="n">
-        <v>14.679</v>
+        <v>14.672</v>
       </c>
       <c r="AZ23" t="n">
-        <v>64.676</v>
+        <v>64.672</v>
       </c>
       <c r="BA23" t="n">
-        <v>19.007</v>
+        <v>19.02</v>
       </c>
       <c r="BB23" t="n">
-        <v>35.817</v>
+        <v>35.821</v>
       </c>
       <c r="BC23" t="n">
-        <v>15.411</v>
+        <v>15.473</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -6183,40 +6183,40 @@
         <v>32.235</v>
       </c>
       <c r="J24" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K24" t="n">
         <v>58.023</v>
       </c>
       <c r="L24" t="n">
-        <v>739.048</v>
+        <v>739.362</v>
       </c>
       <c r="M24" t="n">
         <v>1.763</v>
       </c>
       <c r="N24" t="n">
-        <v>68.423</v>
+        <v>77.221</v>
       </c>
       <c r="O24" t="n">
-        <v>317.657</v>
+        <v>307.036</v>
       </c>
       <c r="P24" t="n">
-        <v>386.08</v>
+        <v>384.257</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.624000000000001</v>
+        <v>8.583</v>
       </c>
       <c r="R24" t="n">
         <v>399.659</v>
       </c>
       <c r="S24" t="n">
-        <v>577.2910000000001</v>
+        <v>577.491</v>
       </c>
       <c r="T24" t="n">
         <v>242.44</v>
       </c>
       <c r="U24" t="n">
-        <v>819.731</v>
+        <v>819.931</v>
       </c>
       <c r="V24" t="n">
         <v>256.539</v>
@@ -6228,28 +6228,28 @@
         <v>256.539</v>
       </c>
       <c r="Y24" t="n">
-        <v>2601.058</v>
+        <v>2599.748</v>
       </c>
       <c r="Z24" t="n">
         <v>20.634</v>
       </c>
       <c r="AA24" t="n">
-        <v>2979.524</v>
+        <v>2980.834</v>
       </c>
       <c r="AB24" t="n">
-        <v>53.589</v>
+        <v>53.613</v>
       </c>
       <c r="AC24" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD24" t="n">
         <v>511.087</v>
       </c>
       <c r="AE24" t="n">
-        <v>2447.803</v>
+        <v>2449.113</v>
       </c>
       <c r="AF24" t="n">
-        <v>173.537</v>
+        <v>196.955</v>
       </c>
       <c r="AG24" t="n">
         <v>37</v>
@@ -6258,34 +6258,34 @@
         <v>3.7</v>
       </c>
       <c r="AI24" t="n">
-        <v>2588.04</v>
+        <v>2612.768</v>
       </c>
       <c r="AJ24" t="n">
-        <v>452.907</v>
+        <v>457.234</v>
       </c>
       <c r="AK24" t="n">
         <v>17.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>2135.133</v>
+        <v>2155.533</v>
       </c>
       <c r="AM24" t="n">
         <v>570.379</v>
       </c>
       <c r="AN24" t="n">
-        <v>3.743</v>
+        <v>3.779</v>
       </c>
       <c r="AO24" t="n">
-        <v>13.308</v>
+        <v>13.302</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.292</v>
+        <v>13.298</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.323</v>
+        <v>6.102</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.944</v>
+        <v>6.911</v>
       </c>
       <c r="AS24" t="n">
         <v>11.296</v>
@@ -6294,10 +6294,10 @@
         <v>7.188</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.42</v>
+        <v>5.347</v>
       </c>
       <c r="AV24" t="n">
-        <v>14.744</v>
+        <v>14.747</v>
       </c>
       <c r="AW24" t="n">
         <v>-3.335</v>
@@ -6306,19 +6306,19 @@
         <v>4.614</v>
       </c>
       <c r="AY24" t="n">
-        <v>7.596</v>
+        <v>7.538</v>
       </c>
       <c r="AZ24" t="n">
-        <v>46.782</v>
+        <v>46.758</v>
       </c>
       <c r="BA24" t="n">
-        <v>20.084</v>
+        <v>20.141</v>
       </c>
       <c r="BB24" t="n">
-        <v>53.589</v>
+        <v>53.613</v>
       </c>
       <c r="BC24" t="n">
-        <v>26.253</v>
+        <v>26.245</v>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
@@ -6361,40 +6361,40 @@
         <v>28.815</v>
       </c>
       <c r="J25" t="n">
-        <v>111.394</v>
+        <v>111.708</v>
       </c>
       <c r="K25" t="n">
         <v>51.867</v>
       </c>
       <c r="L25" t="n">
-        <v>654.457</v>
+        <v>654.771</v>
       </c>
       <c r="M25" t="n">
         <v>1.759</v>
       </c>
       <c r="N25" t="n">
-        <v>60.179</v>
+        <v>67.886</v>
       </c>
       <c r="O25" t="n">
-        <v>279.673</v>
+        <v>270.2</v>
       </c>
       <c r="P25" t="n">
-        <v>339.852</v>
+        <v>338.086</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.492000000000001</v>
+        <v>8.448</v>
       </c>
       <c r="R25" t="n">
         <v>410.711</v>
       </c>
       <c r="S25" t="n">
-        <v>616.264</v>
+        <v>616.477</v>
       </c>
       <c r="T25" t="n">
         <v>258.807</v>
       </c>
       <c r="U25" t="n">
-        <v>875.072</v>
+        <v>875.285</v>
       </c>
       <c r="V25" t="n">
         <v>267.193</v>
@@ -6406,28 +6406,28 @@
         <v>267.193</v>
       </c>
       <c r="Y25" t="n">
-        <v>2547.285</v>
+        <v>2546.046</v>
       </c>
       <c r="Z25" t="n">
         <v>20.634</v>
       </c>
       <c r="AA25" t="n">
-        <v>1174.302</v>
+        <v>1175.541</v>
       </c>
       <c r="AB25" t="n">
-        <v>31.73</v>
+        <v>31.763</v>
       </c>
       <c r="AC25" t="n">
-        <v>96.31399999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AD25" t="n">
         <v>526.458</v>
       </c>
       <c r="AE25" t="n">
-        <v>627.21</v>
+        <v>628.449</v>
       </c>
       <c r="AF25" t="n">
-        <v>169.348</v>
+        <v>175.914</v>
       </c>
       <c r="AG25" t="n">
         <v>37</v>
@@ -6436,34 +6436,34 @@
         <v>3.7</v>
       </c>
       <c r="AI25" t="n">
-        <v>763.258</v>
+        <v>771.063</v>
       </c>
       <c r="AJ25" t="n">
-        <v>133.57</v>
+        <v>134.936</v>
       </c>
       <c r="AK25" t="n">
         <v>17.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>629.688</v>
+        <v>636.127</v>
       </c>
       <c r="AM25" t="n">
         <v>565.0549999999999</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.114</v>
+        <v>1.126</v>
       </c>
       <c r="AO25" t="n">
-        <v>11.564</v>
+        <v>11.558</v>
       </c>
       <c r="AP25" t="n">
-        <v>17.683</v>
+        <v>17.692</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.304</v>
+        <v>6.08</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.183</v>
+        <v>9.135</v>
       </c>
       <c r="AS25" t="n">
         <v>11.296</v>
@@ -6472,10 +6472,10 @@
         <v>11.097</v>
       </c>
       <c r="AU25" t="n">
-        <v>15.428</v>
+        <v>15.457</v>
       </c>
       <c r="AV25" t="n">
-        <v>23.644</v>
+        <v>23.65</v>
       </c>
       <c r="AW25" t="n">
         <v>-3.335</v>
@@ -6484,19 +6484,19 @@
         <v>7.22</v>
       </c>
       <c r="AY25" t="n">
-        <v>10.279</v>
+        <v>10.257</v>
       </c>
       <c r="AZ25" t="n">
-        <v>68.828</v>
+        <v>68.794</v>
       </c>
       <c r="BA25" t="n">
-        <v>25.098</v>
+        <v>25.14</v>
       </c>
       <c r="BB25" t="n">
-        <v>31.73</v>
+        <v>31.763</v>
       </c>
       <c r="BC25" t="n">
-        <v>37.225</v>
+        <v>37.077</v>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
@@ -6539,40 +6539,40 @@
         <v>34.189</v>
       </c>
       <c r="J26" t="n">
-        <v>84.941</v>
+        <v>85.116</v>
       </c>
       <c r="K26" t="n">
         <v>52.853</v>
       </c>
       <c r="L26" t="n">
-        <v>646.909</v>
+        <v>647.085</v>
       </c>
       <c r="M26" t="n">
         <v>1.825</v>
       </c>
       <c r="N26" t="n">
-        <v>52.728</v>
+        <v>59.758</v>
       </c>
       <c r="O26" t="n">
-        <v>323.621</v>
+        <v>316.006</v>
       </c>
       <c r="P26" t="n">
-        <v>376.348</v>
+        <v>375.764</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.356999999999999</v>
+        <v>9.342000000000001</v>
       </c>
       <c r="R26" t="n">
         <v>365.684</v>
       </c>
       <c r="S26" t="n">
-        <v>514.009</v>
+        <v>514.418</v>
       </c>
       <c r="T26" t="n">
         <v>252.755</v>
       </c>
       <c r="U26" t="n">
-        <v>766.764</v>
+        <v>767.173</v>
       </c>
       <c r="V26" t="n">
         <v>272.972</v>
@@ -6596,7 +6596,7 @@
         <v>49.875</v>
       </c>
       <c r="AC26" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD26" t="n">
         <v>451.579</v>
@@ -6605,7 +6605,7 @@
         <v>1923.779</v>
       </c>
       <c r="AF26" t="n">
-        <v>159.514</v>
+        <v>175.138</v>
       </c>
       <c r="AG26" t="n">
         <v>37</v>
@@ -6614,34 +6614,34 @@
         <v>3.7</v>
       </c>
       <c r="AI26" t="n">
-        <v>2049.993</v>
+        <v>2065.617</v>
       </c>
       <c r="AJ26" t="n">
-        <v>368.999</v>
+        <v>371.811</v>
       </c>
       <c r="AK26" t="n">
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>1680.995</v>
+        <v>1693.806</v>
       </c>
       <c r="AM26" t="n">
         <v>591.676</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.841</v>
+        <v>2.863</v>
       </c>
       <c r="AO26" t="n">
-        <v>17.834</v>
+        <v>17.866</v>
       </c>
       <c r="AP26" t="n">
-        <v>13.466</v>
+        <v>13.47</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.723000000000001</v>
+        <v>9.552</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.834</v>
+        <v>7.822</v>
       </c>
       <c r="AS26" t="n">
         <v>9.815</v>
@@ -6650,10 +6650,10 @@
         <v>7.612</v>
       </c>
       <c r="AU26" t="n">
-        <v>31.071</v>
+        <v>31.141</v>
       </c>
       <c r="AV26" t="n">
-        <v>15.961</v>
+        <v>15.969</v>
       </c>
       <c r="AW26" t="n">
         <v>4.587</v>
@@ -6674,7 +6674,7 @@
         <v>49.875</v>
       </c>
       <c r="BC26" t="n">
-        <v>28.555</v>
+        <v>29.535</v>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
@@ -6717,28 +6717,28 @@
         <v>30.693</v>
       </c>
       <c r="J27" t="n">
-        <v>84.941</v>
+        <v>85.116</v>
       </c>
       <c r="K27" t="n">
         <v>47.447</v>
       </c>
       <c r="L27" t="n">
-        <v>581.7140000000001</v>
+        <v>581.889</v>
       </c>
       <c r="M27" t="n">
         <v>1.821</v>
       </c>
       <c r="N27" t="n">
-        <v>45.829</v>
+        <v>51.939</v>
       </c>
       <c r="O27" t="n">
-        <v>285.881</v>
+        <v>279.154</v>
       </c>
       <c r="P27" t="n">
-        <v>331.709</v>
+        <v>331.093</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.186</v>
+        <v>9.169</v>
       </c>
       <c r="R27" t="n">
         <v>375.796</v>
@@ -6762,28 +6762,28 @@
         <v>284.308</v>
       </c>
       <c r="Y27" t="n">
-        <v>2376.013</v>
+        <v>2375.572</v>
       </c>
       <c r="Z27" t="n">
         <v>20.634</v>
       </c>
       <c r="AA27" t="n">
-        <v>822.729</v>
+        <v>823.17</v>
       </c>
       <c r="AB27" t="n">
-        <v>25.887</v>
+        <v>25.901</v>
       </c>
       <c r="AC27" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD27" t="n">
         <v>465.161</v>
       </c>
       <c r="AE27" t="n">
-        <v>336.934</v>
+        <v>337.375</v>
       </c>
       <c r="AF27" t="n">
-        <v>157.179</v>
+        <v>158.89</v>
       </c>
       <c r="AG27" t="n">
         <v>37</v>
@@ -6792,34 +6792,34 @@
         <v>3.7</v>
       </c>
       <c r="AI27" t="n">
-        <v>460.813</v>
+        <v>462.965</v>
       </c>
       <c r="AJ27" t="n">
-        <v>82.946</v>
+        <v>83.334</v>
       </c>
       <c r="AK27" t="n">
         <v>18</v>
       </c>
       <c r="AL27" t="n">
-        <v>377.867</v>
+        <v>379.631</v>
       </c>
       <c r="AM27" t="n">
         <v>586.352</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.644</v>
+        <v>0.647</v>
       </c>
       <c r="AO27" t="n">
-        <v>19.448</v>
+        <v>19.484</v>
       </c>
       <c r="AP27" t="n">
-        <v>18.304</v>
+        <v>18.309</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.475</v>
+        <v>9.272</v>
       </c>
       <c r="AR27" t="n">
-        <v>10.437</v>
+        <v>10.418</v>
       </c>
       <c r="AS27" t="n">
         <v>12.178</v>
@@ -6840,19 +6840,19 @@
         <v>8.946</v>
       </c>
       <c r="AY27" t="n">
-        <v>13.251</v>
+        <v>13.23</v>
       </c>
       <c r="AZ27" t="n">
-        <v>74.762</v>
+        <v>74.748</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.673</v>
+        <v>4.729</v>
       </c>
       <c r="BB27" t="n">
-        <v>25.887</v>
+        <v>25.901</v>
       </c>
       <c r="BC27" t="n">
-        <v>15.078</v>
+        <v>15.615</v>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
@@ -6895,40 +6895,40 @@
         <v>39.907</v>
       </c>
       <c r="J28" t="n">
-        <v>106.441</v>
+        <v>106.616</v>
       </c>
       <c r="K28" t="n">
         <v>60.846</v>
       </c>
       <c r="L28" t="n">
-        <v>724.444</v>
+        <v>724.619</v>
       </c>
       <c r="M28" t="n">
         <v>1.587</v>
       </c>
       <c r="N28" t="n">
-        <v>47.552</v>
+        <v>53.893</v>
       </c>
       <c r="O28" t="n">
-        <v>283.994</v>
+        <v>277.311</v>
       </c>
       <c r="P28" t="n">
-        <v>331.546</v>
+        <v>331.204</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.062</v>
+        <v>7.054</v>
       </c>
       <c r="R28" t="n">
         <v>433.04</v>
       </c>
       <c r="S28" t="n">
-        <v>620.085</v>
+        <v>620.205</v>
       </c>
       <c r="T28" t="n">
         <v>264.934</v>
       </c>
       <c r="U28" t="n">
-        <v>885.019</v>
+        <v>885.139</v>
       </c>
       <c r="V28" t="n">
         <v>260.337</v>
@@ -6940,28 +6940,28 @@
         <v>260.337</v>
       </c>
       <c r="Y28" t="n">
-        <v>2634.385</v>
+        <v>2634.338</v>
       </c>
       <c r="Z28" t="n">
         <v>20.634</v>
       </c>
       <c r="AA28" t="n">
-        <v>439.378</v>
+        <v>439.425</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.391</v>
+        <v>14.393</v>
       </c>
       <c r="AC28" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD28" t="n">
         <v>464.029</v>
       </c>
       <c r="AE28" t="n">
-        <v>-45.285</v>
+        <v>-45.238</v>
       </c>
       <c r="AF28" t="n">
-        <v>186.568</v>
+        <v>172.18</v>
       </c>
       <c r="AG28" t="n">
         <v>37</v>
@@ -6970,34 +6970,34 @@
         <v>3.7</v>
       </c>
       <c r="AI28" t="n">
-        <v>107.983</v>
+        <v>93.642</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18.897</v>
+        <v>16.387</v>
       </c>
       <c r="AK28" t="n">
         <v>17.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>89.086</v>
+        <v>77.255</v>
       </c>
       <c r="AM28" t="n">
         <v>581.027</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.153</v>
+        <v>0.133</v>
       </c>
       <c r="AO28" t="n">
-        <v>24.689</v>
+        <v>24.719</v>
       </c>
       <c r="AP28" t="n">
-        <v>23.728</v>
+        <v>23.734</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10.148</v>
+        <v>10.034</v>
       </c>
       <c r="AR28" t="n">
-        <v>10.859</v>
+        <v>10.848</v>
       </c>
       <c r="AS28" t="n">
         <v>15.477</v>
@@ -7006,10 +7006,10 @@
         <v>14.183</v>
       </c>
       <c r="AU28" t="n">
-        <v>27.158</v>
+        <v>27.175</v>
       </c>
       <c r="AV28" t="n">
-        <v>28.987</v>
+        <v>28.991</v>
       </c>
       <c r="AW28" t="n">
         <v>13.684</v>
@@ -7018,19 +7018,19 @@
         <v>8.526999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>20.733</v>
+        <v>20.73</v>
       </c>
       <c r="AZ28" t="n">
-        <v>86.285</v>
+        <v>86.283</v>
       </c>
       <c r="BA28" t="n">
-        <v>-15.341</v>
+        <v>-15.332</v>
       </c>
       <c r="BB28" t="n">
-        <v>14.391</v>
+        <v>14.393</v>
       </c>
       <c r="BC28" t="n">
-        <v>-41.029</v>
+        <v>-48.861</v>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
@@ -7073,40 +7073,40 @@
         <v>37.093</v>
       </c>
       <c r="J29" t="n">
-        <v>106.441</v>
+        <v>106.616</v>
       </c>
       <c r="K29" t="n">
         <v>56.556</v>
       </c>
       <c r="L29" t="n">
-        <v>746.295</v>
+        <v>746.47</v>
       </c>
       <c r="M29" t="n">
         <v>1.842</v>
       </c>
       <c r="N29" t="n">
-        <v>49.956</v>
+        <v>56.617</v>
       </c>
       <c r="O29" t="n">
-        <v>304.751</v>
+        <v>297.58</v>
       </c>
       <c r="P29" t="n">
-        <v>354.707</v>
+        <v>354.197</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.128</v>
+        <v>8.117000000000001</v>
       </c>
       <c r="R29" t="n">
         <v>419.104</v>
       </c>
       <c r="S29" t="n">
-        <v>699.245</v>
+        <v>699.38</v>
       </c>
       <c r="T29" t="n">
         <v>298.755</v>
       </c>
       <c r="U29" t="n">
-        <v>998</v>
+        <v>998.135</v>
       </c>
       <c r="V29" t="n">
         <v>283.687</v>
@@ -7118,28 +7118,28 @@
         <v>283.687</v>
       </c>
       <c r="Y29" t="n">
-        <v>2801.792</v>
+        <v>2801.592</v>
       </c>
       <c r="Z29" t="n">
         <v>20.634</v>
       </c>
       <c r="AA29" t="n">
-        <v>1247.823</v>
+        <v>1248.022</v>
       </c>
       <c r="AB29" t="n">
-        <v>30.971</v>
+        <v>30.976</v>
       </c>
       <c r="AC29" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD29" t="n">
         <v>551.176</v>
       </c>
       <c r="AE29" t="n">
-        <v>676.013</v>
+        <v>676.213</v>
       </c>
       <c r="AF29" t="n">
-        <v>199.195</v>
+        <v>192.507</v>
       </c>
       <c r="AG29" t="n">
         <v>37</v>
@@ -7148,34 +7148,34 @@
         <v>3.7</v>
       </c>
       <c r="AI29" t="n">
-        <v>841.908</v>
+        <v>835.419</v>
       </c>
       <c r="AJ29" t="n">
-        <v>147.334</v>
+        <v>146.198</v>
       </c>
       <c r="AK29" t="n">
         <v>17.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>694.574</v>
+        <v>689.221</v>
       </c>
       <c r="AM29" t="n">
         <v>575.703</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.206</v>
+        <v>1.197</v>
       </c>
       <c r="AO29" t="n">
-        <v>17.898</v>
+        <v>17.926</v>
       </c>
       <c r="AP29" t="n">
-        <v>18.523</v>
+        <v>18.528</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9.816000000000001</v>
+        <v>9.659000000000001</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.804</v>
+        <v>8.791</v>
       </c>
       <c r="AS29" t="n">
         <v>12.06</v>
@@ -7184,10 +7184,10 @@
         <v>10.402</v>
       </c>
       <c r="AU29" t="n">
-        <v>23.515</v>
+        <v>23.532</v>
       </c>
       <c r="AV29" t="n">
-        <v>24.771</v>
+        <v>24.774</v>
       </c>
       <c r="AW29" t="n">
         <v>26.083</v>
@@ -7196,19 +7196,19 @@
         <v>7.041</v>
       </c>
       <c r="AY29" t="n">
-        <v>18.569</v>
+        <v>18.561</v>
       </c>
       <c r="AZ29" t="n">
-        <v>69.541</v>
+        <v>69.536</v>
       </c>
       <c r="BA29" t="n">
-        <v>-1.045</v>
+        <v>-1.029</v>
       </c>
       <c r="BB29" t="n">
-        <v>30.971</v>
+        <v>30.976</v>
       </c>
       <c r="BC29" t="n">
-        <v>-11.936</v>
+        <v>-12.615</v>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
@@ -7251,40 +7251,40 @@
         <v>36.823</v>
       </c>
       <c r="J30" t="n">
-        <v>106.441</v>
+        <v>106.616</v>
       </c>
       <c r="K30" t="n">
         <v>56.145</v>
       </c>
       <c r="L30" t="n">
-        <v>717.449</v>
+        <v>717.624</v>
       </c>
       <c r="M30" t="n">
         <v>1.825</v>
       </c>
       <c r="N30" t="n">
-        <v>58.37</v>
+        <v>66.04900000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>355.085</v>
+        <v>346.192</v>
       </c>
       <c r="P30" t="n">
-        <v>413.454</v>
+        <v>412.241</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.544</v>
+        <v>9.516</v>
       </c>
       <c r="R30" t="n">
         <v>417.914</v>
       </c>
       <c r="S30" t="n">
-        <v>613.101</v>
+        <v>613.2190000000001</v>
       </c>
       <c r="T30" t="n">
         <v>261.949</v>
       </c>
       <c r="U30" t="n">
-        <v>875.05</v>
+        <v>875.168</v>
       </c>
       <c r="V30" t="n">
         <v>267.975</v>
@@ -7296,28 +7296,28 @@
         <v>267.975</v>
       </c>
       <c r="Y30" t="n">
-        <v>2691.842</v>
+        <v>2690.922</v>
       </c>
       <c r="Z30" t="n">
         <v>20.634</v>
       </c>
       <c r="AA30" t="n">
-        <v>2609.524</v>
+        <v>2610.444</v>
       </c>
       <c r="AB30" t="n">
-        <v>49.416</v>
+        <v>49.433</v>
       </c>
       <c r="AC30" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD30" t="n">
         <v>511.087</v>
       </c>
       <c r="AE30" t="n">
-        <v>2077.803</v>
+        <v>2078.723</v>
       </c>
       <c r="AF30" t="n">
-        <v>159.639</v>
+        <v>181.974</v>
       </c>
       <c r="AG30" t="n">
         <v>37</v>
@@ -7326,34 +7326,34 @@
         <v>3.7</v>
       </c>
       <c r="AI30" t="n">
-        <v>2204.143</v>
+        <v>2227.397</v>
       </c>
       <c r="AJ30" t="n">
-        <v>385.725</v>
+        <v>389.795</v>
       </c>
       <c r="AK30" t="n">
         <v>17.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>1818.418</v>
+        <v>1837.603</v>
       </c>
       <c r="AM30" t="n">
         <v>570.379</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.188</v>
+        <v>3.222</v>
       </c>
       <c r="AO30" t="n">
-        <v>10.904</v>
+        <v>10.901</v>
       </c>
       <c r="AP30" t="n">
-        <v>13.586</v>
+        <v>13.589</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9.859</v>
+        <v>9.707000000000001</v>
       </c>
       <c r="AR30" t="n">
-        <v>7.829</v>
+        <v>7.807</v>
       </c>
       <c r="AS30" t="n">
         <v>14.283</v>
@@ -7362,10 +7362,10 @@
         <v>7.914</v>
       </c>
       <c r="AU30" t="n">
-        <v>14.123</v>
+        <v>14.077</v>
       </c>
       <c r="AV30" t="n">
-        <v>16.571</v>
+        <v>16.573</v>
       </c>
       <c r="AW30" t="n">
         <v>-1.831</v>
@@ -7374,19 +7374,19 @@
         <v>5.075</v>
       </c>
       <c r="AY30" t="n">
-        <v>10.836</v>
+        <v>10.798</v>
       </c>
       <c r="AZ30" t="n">
-        <v>50.975</v>
+        <v>50.957</v>
       </c>
       <c r="BA30" t="n">
-        <v>8.912000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BB30" t="n">
-        <v>49.416</v>
+        <v>49.433</v>
       </c>
       <c r="BC30" t="n">
-        <v>12.214</v>
+        <v>12.54</v>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
@@ -7429,40 +7429,40 @@
         <v>33</v>
       </c>
       <c r="J31" t="n">
-        <v>106.441</v>
+        <v>106.616</v>
       </c>
       <c r="K31" t="n">
         <v>50.316</v>
       </c>
       <c r="L31" t="n">
-        <v>642.025</v>
+        <v>642.2</v>
       </c>
       <c r="M31" t="n">
         <v>1.821</v>
       </c>
       <c r="N31" t="n">
-        <v>51.357</v>
+        <v>58.097</v>
       </c>
       <c r="O31" t="n">
-        <v>312.968</v>
+        <v>305.036</v>
       </c>
       <c r="P31" t="n">
-        <v>364.325</v>
+        <v>363.133</v>
       </c>
       <c r="Q31" t="n">
-        <v>9.384</v>
+        <v>9.353</v>
       </c>
       <c r="R31" t="n">
         <v>429.471</v>
       </c>
       <c r="S31" t="n">
-        <v>654.492</v>
+        <v>654.6180000000001</v>
       </c>
       <c r="T31" t="n">
         <v>279.634</v>
       </c>
       <c r="U31" t="n">
-        <v>934.125</v>
+        <v>934.251</v>
       </c>
       <c r="V31" t="n">
         <v>279.104</v>
@@ -7474,28 +7474,28 @@
         <v>279.104</v>
       </c>
       <c r="Y31" t="n">
-        <v>2649.049</v>
+        <v>2648.159</v>
       </c>
       <c r="Z31" t="n">
         <v>20.634</v>
       </c>
       <c r="AA31" t="n">
-        <v>837.349</v>
+        <v>838.24</v>
       </c>
       <c r="AB31" t="n">
-        <v>24.161</v>
+        <v>24.186</v>
       </c>
       <c r="AC31" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD31" t="n">
         <v>526.458</v>
       </c>
       <c r="AE31" t="n">
-        <v>290.257</v>
+        <v>291.147</v>
       </c>
       <c r="AF31" t="n">
-        <v>156.779</v>
+        <v>163.983</v>
       </c>
       <c r="AG31" t="n">
         <v>37</v>
@@ -7504,34 +7504,34 @@
         <v>3.7</v>
       </c>
       <c r="AI31" t="n">
-        <v>413.736</v>
+        <v>421.831</v>
       </c>
       <c r="AJ31" t="n">
-        <v>72.404</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="AK31" t="n">
         <v>17.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>341.332</v>
+        <v>348.01</v>
       </c>
       <c r="AM31" t="n">
         <v>565.0549999999999</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.604</v>
+        <v>0.616</v>
       </c>
       <c r="AO31" t="n">
-        <v>10.368</v>
+        <v>10.365</v>
       </c>
       <c r="AP31" t="n">
-        <v>18.525</v>
+        <v>18.53</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9.833</v>
+        <v>9.677</v>
       </c>
       <c r="AR31" t="n">
-        <v>10.512</v>
+        <v>10.478</v>
       </c>
       <c r="AS31" t="n">
         <v>14.283</v>
@@ -7540,10 +7540,10 @@
         <v>12.392</v>
       </c>
       <c r="AU31" t="n">
-        <v>16.404</v>
+        <v>16.42</v>
       </c>
       <c r="AV31" t="n">
-        <v>26.953</v>
+        <v>26.957</v>
       </c>
       <c r="AW31" t="n">
         <v>-1.831</v>
@@ -7552,19 +7552,19 @@
         <v>8.053000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>11.491</v>
+        <v>11.475</v>
       </c>
       <c r="AZ31" t="n">
-        <v>76.435</v>
+        <v>76.40900000000001</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.777</v>
+        <v>1.831</v>
       </c>
       <c r="BB31" t="n">
-        <v>24.161</v>
+        <v>24.186</v>
       </c>
       <c r="BC31" t="n">
-        <v>-6.264</v>
+        <v>-4.874</v>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
@@ -7607,40 +7607,40 @@
         <v>24.134</v>
       </c>
       <c r="J32" t="n">
-        <v>115.762</v>
+        <v>116.063</v>
       </c>
       <c r="K32" t="n">
         <v>52.853</v>
       </c>
       <c r="L32" t="n">
-        <v>635.348</v>
+        <v>635.65</v>
       </c>
       <c r="M32" t="n">
         <v>1.7</v>
       </c>
       <c r="N32" t="n">
-        <v>78.328</v>
+        <v>84.59399999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>272.685</v>
+        <v>265.413</v>
       </c>
       <c r="P32" t="n">
-        <v>351.013</v>
+        <v>350.007</v>
       </c>
       <c r="Q32" t="n">
-        <v>8.727</v>
+        <v>8.702</v>
       </c>
       <c r="R32" t="n">
         <v>352.506</v>
       </c>
       <c r="S32" t="n">
-        <v>562.169</v>
+        <v>562.872</v>
       </c>
       <c r="T32" t="n">
         <v>222.535</v>
       </c>
       <c r="U32" t="n">
-        <v>784.704</v>
+        <v>785.408</v>
       </c>
       <c r="V32" t="n">
         <v>257.807</v>
@@ -7658,13 +7658,13 @@
         <v>20.634</v>
       </c>
       <c r="AA32" t="n">
-        <v>2443.293</v>
+        <v>2443.292</v>
       </c>
       <c r="AB32" t="n">
         <v>50.859</v>
       </c>
       <c r="AC32" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD32" t="n">
         <v>451.579</v>
@@ -7673,7 +7673,7 @@
         <v>1971.079</v>
       </c>
       <c r="AF32" t="n">
-        <v>162.889</v>
+        <v>183.549</v>
       </c>
       <c r="AG32" t="n">
         <v>37</v>
@@ -7682,34 +7682,34 @@
         <v>3.7</v>
       </c>
       <c r="AI32" t="n">
-        <v>2100.669</v>
+        <v>2121.328</v>
       </c>
       <c r="AJ32" t="n">
-        <v>378.12</v>
+        <v>381.839</v>
       </c>
       <c r="AK32" t="n">
         <v>18</v>
       </c>
       <c r="AL32" t="n">
-        <v>1722.548</v>
+        <v>1739.489</v>
       </c>
       <c r="AM32" t="n">
         <v>591.676</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.911</v>
+        <v>2.94</v>
       </c>
       <c r="AO32" t="n">
-        <v>15.728</v>
+        <v>15.783</v>
       </c>
       <c r="AP32" t="n">
-        <v>13.225</v>
+        <v>13.232</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.336</v>
+        <v>2.043</v>
       </c>
       <c r="AR32" t="n">
-        <v>7.307</v>
+        <v>7.286</v>
       </c>
       <c r="AS32" t="n">
         <v>5.858</v>
@@ -7718,10 +7718,10 @@
         <v>7.338</v>
       </c>
       <c r="AU32" t="n">
-        <v>34.137</v>
+        <v>34.258</v>
       </c>
       <c r="AV32" t="n">
-        <v>16.334</v>
+        <v>16.349</v>
       </c>
       <c r="AW32" t="n">
         <v>-1.224</v>
@@ -7742,7 +7742,7 @@
         <v>50.859</v>
       </c>
       <c r="BC32" t="n">
-        <v>31.733</v>
+        <v>33.029</v>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
@@ -7785,28 +7785,28 @@
         <v>21.665</v>
       </c>
       <c r="J33" t="n">
-        <v>115.762</v>
+        <v>116.063</v>
       </c>
       <c r="K33" t="n">
         <v>47.447</v>
       </c>
       <c r="L33" t="n">
-        <v>575.013</v>
+        <v>575.314</v>
       </c>
       <c r="M33" t="n">
         <v>1.697</v>
       </c>
       <c r="N33" t="n">
-        <v>68.07899999999999</v>
+        <v>73.52500000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>240.885</v>
+        <v>234.461</v>
       </c>
       <c r="P33" t="n">
-        <v>308.964</v>
+        <v>307.986</v>
       </c>
       <c r="Q33" t="n">
-        <v>8.555999999999999</v>
+        <v>8.529</v>
       </c>
       <c r="R33" t="n">
         <v>362.254</v>
@@ -7830,28 +7830,28 @@
         <v>268.513</v>
       </c>
       <c r="Y33" t="n">
-        <v>2228.474</v>
+        <v>2227.798</v>
       </c>
       <c r="Z33" t="n">
         <v>20.634</v>
       </c>
       <c r="AA33" t="n">
-        <v>970.268</v>
+        <v>970.943</v>
       </c>
       <c r="AB33" t="n">
-        <v>30.53</v>
+        <v>30.551</v>
       </c>
       <c r="AC33" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD33" t="n">
         <v>465.161</v>
       </c>
       <c r="AE33" t="n">
-        <v>484.473</v>
+        <v>485.149</v>
       </c>
       <c r="AF33" t="n">
-        <v>160.409</v>
+        <v>165.495</v>
       </c>
       <c r="AG33" t="n">
         <v>37</v>
@@ -7860,34 +7860,34 @@
         <v>3.7</v>
       </c>
       <c r="AI33" t="n">
-        <v>611.582</v>
+        <v>617.3440000000001</v>
       </c>
       <c r="AJ33" t="n">
-        <v>110.085</v>
+        <v>111.122</v>
       </c>
       <c r="AK33" t="n">
         <v>18</v>
       </c>
       <c r="AL33" t="n">
-        <v>501.498</v>
+        <v>506.222</v>
       </c>
       <c r="AM33" t="n">
         <v>586.352</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.855</v>
+        <v>0.863</v>
       </c>
       <c r="AO33" t="n">
-        <v>18.072</v>
+        <v>18.134</v>
       </c>
       <c r="AP33" t="n">
-        <v>18.093</v>
+        <v>18.102</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.968</v>
+        <v>1.646</v>
       </c>
       <c r="AR33" t="n">
-        <v>9.722</v>
+        <v>9.691000000000001</v>
       </c>
       <c r="AS33" t="n">
         <v>8.135999999999999</v>
@@ -7908,19 +7908,19 @@
         <v>8.449</v>
       </c>
       <c r="AY33" t="n">
-        <v>6.219</v>
+        <v>6.187</v>
       </c>
       <c r="AZ33" t="n">
-        <v>70.12</v>
+        <v>70.098</v>
       </c>
       <c r="BA33" t="n">
-        <v>23.444</v>
+        <v>23.53</v>
       </c>
       <c r="BB33" t="n">
-        <v>30.53</v>
+        <v>30.551</v>
       </c>
       <c r="BC33" t="n">
-        <v>52.729</v>
+        <v>54.168</v>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
@@ -7963,40 +7963,40 @@
         <v>28.17</v>
       </c>
       <c r="J34" t="n">
-        <v>122.262</v>
+        <v>122.563</v>
       </c>
       <c r="K34" t="n">
         <v>60.846</v>
       </c>
       <c r="L34" t="n">
-        <v>693.3200000000001</v>
+        <v>693.621</v>
       </c>
       <c r="M34" t="n">
         <v>1.479</v>
       </c>
       <c r="N34" t="n">
-        <v>70.998</v>
+        <v>76.678</v>
       </c>
       <c r="O34" t="n">
-        <v>239.295</v>
+        <v>232.914</v>
       </c>
       <c r="P34" t="n">
-        <v>310.293</v>
+        <v>309.592</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.609</v>
+        <v>6.594</v>
       </c>
       <c r="R34" t="n">
         <v>399.166</v>
       </c>
       <c r="S34" t="n">
-        <v>556.896</v>
+        <v>557.081</v>
       </c>
       <c r="T34" t="n">
         <v>230.488</v>
       </c>
       <c r="U34" t="n">
-        <v>787.383</v>
+        <v>787.569</v>
       </c>
       <c r="V34" t="n">
         <v>240.676</v>
@@ -8008,28 +8008,28 @@
         <v>240.676</v>
       </c>
       <c r="Y34" t="n">
-        <v>2430.838</v>
+        <v>2430.624</v>
       </c>
       <c r="Z34" t="n">
         <v>20.634</v>
       </c>
       <c r="AA34" t="n">
-        <v>642.925</v>
+        <v>643.139</v>
       </c>
       <c r="AB34" t="n">
-        <v>21.058</v>
+        <v>21.065</v>
       </c>
       <c r="AC34" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD34" t="n">
         <v>464.029</v>
       </c>
       <c r="AE34" t="n">
-        <v>158.262</v>
+        <v>158.477</v>
       </c>
       <c r="AF34" t="n">
-        <v>191.42</v>
+        <v>180.262</v>
       </c>
       <c r="AG34" t="n">
         <v>37</v>
@@ -8038,34 +8038,34 @@
         <v>3.7</v>
       </c>
       <c r="AI34" t="n">
-        <v>316.382</v>
+        <v>305.439</v>
       </c>
       <c r="AJ34" t="n">
-        <v>55.367</v>
+        <v>53.452</v>
       </c>
       <c r="AK34" t="n">
         <v>17.5</v>
       </c>
       <c r="AL34" t="n">
-        <v>261.015</v>
+        <v>251.987</v>
       </c>
       <c r="AM34" t="n">
         <v>581.027</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.449</v>
+        <v>0.434</v>
       </c>
       <c r="AO34" t="n">
-        <v>19.332</v>
+        <v>19.384</v>
       </c>
       <c r="AP34" t="n">
-        <v>22.708</v>
+        <v>22.718</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.087</v>
+        <v>2.854</v>
       </c>
       <c r="AR34" t="n">
-        <v>10.163</v>
+        <v>10.14</v>
       </c>
       <c r="AS34" t="n">
         <v>6.444</v>
@@ -8074,10 +8074,10 @@
         <v>13.074</v>
       </c>
       <c r="AU34" t="n">
-        <v>13.13</v>
+        <v>13.156</v>
       </c>
       <c r="AV34" t="n">
-        <v>25.789</v>
+        <v>25.795</v>
       </c>
       <c r="AW34" t="n">
         <v>5.099</v>
@@ -8086,19 +8086,19 @@
         <v>7.883</v>
       </c>
       <c r="AY34" t="n">
-        <v>11.404</v>
+        <v>11.394</v>
       </c>
       <c r="AZ34" t="n">
-        <v>79.61799999999999</v>
+        <v>79.611</v>
       </c>
       <c r="BA34" t="n">
-        <v>23.878</v>
+        <v>23.919</v>
       </c>
       <c r="BB34" t="n">
-        <v>21.058</v>
+        <v>21.065</v>
       </c>
       <c r="BC34" t="n">
-        <v>72.78100000000001</v>
+        <v>66.80500000000001</v>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
@@ -8141,40 +8141,40 @@
         <v>26.183</v>
       </c>
       <c r="J35" t="n">
-        <v>122.262</v>
+        <v>122.563</v>
       </c>
       <c r="K35" t="n">
         <v>56.556</v>
       </c>
       <c r="L35" t="n">
-        <v>714.028</v>
+        <v>714.329</v>
       </c>
       <c r="M35" t="n">
         <v>1.717</v>
       </c>
       <c r="N35" t="n">
-        <v>74.58799999999999</v>
+        <v>80.55500000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>256.785</v>
+        <v>249.937</v>
       </c>
       <c r="P35" t="n">
-        <v>331.373</v>
+        <v>330.492</v>
       </c>
       <c r="Q35" t="n">
-        <v>7.594</v>
+        <v>7.573</v>
       </c>
       <c r="R35" t="n">
         <v>386.32</v>
       </c>
       <c r="S35" t="n">
-        <v>627.989</v>
+        <v>628.198</v>
       </c>
       <c r="T35" t="n">
         <v>259.912</v>
       </c>
       <c r="U35" t="n">
-        <v>887.901</v>
+        <v>888.11</v>
       </c>
       <c r="V35" t="n">
         <v>262.262</v>
@@ -8186,28 +8186,28 @@
         <v>262.262</v>
       </c>
       <c r="Y35" t="n">
-        <v>2581.883</v>
+        <v>2581.513</v>
       </c>
       <c r="Z35" t="n">
         <v>20.634</v>
       </c>
       <c r="AA35" t="n">
-        <v>1467.732</v>
+        <v>1468.102</v>
       </c>
       <c r="AB35" t="n">
-        <v>36.429</v>
+        <v>36.439</v>
       </c>
       <c r="AC35" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD35" t="n">
         <v>551.176</v>
       </c>
       <c r="AE35" t="n">
-        <v>895.923</v>
+        <v>896.292</v>
       </c>
       <c r="AF35" t="n">
-        <v>204.684</v>
+        <v>202.848</v>
       </c>
       <c r="AG35" t="n">
         <v>37</v>
@@ -8216,34 +8216,34 @@
         <v>3.7</v>
       </c>
       <c r="AI35" t="n">
-        <v>1067.306</v>
+        <v>1065.84</v>
       </c>
       <c r="AJ35" t="n">
-        <v>186.779</v>
+        <v>186.522</v>
       </c>
       <c r="AK35" t="n">
         <v>17.5</v>
       </c>
       <c r="AL35" t="n">
-        <v>880.528</v>
+        <v>879.318</v>
       </c>
       <c r="AM35" t="n">
         <v>575.703</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.529</v>
+        <v>1.527</v>
       </c>
       <c r="AO35" t="n">
-        <v>12.801</v>
+        <v>12.848</v>
       </c>
       <c r="AP35" t="n">
-        <v>17.722</v>
+        <v>17.73</v>
       </c>
       <c r="AQ35" t="n">
-        <v>2.592</v>
+        <v>2.32</v>
       </c>
       <c r="AR35" t="n">
-        <v>8.225</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="AS35" t="n">
         <v>3.294</v>
@@ -8252,10 +8252,10 @@
         <v>9.589</v>
       </c>
       <c r="AU35" t="n">
-        <v>9.888999999999999</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AV35" t="n">
-        <v>22.038</v>
+        <v>22.043</v>
       </c>
       <c r="AW35" t="n">
         <v>16.561</v>
@@ -8264,19 +8264,19 @@
         <v>6.509</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.263</v>
+        <v>9.247</v>
       </c>
       <c r="AZ35" t="n">
-        <v>64.083</v>
+        <v>64.074</v>
       </c>
       <c r="BA35" t="n">
-        <v>16.394</v>
+        <v>16.424</v>
       </c>
       <c r="BB35" t="n">
-        <v>36.429</v>
+        <v>36.439</v>
       </c>
       <c r="BC35" t="n">
-        <v>11.641</v>
+        <v>11.488</v>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
@@ -8319,40 +8319,40 @@
         <v>25.993</v>
       </c>
       <c r="J36" t="n">
-        <v>122.262</v>
+        <v>122.563</v>
       </c>
       <c r="K36" t="n">
         <v>56.145</v>
       </c>
       <c r="L36" t="n">
-        <v>687.178</v>
+        <v>687.48</v>
       </c>
       <c r="M36" t="n">
         <v>1.7</v>
       </c>
       <c r="N36" t="n">
-        <v>81.282</v>
+        <v>87.533</v>
       </c>
       <c r="O36" t="n">
-        <v>279.055</v>
+        <v>270.836</v>
       </c>
       <c r="P36" t="n">
-        <v>360.337</v>
+        <v>358.369</v>
       </c>
       <c r="Q36" t="n">
-        <v>8.318</v>
+        <v>8.272</v>
       </c>
       <c r="R36" t="n">
         <v>385.223</v>
       </c>
       <c r="S36" t="n">
-        <v>550.623</v>
+        <v>550.806</v>
       </c>
       <c r="T36" t="n">
         <v>227.891</v>
       </c>
       <c r="U36" t="n">
-        <v>778.514</v>
+        <v>778.698</v>
       </c>
       <c r="V36" t="n">
         <v>247.737</v>
@@ -8364,28 +8364,28 @@
         <v>247.737</v>
       </c>
       <c r="Y36" t="n">
-        <v>2458.99</v>
+        <v>2457.507</v>
       </c>
       <c r="Z36" t="n">
         <v>20.634</v>
       </c>
       <c r="AA36" t="n">
-        <v>2842.377</v>
+        <v>2843.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>53.825</v>
+        <v>53.854</v>
       </c>
       <c r="AC36" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD36" t="n">
         <v>511.087</v>
       </c>
       <c r="AE36" t="n">
-        <v>2310.656</v>
+        <v>2312.139</v>
       </c>
       <c r="AF36" t="n">
-        <v>170.01</v>
+        <v>191.145</v>
       </c>
       <c r="AG36" t="n">
         <v>37</v>
@@ -8394,34 +8394,34 @@
         <v>3.7</v>
       </c>
       <c r="AI36" t="n">
-        <v>2447.366</v>
+        <v>2469.984</v>
       </c>
       <c r="AJ36" t="n">
-        <v>428.289</v>
+        <v>432.247</v>
       </c>
       <c r="AK36" t="n">
         <v>17.5</v>
       </c>
       <c r="AL36" t="n">
-        <v>2019.077</v>
+        <v>2037.737</v>
       </c>
       <c r="AM36" t="n">
         <v>570.379</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.54</v>
+        <v>3.573</v>
       </c>
       <c r="AO36" t="n">
-        <v>8.157999999999999</v>
+        <v>8.154</v>
       </c>
       <c r="AP36" t="n">
-        <v>13.013</v>
+        <v>13.019</v>
       </c>
       <c r="AQ36" t="n">
-        <v>2.656</v>
+        <v>2.389</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.824</v>
+        <v>6.786</v>
       </c>
       <c r="AS36" t="n">
         <v>9.281000000000001</v>
@@ -8430,10 +8430,10 @@
         <v>7.295</v>
       </c>
       <c r="AU36" t="n">
-        <v>-0.789</v>
+        <v>-0.854</v>
       </c>
       <c r="AV36" t="n">
-        <v>14.743</v>
+        <v>14.746</v>
       </c>
       <c r="AW36" t="n">
         <v>-3.906</v>
@@ -8442,19 +8442,19 @@
         <v>4.691</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.259</v>
+        <v>3.197</v>
       </c>
       <c r="AZ36" t="n">
-        <v>46.565</v>
+        <v>46.537</v>
       </c>
       <c r="BA36" t="n">
-        <v>16.334</v>
+        <v>16.395</v>
       </c>
       <c r="BB36" t="n">
-        <v>53.825</v>
+        <v>53.854</v>
       </c>
       <c r="BC36" t="n">
-        <v>21.591</v>
+        <v>21.52</v>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
@@ -8497,40 +8497,40 @@
         <v>23.294</v>
       </c>
       <c r="J37" t="n">
-        <v>122.262</v>
+        <v>122.563</v>
       </c>
       <c r="K37" t="n">
         <v>50.316</v>
       </c>
       <c r="L37" t="n">
-        <v>617.355</v>
+        <v>617.657</v>
       </c>
       <c r="M37" t="n">
         <v>1.697</v>
       </c>
       <c r="N37" t="n">
-        <v>71.42100000000001</v>
+        <v>76.89100000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>245.626</v>
+        <v>238.32</v>
       </c>
       <c r="P37" t="n">
-        <v>317.047</v>
+        <v>315.211</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.166</v>
+        <v>8.119</v>
       </c>
       <c r="R37" t="n">
         <v>395.876</v>
       </c>
       <c r="S37" t="n">
-        <v>587.796</v>
+        <v>587.992</v>
       </c>
       <c r="T37" t="n">
         <v>243.277</v>
       </c>
       <c r="U37" t="n">
-        <v>831.072</v>
+        <v>831.268</v>
       </c>
       <c r="V37" t="n">
         <v>258.025</v>
@@ -8542,28 +8542,28 @@
         <v>258.025</v>
       </c>
       <c r="Y37" t="n">
-        <v>2419.376</v>
+        <v>2418.037</v>
       </c>
       <c r="Z37" t="n">
         <v>20.634</v>
       </c>
       <c r="AA37" t="n">
-        <v>1067.022</v>
+        <v>1068.361</v>
       </c>
       <c r="AB37" t="n">
-        <v>30.787</v>
+        <v>30.826</v>
       </c>
       <c r="AC37" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD37" t="n">
         <v>526.458</v>
       </c>
       <c r="AE37" t="n">
-        <v>519.9299999999999</v>
+        <v>521.269</v>
       </c>
       <c r="AF37" t="n">
-        <v>166.64</v>
+        <v>171.155</v>
       </c>
       <c r="AG37" t="n">
         <v>37</v>
@@ -8572,34 +8572,34 @@
         <v>3.7</v>
       </c>
       <c r="AI37" t="n">
-        <v>653.27</v>
+        <v>659.124</v>
       </c>
       <c r="AJ37" t="n">
-        <v>114.322</v>
+        <v>115.347</v>
       </c>
       <c r="AK37" t="n">
         <v>17.5</v>
       </c>
       <c r="AL37" t="n">
-        <v>538.948</v>
+        <v>543.777</v>
       </c>
       <c r="AM37" t="n">
         <v>565.0549999999999</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.954</v>
+        <v>0.962</v>
       </c>
       <c r="AO37" t="n">
-        <v>7.364</v>
+        <v>7.36</v>
       </c>
       <c r="AP37" t="n">
-        <v>17.813</v>
+        <v>17.822</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.616</v>
+        <v>2.346</v>
       </c>
       <c r="AR37" t="n">
-        <v>9.148</v>
+        <v>9.095000000000001</v>
       </c>
       <c r="AS37" t="n">
         <v>9.281000000000001</v>
@@ -8608,10 +8608,10 @@
         <v>11.422</v>
       </c>
       <c r="AU37" t="n">
-        <v>16.441</v>
+        <v>16.468</v>
       </c>
       <c r="AV37" t="n">
-        <v>23.979</v>
+        <v>23.985</v>
       </c>
       <c r="AW37" t="n">
         <v>-3.906</v>
@@ -8620,19 +8620,19 @@
         <v>7.445</v>
       </c>
       <c r="AY37" t="n">
-        <v>8.566000000000001</v>
+        <v>8.539</v>
       </c>
       <c r="AZ37" t="n">
-        <v>69.80800000000001</v>
+        <v>69.76900000000001</v>
       </c>
       <c r="BA37" t="n">
-        <v>9.972</v>
+        <v>10.033</v>
       </c>
       <c r="BB37" t="n">
-        <v>30.787</v>
+        <v>30.826</v>
       </c>
       <c r="BC37" t="n">
-        <v>11.518</v>
+        <v>11.467</v>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
@@ -8675,40 +8675,40 @@
         <v>33.757</v>
       </c>
       <c r="J38" t="n">
-        <v>84.941</v>
+        <v>85.116</v>
       </c>
       <c r="K38" t="n">
         <v>52.184</v>
       </c>
       <c r="L38" t="n">
-        <v>633.454</v>
+        <v>633.629</v>
       </c>
       <c r="M38" t="n">
         <v>1.825</v>
       </c>
       <c r="N38" t="n">
-        <v>52.061</v>
+        <v>59.002</v>
       </c>
       <c r="O38" t="n">
-        <v>323.621</v>
+        <v>316.006</v>
       </c>
       <c r="P38" t="n">
-        <v>375.681</v>
+        <v>375.008</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.460000000000001</v>
+        <v>9.443</v>
       </c>
       <c r="R38" t="n">
         <v>365.684</v>
       </c>
       <c r="S38" t="n">
-        <v>514.009</v>
+        <v>514.418</v>
       </c>
       <c r="T38" t="n">
         <v>252.755</v>
       </c>
       <c r="U38" t="n">
-        <v>766.764</v>
+        <v>767.173</v>
       </c>
       <c r="V38" t="n">
         <v>272.972</v>
@@ -8720,28 +8720,28 @@
         <v>272.972</v>
       </c>
       <c r="Y38" t="n">
-        <v>2414.554</v>
+        <v>2414.465</v>
       </c>
       <c r="Z38" t="n">
         <v>20.634</v>
       </c>
       <c r="AA38" t="n">
-        <v>2361.08</v>
+        <v>2361.169</v>
       </c>
       <c r="AB38" t="n">
-        <v>49.655</v>
+        <v>49.657</v>
       </c>
       <c r="AC38" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD38" t="n">
         <v>451.579</v>
       </c>
       <c r="AE38" t="n">
-        <v>1888.867</v>
+        <v>1888.956</v>
       </c>
       <c r="AF38" t="n">
-        <v>158.724</v>
+        <v>174.347</v>
       </c>
       <c r="AG38" t="n">
         <v>37</v>
@@ -8750,34 +8750,34 @@
         <v>3.7</v>
       </c>
       <c r="AI38" t="n">
-        <v>2014.29</v>
+        <v>2030.003</v>
       </c>
       <c r="AJ38" t="n">
-        <v>362.572</v>
+        <v>365.401</v>
       </c>
       <c r="AK38" t="n">
         <v>18</v>
       </c>
       <c r="AL38" t="n">
-        <v>1651.718</v>
+        <v>1664.603</v>
       </c>
       <c r="AM38" t="n">
         <v>591.676</v>
       </c>
       <c r="AN38" t="n">
-        <v>2.792</v>
+        <v>2.813</v>
       </c>
       <c r="AO38" t="n">
-        <v>15.383</v>
+        <v>15.415</v>
       </c>
       <c r="AP38" t="n">
-        <v>13.322</v>
+        <v>13.326</v>
       </c>
       <c r="AQ38" t="n">
-        <v>9.528</v>
+        <v>9.332000000000001</v>
       </c>
       <c r="AR38" t="n">
-        <v>7.901</v>
+        <v>7.887</v>
       </c>
       <c r="AS38" t="n">
         <v>9.815</v>
@@ -8786,10 +8786,10 @@
         <v>7.691</v>
       </c>
       <c r="AU38" t="n">
-        <v>31.071</v>
+        <v>31.141</v>
       </c>
       <c r="AV38" t="n">
-        <v>16.125</v>
+        <v>16.134</v>
       </c>
       <c r="AW38" t="n">
         <v>4.587</v>
@@ -8798,19 +8798,19 @@
         <v>5.741</v>
       </c>
       <c r="AY38" t="n">
-        <v>16.589</v>
+        <v>16.585</v>
       </c>
       <c r="AZ38" t="n">
-        <v>50.779</v>
+        <v>50.777</v>
       </c>
       <c r="BA38" t="n">
-        <v>15.118</v>
+        <v>15.123</v>
       </c>
       <c r="BB38" t="n">
-        <v>49.655</v>
+        <v>49.657</v>
       </c>
       <c r="BC38" t="n">
-        <v>26.316</v>
+        <v>27.302</v>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
@@ -8853,28 +8853,28 @@
         <v>30.659</v>
       </c>
       <c r="J39" t="n">
-        <v>84.941</v>
+        <v>85.116</v>
       </c>
       <c r="K39" t="n">
         <v>47.395</v>
       </c>
       <c r="L39" t="n">
-        <v>575.3440000000001</v>
+        <v>575.52</v>
       </c>
       <c r="M39" t="n">
         <v>1.821</v>
       </c>
       <c r="N39" t="n">
-        <v>45.778</v>
+        <v>51.881</v>
       </c>
       <c r="O39" t="n">
-        <v>285.881</v>
+        <v>279.154</v>
       </c>
       <c r="P39" t="n">
-        <v>331.658</v>
+        <v>331.035</v>
       </c>
       <c r="Q39" t="n">
-        <v>9.195</v>
+        <v>9.178000000000001</v>
       </c>
       <c r="R39" t="n">
         <v>375.796</v>
@@ -8898,28 +8898,28 @@
         <v>284.308</v>
       </c>
       <c r="Y39" t="n">
-        <v>2369.592</v>
+        <v>2369.145</v>
       </c>
       <c r="Z39" t="n">
         <v>20.634</v>
       </c>
       <c r="AA39" t="n">
-        <v>774.849</v>
+        <v>775.296</v>
       </c>
       <c r="AB39" t="n">
-        <v>24.805</v>
+        <v>24.819</v>
       </c>
       <c r="AC39" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD39" t="n">
         <v>465.161</v>
       </c>
       <c r="AE39" t="n">
-        <v>289.054</v>
+        <v>289.502</v>
       </c>
       <c r="AF39" t="n">
-        <v>156.742</v>
+        <v>157.663</v>
       </c>
       <c r="AG39" t="n">
         <v>37</v>
@@ -8928,34 +8928,34 @@
         <v>3.7</v>
       </c>
       <c r="AI39" t="n">
-        <v>412.497</v>
+        <v>413.865</v>
       </c>
       <c r="AJ39" t="n">
-        <v>74.249</v>
+        <v>74.496</v>
       </c>
       <c r="AK39" t="n">
         <v>18</v>
       </c>
       <c r="AL39" t="n">
-        <v>338.247</v>
+        <v>339.369</v>
       </c>
       <c r="AM39" t="n">
         <v>586.352</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.577</v>
+        <v>0.579</v>
       </c>
       <c r="AO39" t="n">
-        <v>18.141</v>
+        <v>18.177</v>
       </c>
       <c r="AP39" t="n">
-        <v>18.418</v>
+        <v>18.424</v>
       </c>
       <c r="AQ39" t="n">
-        <v>9.458</v>
+        <v>9.253</v>
       </c>
       <c r="AR39" t="n">
-        <v>10.617</v>
+        <v>10.597</v>
       </c>
       <c r="AS39" t="n">
         <v>12.178</v>
@@ -8976,19 +8976,19 @@
         <v>9.101000000000001</v>
       </c>
       <c r="AY39" t="n">
-        <v>12.945</v>
+        <v>12.924</v>
       </c>
       <c r="AZ39" t="n">
-        <v>75.85599999999999</v>
+        <v>75.842</v>
       </c>
       <c r="BA39" t="n">
-        <v>-1.419</v>
+        <v>-1.362</v>
       </c>
       <c r="BB39" t="n">
-        <v>24.805</v>
+        <v>24.819</v>
       </c>
       <c r="BC39" t="n">
-        <v>3.012</v>
+        <v>3.354</v>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
@@ -9031,40 +9031,40 @@
         <v>38.617</v>
       </c>
       <c r="J40" t="n">
-        <v>106.441</v>
+        <v>106.616</v>
       </c>
       <c r="K40" t="n">
         <v>58.879</v>
       </c>
       <c r="L40" t="n">
-        <v>684.808</v>
+        <v>684.9829999999999</v>
       </c>
       <c r="M40" t="n">
         <v>1.587</v>
       </c>
       <c r="N40" t="n">
-        <v>46.015</v>
+        <v>52.15</v>
       </c>
       <c r="O40" t="n">
-        <v>283.994</v>
+        <v>277.311</v>
       </c>
       <c r="P40" t="n">
-        <v>330.008</v>
+        <v>329.461</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.264</v>
+        <v>7.252</v>
       </c>
       <c r="R40" t="n">
         <v>433.04</v>
       </c>
       <c r="S40" t="n">
-        <v>620.085</v>
+        <v>620.205</v>
       </c>
       <c r="T40" t="n">
         <v>264.934</v>
       </c>
       <c r="U40" t="n">
-        <v>885.019</v>
+        <v>885.139</v>
       </c>
       <c r="V40" t="n">
         <v>260.337</v>
@@ -9076,28 +9076,28 @@
         <v>260.337</v>
       </c>
       <c r="Y40" t="n">
-        <v>2593.212</v>
+        <v>2592.96</v>
       </c>
       <c r="Z40" t="n">
         <v>20.634</v>
       </c>
       <c r="AA40" t="n">
-        <v>422.585</v>
+        <v>422.837</v>
       </c>
       <c r="AB40" t="n">
-        <v>14.109</v>
+        <v>14.117</v>
       </c>
       <c r="AC40" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD40" t="n">
         <v>464.029</v>
       </c>
       <c r="AE40" t="n">
-        <v>-62.078</v>
+        <v>-61.826</v>
       </c>
       <c r="AF40" t="n">
-        <v>183.496</v>
+        <v>168.672</v>
       </c>
       <c r="AG40" t="n">
         <v>37</v>
@@ -9106,34 +9106,34 @@
         <v>3.7</v>
       </c>
       <c r="AI40" t="n">
-        <v>88.119</v>
+        <v>73.547</v>
       </c>
       <c r="AJ40" t="n">
-        <v>15.421</v>
+        <v>12.871</v>
       </c>
       <c r="AK40" t="n">
         <v>17.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>72.69799999999999</v>
+        <v>60.676</v>
       </c>
       <c r="AM40" t="n">
         <v>581.027</v>
       </c>
       <c r="AN40" t="n">
-        <v>0.125</v>
+        <v>0.104</v>
       </c>
       <c r="AO40" t="n">
-        <v>17.867</v>
+        <v>17.897</v>
       </c>
       <c r="AP40" t="n">
-        <v>22.864</v>
+        <v>22.87</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.637</v>
+        <v>9.456</v>
       </c>
       <c r="AR40" t="n">
-        <v>11.018</v>
+        <v>11</v>
       </c>
       <c r="AS40" t="n">
         <v>15.477</v>
@@ -9142,10 +9142,10 @@
         <v>14.458</v>
       </c>
       <c r="AU40" t="n">
-        <v>27.158</v>
+        <v>27.175</v>
       </c>
       <c r="AV40" t="n">
-        <v>29.548</v>
+        <v>29.552</v>
       </c>
       <c r="AW40" t="n">
         <v>13.684</v>
@@ -9154,19 +9154,19 @@
         <v>8.692</v>
       </c>
       <c r="AY40" t="n">
-        <v>18.846</v>
+        <v>18.834</v>
       </c>
       <c r="AZ40" t="n">
-        <v>86.58</v>
+        <v>86.572</v>
       </c>
       <c r="BA40" t="n">
-        <v>-18.577</v>
+        <v>-18.528</v>
       </c>
       <c r="BB40" t="n">
-        <v>14.109</v>
+        <v>14.117</v>
       </c>
       <c r="BC40" t="n">
-        <v>-51.877</v>
+        <v>-59.835</v>
       </c>
       <c r="BD40" t="inlineStr">
         <is>
@@ -9209,40 +9209,40 @@
         <v>36.075</v>
       </c>
       <c r="J41" t="n">
-        <v>106.441</v>
+        <v>106.616</v>
       </c>
       <c r="K41" t="n">
         <v>55.004</v>
       </c>
       <c r="L41" t="n">
-        <v>709.669</v>
+        <v>709.8440000000001</v>
       </c>
       <c r="M41" t="n">
         <v>1.842</v>
       </c>
       <c r="N41" t="n">
-        <v>48.585</v>
+        <v>55.063</v>
       </c>
       <c r="O41" t="n">
-        <v>304.751</v>
+        <v>297.58</v>
       </c>
       <c r="P41" t="n">
-        <v>353.336</v>
+        <v>352.643</v>
       </c>
       <c r="Q41" t="n">
-        <v>8.324999999999999</v>
+        <v>8.308999999999999</v>
       </c>
       <c r="R41" t="n">
         <v>419.104</v>
       </c>
       <c r="S41" t="n">
-        <v>699.245</v>
+        <v>699.38</v>
       </c>
       <c r="T41" t="n">
         <v>298.755</v>
       </c>
       <c r="U41" t="n">
-        <v>998</v>
+        <v>998.135</v>
       </c>
       <c r="V41" t="n">
         <v>283.687</v>
@@ -9254,28 +9254,28 @@
         <v>283.687</v>
       </c>
       <c r="Y41" t="n">
-        <v>2763.795</v>
+        <v>2763.412</v>
       </c>
       <c r="Z41" t="n">
         <v>20.634</v>
       </c>
       <c r="AA41" t="n">
-        <v>1060.563</v>
+        <v>1060.945</v>
       </c>
       <c r="AB41" t="n">
-        <v>27.882</v>
+        <v>27.892</v>
       </c>
       <c r="AC41" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD41" t="n">
         <v>551.176</v>
       </c>
       <c r="AE41" t="n">
-        <v>488.753</v>
+        <v>489.136</v>
       </c>
       <c r="AF41" t="n">
-        <v>196.115</v>
+        <v>186.355</v>
       </c>
       <c r="AG41" t="n">
         <v>37</v>
@@ -9284,34 +9284,34 @@
         <v>3.7</v>
       </c>
       <c r="AI41" t="n">
-        <v>651.568</v>
+        <v>642.191</v>
       </c>
       <c r="AJ41" t="n">
-        <v>114.024</v>
+        <v>112.383</v>
       </c>
       <c r="AK41" t="n">
         <v>17.5</v>
       </c>
       <c r="AL41" t="n">
-        <v>537.544</v>
+        <v>529.808</v>
       </c>
       <c r="AM41" t="n">
         <v>575.703</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="AO41" t="n">
-        <v>12.112</v>
+        <v>12.14</v>
       </c>
       <c r="AP41" t="n">
-        <v>18.657</v>
+        <v>18.662</v>
       </c>
       <c r="AQ41" t="n">
-        <v>9.391999999999999</v>
+        <v>9.177</v>
       </c>
       <c r="AR41" t="n">
-        <v>9.289</v>
+        <v>9.271000000000001</v>
       </c>
       <c r="AS41" t="n">
         <v>12.06</v>
@@ -9320,10 +9320,10 @@
         <v>11.018</v>
       </c>
       <c r="AU41" t="n">
-        <v>23.515</v>
+        <v>23.532</v>
       </c>
       <c r="AV41" t="n">
-        <v>26.237</v>
+        <v>26.241</v>
       </c>
       <c r="AW41" t="n">
         <v>26.083</v>
@@ -9332,19 +9332,19 @@
         <v>7.458</v>
       </c>
       <c r="AY41" t="n">
-        <v>16.961</v>
+        <v>16.945</v>
       </c>
       <c r="AZ41" t="n">
-        <v>72.66</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="BA41" t="n">
-        <v>-15.895</v>
+        <v>-15.865</v>
       </c>
       <c r="BB41" t="n">
-        <v>27.882</v>
+        <v>27.892</v>
       </c>
       <c r="BC41" t="n">
-        <v>-31.845</v>
+        <v>-32.826</v>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
@@ -9387,40 +9387,40 @@
         <v>35.391</v>
       </c>
       <c r="J42" t="n">
-        <v>106.441</v>
+        <v>106.616</v>
       </c>
       <c r="K42" t="n">
         <v>53.961</v>
       </c>
       <c r="L42" t="n">
-        <v>673.168</v>
+        <v>673.3440000000001</v>
       </c>
       <c r="M42" t="n">
         <v>1.825</v>
       </c>
       <c r="N42" t="n">
-        <v>56.717</v>
+        <v>64.164</v>
       </c>
       <c r="O42" t="n">
-        <v>354.455</v>
+        <v>345.495</v>
       </c>
       <c r="P42" t="n">
-        <v>411.173</v>
+        <v>409.659</v>
       </c>
       <c r="Q42" t="n">
-        <v>9.875</v>
+        <v>9.839</v>
       </c>
       <c r="R42" t="n">
         <v>417.914</v>
       </c>
       <c r="S42" t="n">
-        <v>613.101</v>
+        <v>613.2190000000001</v>
       </c>
       <c r="T42" t="n">
         <v>261.949</v>
       </c>
       <c r="U42" t="n">
-        <v>875.05</v>
+        <v>875.168</v>
       </c>
       <c r="V42" t="n">
         <v>267.975</v>
@@ -9432,28 +9432,28 @@
         <v>267.975</v>
       </c>
       <c r="Y42" t="n">
-        <v>2645.28</v>
+        <v>2644.06</v>
       </c>
       <c r="Z42" t="n">
         <v>20.634</v>
       </c>
       <c r="AA42" t="n">
-        <v>2311.892</v>
+        <v>2313.112</v>
       </c>
       <c r="AB42" t="n">
-        <v>46.832</v>
+        <v>46.857</v>
       </c>
       <c r="AC42" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD42" t="n">
         <v>511.087</v>
       </c>
       <c r="AE42" t="n">
-        <v>1780.171</v>
+        <v>1781.391</v>
       </c>
       <c r="AF42" t="n">
-        <v>156.508</v>
+        <v>176.293</v>
       </c>
       <c r="AG42" t="n">
         <v>37</v>
@@ -9462,34 +9462,34 @@
         <v>3.7</v>
       </c>
       <c r="AI42" t="n">
-        <v>1903.379</v>
+        <v>1924.384</v>
       </c>
       <c r="AJ42" t="n">
-        <v>333.091</v>
+        <v>336.767</v>
       </c>
       <c r="AK42" t="n">
         <v>17.5</v>
       </c>
       <c r="AL42" t="n">
-        <v>1570.288</v>
+        <v>1587.617</v>
       </c>
       <c r="AM42" t="n">
         <v>570.379</v>
       </c>
       <c r="AN42" t="n">
-        <v>2.753</v>
+        <v>2.783</v>
       </c>
       <c r="AO42" t="n">
-        <v>6.27</v>
+        <v>6.268</v>
       </c>
       <c r="AP42" t="n">
-        <v>13.636</v>
+        <v>13.64</v>
       </c>
       <c r="AQ42" t="n">
-        <v>9.446999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="AR42" t="n">
-        <v>8.329000000000001</v>
+        <v>8.298999999999999</v>
       </c>
       <c r="AS42" t="n">
         <v>14.283</v>
@@ -9498,10 +9498,10 @@
         <v>8.465999999999999</v>
       </c>
       <c r="AU42" t="n">
-        <v>14.123</v>
+        <v>14.077</v>
       </c>
       <c r="AV42" t="n">
-        <v>17.726</v>
+        <v>17.728</v>
       </c>
       <c r="AW42" t="n">
         <v>-1.831</v>
@@ -9510,19 +9510,19 @@
         <v>5.428</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.555999999999999</v>
+        <v>9.509</v>
       </c>
       <c r="AZ42" t="n">
-        <v>53.586</v>
+        <v>53.561</v>
       </c>
       <c r="BA42" t="n">
-        <v>-2.083</v>
+        <v>-2.035</v>
       </c>
       <c r="BB42" t="n">
-        <v>46.832</v>
+        <v>46.857</v>
       </c>
       <c r="BC42" t="n">
-        <v>-1.38</v>
+        <v>-1.064</v>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
@@ -9565,40 +9565,40 @@
         <v>32.119</v>
       </c>
       <c r="J43" t="n">
-        <v>106.441</v>
+        <v>106.616</v>
       </c>
       <c r="K43" t="n">
         <v>48.972</v>
       </c>
       <c r="L43" t="n">
-        <v>616.6799999999999</v>
+        <v>616.855</v>
       </c>
       <c r="M43" t="n">
         <v>1.821</v>
       </c>
       <c r="N43" t="n">
-        <v>50.033</v>
+        <v>56.598</v>
       </c>
       <c r="O43" t="n">
-        <v>312.92</v>
+        <v>304.983</v>
       </c>
       <c r="P43" t="n">
-        <v>362.953</v>
+        <v>361.581</v>
       </c>
       <c r="Q43" t="n">
-        <v>9.605</v>
+        <v>9.569000000000001</v>
       </c>
       <c r="R43" t="n">
         <v>429.471</v>
       </c>
       <c r="S43" t="n">
-        <v>654.492</v>
+        <v>654.6180000000001</v>
       </c>
       <c r="T43" t="n">
         <v>279.634</v>
       </c>
       <c r="U43" t="n">
-        <v>934.125</v>
+        <v>934.251</v>
       </c>
       <c r="V43" t="n">
         <v>279.104</v>
@@ -9610,28 +9610,28 @@
         <v>279.104</v>
       </c>
       <c r="Y43" t="n">
-        <v>2622.332</v>
+        <v>2621.262</v>
       </c>
       <c r="Z43" t="n">
         <v>20.634</v>
       </c>
       <c r="AA43" t="n">
-        <v>611.211</v>
+        <v>612.282</v>
       </c>
       <c r="AB43" t="n">
-        <v>19.024</v>
+        <v>19.057</v>
       </c>
       <c r="AC43" t="n">
-        <v>21.47</v>
+        <v>22.054</v>
       </c>
       <c r="AD43" t="n">
         <v>526.458</v>
       </c>
       <c r="AE43" t="n">
-        <v>64.119</v>
+        <v>65.18899999999999</v>
       </c>
       <c r="AF43" t="n">
-        <v>154.898</v>
+        <v>159.777</v>
       </c>
       <c r="AG43" t="n">
         <v>37</v>
@@ -9640,34 +9640,34 @@
         <v>3.7</v>
       </c>
       <c r="AI43" t="n">
-        <v>185.717</v>
+        <v>191.666</v>
       </c>
       <c r="AJ43" t="n">
-        <v>32.5</v>
+        <v>33.542</v>
       </c>
       <c r="AK43" t="n">
         <v>17.5</v>
       </c>
       <c r="AL43" t="n">
-        <v>153.216</v>
+        <v>158.124</v>
       </c>
       <c r="AM43" t="n">
         <v>565.0549999999999</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.271</v>
+        <v>0.28</v>
       </c>
       <c r="AO43" t="n">
-        <v>7.184</v>
+        <v>7.182</v>
       </c>
       <c r="AP43" t="n">
-        <v>19.194</v>
+        <v>19.199</v>
       </c>
       <c r="AQ43" t="n">
-        <v>9.436</v>
+        <v>9.227</v>
       </c>
       <c r="AR43" t="n">
-        <v>11.297</v>
+        <v>11.254</v>
       </c>
       <c r="AS43" t="n">
         <v>14.283</v>
@@ -9676,10 +9676,10 @@
         <v>13.367</v>
       </c>
       <c r="AU43" t="n">
-        <v>16.404</v>
+        <v>16.42</v>
       </c>
       <c r="AV43" t="n">
-        <v>29.074</v>
+        <v>29.078</v>
       </c>
       <c r="AW43" t="n">
         <v>-1.831</v>
@@ -9688,19 +9688,19 @@
         <v>8.686999999999999</v>
       </c>
       <c r="AY43" t="n">
-        <v>10.666</v>
+        <v>10.642</v>
       </c>
       <c r="AZ43" t="n">
-        <v>81.619</v>
+        <v>81.58499999999999</v>
       </c>
       <c r="BA43" t="n">
-        <v>-21.119</v>
+        <v>-21.026</v>
       </c>
       <c r="BB43" t="n">
-        <v>19.024</v>
+        <v>19.057</v>
       </c>
       <c r="BC43" t="n">
-        <v>-52.996</v>
+        <v>-51.65</v>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
@@ -9743,40 +9743,40 @@
         <v>24.377</v>
       </c>
       <c r="J44" t="n">
-        <v>115.762</v>
+        <v>116.063</v>
       </c>
       <c r="K44" t="n">
         <v>53.387</v>
       </c>
       <c r="L44" t="n">
-        <v>646.691</v>
+        <v>646.992</v>
       </c>
       <c r="M44" t="n">
         <v>1.7</v>
       </c>
       <c r="N44" t="n">
-        <v>79.119</v>
+        <v>85.44799999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>272.685</v>
+        <v>265.413</v>
       </c>
       <c r="P44" t="n">
-        <v>351.804</v>
+        <v>350.862</v>
       </c>
       <c r="Q44" t="n">
-        <v>8.659000000000001</v>
+        <v>8.635999999999999</v>
       </c>
       <c r="R44" t="n">
         <v>352.506</v>
       </c>
       <c r="S44" t="n">
-        <v>562.169</v>
+        <v>562.872</v>
       </c>
       <c r="T44" t="n">
         <v>222.535</v>
       </c>
       <c r="U44" t="n">
-        <v>784.704</v>
+        <v>785.408</v>
       </c>
       <c r="V44" t="n">
         <v>257.807</v>
@@ -9788,28 +9788,28 @@
         <v>257.807</v>
       </c>
       <c r="Y44" t="n">
-        <v>2393.511</v>
+        <v>2393.574</v>
       </c>
       <c r="Z44" t="n">
         <v>20.634</v>
       </c>
       <c r="AA44" t="n">
-        <v>2505.123</v>
+        <v>2505.06</v>
       </c>
       <c r="AB44" t="n">
-        <v>51.356</v>
+        <v>51.354</v>
       </c>
       <c r="AC44" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD44" t="n">
         <v>451.579</v>
       </c>
       <c r="AE44" t="n">
-        <v>2032.91</v>
+        <v>2032.847</v>
       </c>
       <c r="AF44" t="n">
-        <v>163.695</v>
+        <v>184.355</v>
       </c>
       <c r="AG44" t="n">
         <v>37</v>
@@ -9818,34 +9818,34 @@
         <v>3.7</v>
       </c>
       <c r="AI44" t="n">
-        <v>2163.305</v>
+        <v>2183.901</v>
       </c>
       <c r="AJ44" t="n">
-        <v>389.395</v>
+        <v>393.102</v>
       </c>
       <c r="AK44" t="n">
         <v>18</v>
       </c>
       <c r="AL44" t="n">
-        <v>1773.91</v>
+        <v>1790.799</v>
       </c>
       <c r="AM44" t="n">
         <v>591.676</v>
       </c>
       <c r="AN44" t="n">
-        <v>2.998</v>
+        <v>3.027</v>
       </c>
       <c r="AO44" t="n">
-        <v>17.794</v>
+        <v>17.849</v>
       </c>
       <c r="AP44" t="n">
-        <v>13.257</v>
+        <v>13.263</v>
       </c>
       <c r="AQ44" t="n">
-        <v>2.567</v>
+        <v>2.292</v>
       </c>
       <c r="AR44" t="n">
-        <v>7.212</v>
+        <v>7.193</v>
       </c>
       <c r="AS44" t="n">
         <v>5.858</v>
@@ -9854,10 +9854,10 @@
         <v>7.226</v>
       </c>
       <c r="AU44" t="n">
-        <v>34.137</v>
+        <v>34.258</v>
       </c>
       <c r="AV44" t="n">
-        <v>16.087</v>
+        <v>16.101</v>
       </c>
       <c r="AW44" t="n">
         <v>-1.224</v>
@@ -9866,19 +9866,19 @@
         <v>5.285</v>
       </c>
       <c r="AY44" t="n">
-        <v>15.573</v>
+        <v>15.576</v>
       </c>
       <c r="AZ44" t="n">
-        <v>49.067</v>
+        <v>49.069</v>
       </c>
       <c r="BA44" t="n">
-        <v>22.142</v>
+        <v>22.138</v>
       </c>
       <c r="BB44" t="n">
-        <v>51.356</v>
+        <v>51.354</v>
       </c>
       <c r="BC44" t="n">
-        <v>35.661</v>
+        <v>36.953</v>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
@@ -9921,28 +9921,28 @@
         <v>21.814</v>
       </c>
       <c r="J45" t="n">
-        <v>115.762</v>
+        <v>116.063</v>
       </c>
       <c r="K45" t="n">
         <v>47.772</v>
       </c>
       <c r="L45" t="n">
-        <v>583.583</v>
+        <v>583.885</v>
       </c>
       <c r="M45" t="n">
         <v>1.697</v>
       </c>
       <c r="N45" t="n">
-        <v>68.545</v>
+        <v>74.02800000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>240.885</v>
+        <v>234.461</v>
       </c>
       <c r="P45" t="n">
-        <v>309.43</v>
+        <v>308.49</v>
       </c>
       <c r="Q45" t="n">
-        <v>8.510999999999999</v>
+        <v>8.484999999999999</v>
       </c>
       <c r="R45" t="n">
         <v>362.254</v>
@@ -9966,28 +9966,28 @@
         <v>268.513</v>
       </c>
       <c r="Y45" t="n">
-        <v>2237.51</v>
+        <v>2236.872</v>
       </c>
       <c r="Z45" t="n">
         <v>20.634</v>
       </c>
       <c r="AA45" t="n">
-        <v>1011.06</v>
+        <v>1011.699</v>
       </c>
       <c r="AB45" t="n">
-        <v>31.322</v>
+        <v>31.342</v>
       </c>
       <c r="AC45" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD45" t="n">
         <v>465.161</v>
       </c>
       <c r="AE45" t="n">
-        <v>525.266</v>
+        <v>525.904</v>
       </c>
       <c r="AF45" t="n">
-        <v>161.08</v>
+        <v>166.972</v>
       </c>
       <c r="AG45" t="n">
         <v>37</v>
@@ -9996,34 +9996,34 @@
         <v>3.7</v>
       </c>
       <c r="AI45" t="n">
-        <v>653.045</v>
+        <v>659.576</v>
       </c>
       <c r="AJ45" t="n">
-        <v>117.548</v>
+        <v>118.724</v>
       </c>
       <c r="AK45" t="n">
         <v>18</v>
       </c>
       <c r="AL45" t="n">
-        <v>535.497</v>
+        <v>540.852</v>
       </c>
       <c r="AM45" t="n">
         <v>586.352</v>
       </c>
       <c r="AN45" t="n">
-        <v>0.913</v>
+        <v>0.922</v>
       </c>
       <c r="AO45" t="n">
-        <v>19.832</v>
+        <v>19.894</v>
       </c>
       <c r="AP45" t="n">
-        <v>18.079</v>
+        <v>18.088</v>
       </c>
       <c r="AQ45" t="n">
-        <v>2.122</v>
+        <v>1.812</v>
       </c>
       <c r="AR45" t="n">
-        <v>9.586</v>
+        <v>9.557</v>
       </c>
       <c r="AS45" t="n">
         <v>8.135999999999999</v>
@@ -10044,19 +10044,19 @@
         <v>8.318</v>
       </c>
       <c r="AY45" t="n">
-        <v>6.65</v>
+        <v>6.619</v>
       </c>
       <c r="AZ45" t="n">
-        <v>69.31699999999999</v>
+        <v>69.297</v>
       </c>
       <c r="BA45" t="n">
-        <v>28.634</v>
+        <v>28.715</v>
       </c>
       <c r="BB45" t="n">
-        <v>31.322</v>
+        <v>31.342</v>
       </c>
       <c r="BC45" t="n">
-        <v>63.084</v>
+        <v>64.715</v>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
@@ -10099,40 +10099,40 @@
         <v>28.773</v>
       </c>
       <c r="J46" t="n">
-        <v>122.262</v>
+        <v>122.563</v>
       </c>
       <c r="K46" t="n">
         <v>62.15</v>
       </c>
       <c r="L46" t="n">
-        <v>717.742</v>
+        <v>718.044</v>
       </c>
       <c r="M46" t="n">
         <v>1.479</v>
       </c>
       <c r="N46" t="n">
-        <v>72.51900000000001</v>
+        <v>78.321</v>
       </c>
       <c r="O46" t="n">
-        <v>239.295</v>
+        <v>232.914</v>
       </c>
       <c r="P46" t="n">
-        <v>311.814</v>
+        <v>311.234</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.502</v>
+        <v>6.49</v>
       </c>
       <c r="R46" t="n">
         <v>399.166</v>
       </c>
       <c r="S46" t="n">
-        <v>556.896</v>
+        <v>557.081</v>
       </c>
       <c r="T46" t="n">
         <v>230.488</v>
       </c>
       <c r="U46" t="n">
-        <v>787.383</v>
+        <v>787.569</v>
       </c>
       <c r="V46" t="n">
         <v>240.676</v>
@@ -10144,28 +10144,28 @@
         <v>240.676</v>
       </c>
       <c r="Y46" t="n">
-        <v>2456.782</v>
+        <v>2456.689</v>
       </c>
       <c r="Z46" t="n">
         <v>20.634</v>
       </c>
       <c r="AA46" t="n">
-        <v>683.79</v>
+        <v>683.8819999999999</v>
       </c>
       <c r="AB46" t="n">
-        <v>21.917</v>
+        <v>21.92</v>
       </c>
       <c r="AC46" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD46" t="n">
         <v>464.029</v>
       </c>
       <c r="AE46" t="n">
-        <v>199.127</v>
+        <v>199.22</v>
       </c>
       <c r="AF46" t="n">
-        <v>193.686</v>
+        <v>183.199</v>
       </c>
       <c r="AG46" t="n">
         <v>37</v>
@@ -10174,34 +10174,34 @@
         <v>3.7</v>
       </c>
       <c r="AI46" t="n">
-        <v>359.513</v>
+        <v>349.119</v>
       </c>
       <c r="AJ46" t="n">
-        <v>62.915</v>
+        <v>61.096</v>
       </c>
       <c r="AK46" t="n">
         <v>17.5</v>
       </c>
       <c r="AL46" t="n">
-        <v>296.598</v>
+        <v>288.023</v>
       </c>
       <c r="AM46" t="n">
         <v>581.027</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.51</v>
+        <v>0.496</v>
       </c>
       <c r="AO46" t="n">
-        <v>23.536</v>
+        <v>23.588</v>
       </c>
       <c r="AP46" t="n">
-        <v>23.005</v>
+        <v>23.015</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.593</v>
+        <v>3.4</v>
       </c>
       <c r="AR46" t="n">
-        <v>9.994</v>
+        <v>9.976000000000001</v>
       </c>
       <c r="AS46" t="n">
         <v>6.444</v>
@@ -10210,10 +10210,10 @@
         <v>12.794</v>
       </c>
       <c r="AU46" t="n">
-        <v>13.13</v>
+        <v>13.156</v>
       </c>
       <c r="AV46" t="n">
-        <v>25.237</v>
+        <v>25.243</v>
       </c>
       <c r="AW46" t="n">
         <v>5.099</v>
@@ -10222,19 +10222,19 @@
         <v>7.714</v>
       </c>
       <c r="AY46" t="n">
-        <v>12.593</v>
+        <v>12.589</v>
       </c>
       <c r="AZ46" t="n">
-        <v>78.745</v>
+        <v>78.742</v>
       </c>
       <c r="BA46" t="n">
-        <v>31.751</v>
+        <v>31.769</v>
       </c>
       <c r="BB46" t="n">
-        <v>21.917</v>
+        <v>21.92</v>
       </c>
       <c r="BC46" t="n">
-        <v>96.33499999999999</v>
+        <v>90.65900000000001</v>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
@@ -10277,40 +10277,40 @@
         <v>26.897</v>
       </c>
       <c r="J47" t="n">
-        <v>122.262</v>
+        <v>122.563</v>
       </c>
       <c r="K47" t="n">
         <v>58.097</v>
       </c>
       <c r="L47" t="n">
-        <v>744.923</v>
+        <v>745.225</v>
       </c>
       <c r="M47" t="n">
         <v>1.717</v>
       </c>
       <c r="N47" t="n">
-        <v>76.62</v>
+        <v>82.749</v>
       </c>
       <c r="O47" t="n">
-        <v>256.785</v>
+        <v>249.937</v>
       </c>
       <c r="P47" t="n">
-        <v>333.405</v>
+        <v>332.687</v>
       </c>
       <c r="Q47" t="n">
-        <v>7.437</v>
+        <v>7.421</v>
       </c>
       <c r="R47" t="n">
         <v>386.32</v>
       </c>
       <c r="S47" t="n">
-        <v>627.989</v>
+        <v>628.198</v>
       </c>
       <c r="T47" t="n">
         <v>259.912</v>
       </c>
       <c r="U47" t="n">
-        <v>887.901</v>
+        <v>888.11</v>
       </c>
       <c r="V47" t="n">
         <v>262.262</v>
@@ -10322,28 +10322,28 @@
         <v>262.262</v>
       </c>
       <c r="Y47" t="n">
-        <v>2614.81</v>
+        <v>2614.603</v>
       </c>
       <c r="Z47" t="n">
         <v>20.634</v>
       </c>
       <c r="AA47" t="n">
-        <v>1595.729</v>
+        <v>1595.936</v>
       </c>
       <c r="AB47" t="n">
-        <v>38.085</v>
+        <v>38.09</v>
       </c>
       <c r="AC47" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD47" t="n">
         <v>551.176</v>
       </c>
       <c r="AE47" t="n">
-        <v>1023.92</v>
+        <v>1024.127</v>
       </c>
       <c r="AF47" t="n">
-        <v>207.772</v>
+        <v>208.203</v>
       </c>
       <c r="AG47" t="n">
         <v>37</v>
@@ -10352,34 +10352,34 @@
         <v>3.7</v>
       </c>
       <c r="AI47" t="n">
-        <v>1198.392</v>
+        <v>1199.029</v>
       </c>
       <c r="AJ47" t="n">
-        <v>209.719</v>
+        <v>209.83</v>
       </c>
       <c r="AK47" t="n">
         <v>17.5</v>
       </c>
       <c r="AL47" t="n">
-        <v>988.673</v>
+        <v>989.199</v>
       </c>
       <c r="AM47" t="n">
         <v>575.703</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.717</v>
+        <v>1.718</v>
       </c>
       <c r="AO47" t="n">
-        <v>17.681</v>
+        <v>17.729</v>
       </c>
       <c r="AP47" t="n">
-        <v>17.779</v>
+        <v>17.786</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.221</v>
+        <v>2.999</v>
       </c>
       <c r="AR47" t="n">
-        <v>7.957</v>
+        <v>7.94</v>
       </c>
       <c r="AS47" t="n">
         <v>3.294</v>
@@ -10388,10 +10388,10 @@
         <v>9.220000000000001</v>
       </c>
       <c r="AU47" t="n">
-        <v>9.888999999999999</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="AV47" t="n">
-        <v>21.191</v>
+        <v>21.196</v>
       </c>
       <c r="AW47" t="n">
         <v>16.561</v>
@@ -10400,19 +10400,19 @@
         <v>6.259</v>
       </c>
       <c r="AY47" t="n">
-        <v>10.656</v>
+        <v>10.648</v>
       </c>
       <c r="AZ47" t="n">
-        <v>62.407</v>
+        <v>62.402</v>
       </c>
       <c r="BA47" t="n">
-        <v>26.545</v>
+        <v>26.561</v>
       </c>
       <c r="BB47" t="n">
-        <v>38.085</v>
+        <v>38.09</v>
       </c>
       <c r="BC47" t="n">
-        <v>25.353</v>
+        <v>25.419</v>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
@@ -10455,40 +10455,40 @@
         <v>26.862</v>
       </c>
       <c r="J48" t="n">
-        <v>122.262</v>
+        <v>122.563</v>
       </c>
       <c r="K48" t="n">
         <v>58.023</v>
       </c>
       <c r="L48" t="n">
-        <v>725.61</v>
+        <v>725.9109999999999</v>
       </c>
       <c r="M48" t="n">
         <v>1.7</v>
       </c>
       <c r="N48" t="n">
-        <v>83.348</v>
+        <v>89.77500000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>279.684</v>
+        <v>271.497</v>
       </c>
       <c r="P48" t="n">
-        <v>363.032</v>
+        <v>361.272</v>
       </c>
       <c r="Q48" t="n">
-        <v>8.109</v>
+        <v>8.069000000000001</v>
       </c>
       <c r="R48" t="n">
         <v>385.223</v>
       </c>
       <c r="S48" t="n">
-        <v>550.623</v>
+        <v>550.806</v>
       </c>
       <c r="T48" t="n">
         <v>227.891</v>
       </c>
       <c r="U48" t="n">
-        <v>778.514</v>
+        <v>778.698</v>
       </c>
       <c r="V48" t="n">
         <v>247.737</v>
@@ -10500,28 +10500,28 @@
         <v>247.737</v>
       </c>
       <c r="Y48" t="n">
-        <v>2500.116</v>
+        <v>2498.841</v>
       </c>
       <c r="Z48" t="n">
         <v>20.634</v>
       </c>
       <c r="AA48" t="n">
-        <v>3080.465</v>
+        <v>3081.741</v>
       </c>
       <c r="AB48" t="n">
-        <v>55.405</v>
+        <v>55.428</v>
       </c>
       <c r="AC48" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD48" t="n">
         <v>511.087</v>
       </c>
       <c r="AE48" t="n">
-        <v>2548.744</v>
+        <v>2550.02</v>
       </c>
       <c r="AF48" t="n">
-        <v>173.537</v>
+        <v>196.955</v>
       </c>
       <c r="AG48" t="n">
         <v>37</v>
@@ -10530,34 +10530,34 @@
         <v>3.7</v>
       </c>
       <c r="AI48" t="n">
-        <v>2688.982</v>
+        <v>2713.675</v>
       </c>
       <c r="AJ48" t="n">
-        <v>470.572</v>
+        <v>474.893</v>
       </c>
       <c r="AK48" t="n">
         <v>17.5</v>
       </c>
       <c r="AL48" t="n">
-        <v>2218.41</v>
+        <v>2238.782</v>
       </c>
       <c r="AM48" t="n">
         <v>570.379</v>
       </c>
       <c r="AN48" t="n">
-        <v>3.889</v>
+        <v>3.925</v>
       </c>
       <c r="AO48" t="n">
-        <v>12.204</v>
+        <v>12.198</v>
       </c>
       <c r="AP48" t="n">
-        <v>13.051</v>
+        <v>13.056</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.192</v>
+        <v>2.967</v>
       </c>
       <c r="AR48" t="n">
-        <v>6.529</v>
+        <v>6.498</v>
       </c>
       <c r="AS48" t="n">
         <v>9.281000000000001</v>
@@ -10566,10 +10566,10 @@
         <v>6.929</v>
       </c>
       <c r="AU48" t="n">
-        <v>-0.789</v>
+        <v>-0.854</v>
       </c>
       <c r="AV48" t="n">
-        <v>14.002</v>
+        <v>14.005</v>
       </c>
       <c r="AW48" t="n">
         <v>-3.906</v>
@@ -10578,19 +10578,19 @@
         <v>4.456</v>
       </c>
       <c r="AY48" t="n">
-        <v>4.454</v>
+        <v>4.398</v>
       </c>
       <c r="AZ48" t="n">
-        <v>44.967</v>
+        <v>44.944</v>
       </c>
       <c r="BA48" t="n">
-        <v>22.967</v>
+        <v>23.021</v>
       </c>
       <c r="BB48" t="n">
-        <v>55.405</v>
+        <v>55.428</v>
       </c>
       <c r="BC48" t="n">
-        <v>29.727</v>
+        <v>29.684</v>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
@@ -10633,40 +10633,40 @@
         <v>24.012</v>
       </c>
       <c r="J49" t="n">
-        <v>122.262</v>
+        <v>122.563</v>
       </c>
       <c r="K49" t="n">
         <v>51.867</v>
       </c>
       <c r="L49" t="n">
-        <v>644.232</v>
+        <v>644.533</v>
       </c>
       <c r="M49" t="n">
         <v>1.697</v>
       </c>
       <c r="N49" t="n">
-        <v>73.233</v>
+        <v>78.851</v>
       </c>
       <c r="O49" t="n">
-        <v>245.997</v>
+        <v>238.709</v>
       </c>
       <c r="P49" t="n">
-        <v>319.229</v>
+        <v>317.56</v>
       </c>
       <c r="Q49" t="n">
-        <v>7.977</v>
+        <v>7.935</v>
       </c>
       <c r="R49" t="n">
         <v>395.876</v>
       </c>
       <c r="S49" t="n">
-        <v>587.796</v>
+        <v>587.992</v>
       </c>
       <c r="T49" t="n">
         <v>243.277</v>
       </c>
       <c r="U49" t="n">
-        <v>831.072</v>
+        <v>831.268</v>
       </c>
       <c r="V49" t="n">
         <v>258.025</v>
@@ -10678,28 +10678,28 @@
         <v>258.025</v>
       </c>
       <c r="Y49" t="n">
-        <v>2448.435</v>
+        <v>2447.263</v>
       </c>
       <c r="Z49" t="n">
         <v>20.634</v>
       </c>
       <c r="AA49" t="n">
-        <v>1273.152</v>
+        <v>1274.323</v>
       </c>
       <c r="AB49" t="n">
-        <v>34.401</v>
+        <v>34.432</v>
       </c>
       <c r="AC49" t="n">
-        <v>165.873</v>
+        <v>166.878</v>
       </c>
       <c r="AD49" t="n">
         <v>526.458</v>
       </c>
       <c r="AE49" t="n">
-        <v>726.0599999999999</v>
+        <v>727.231</v>
       </c>
       <c r="AF49" t="n">
-        <v>169.348</v>
+        <v>175.914</v>
       </c>
       <c r="AG49" t="n">
         <v>37</v>
@@ -10708,34 +10708,34 @@
         <v>3.7</v>
       </c>
       <c r="AI49" t="n">
-        <v>862.1079999999999</v>
+        <v>869.845</v>
       </c>
       <c r="AJ49" t="n">
-        <v>150.869</v>
+        <v>152.223</v>
       </c>
       <c r="AK49" t="n">
         <v>17.5</v>
       </c>
       <c r="AL49" t="n">
-        <v>711.239</v>
+        <v>717.622</v>
       </c>
       <c r="AM49" t="n">
         <v>565.0549999999999</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.259</v>
+        <v>1.27</v>
       </c>
       <c r="AO49" t="n">
-        <v>10.392</v>
+        <v>10.387</v>
       </c>
       <c r="AP49" t="n">
-        <v>17.407</v>
+        <v>17.415</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.167</v>
+        <v>2.94</v>
       </c>
       <c r="AR49" t="n">
-        <v>8.625999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="AS49" t="n">
         <v>9.281000000000001</v>
@@ -10744,10 +10744,10 @@
         <v>10.697</v>
       </c>
       <c r="AU49" t="n">
-        <v>16.441</v>
+        <v>16.468</v>
       </c>
       <c r="AV49" t="n">
-        <v>22.456</v>
+        <v>22.461</v>
       </c>
       <c r="AW49" t="n">
         <v>-3.906</v>
@@ -10756,19 +10756,19 @@
         <v>6.972</v>
       </c>
       <c r="AY49" t="n">
-        <v>9.427</v>
+        <v>9.406000000000001</v>
       </c>
       <c r="AZ49" t="n">
-        <v>66.157</v>
+        <v>66.125</v>
       </c>
       <c r="BA49" t="n">
-        <v>25.922</v>
+        <v>25.959</v>
       </c>
       <c r="BB49" t="n">
-        <v>34.401</v>
+        <v>34.432</v>
       </c>
       <c r="BC49" t="n">
-        <v>37.824</v>
+        <v>37.684</v>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
@@ -11025,19 +11025,19 @@
         <v>105.415</v>
       </c>
       <c r="F2" t="n">
-        <v>2432.196</v>
+        <v>2432.824</v>
       </c>
       <c r="G2" t="n">
-        <v>1305.817</v>
+        <v>1303.73</v>
       </c>
       <c r="H2" t="n">
         <v>1477.12</v>
       </c>
       <c r="I2" t="n">
-        <v>3039.691</v>
+        <v>3040.423</v>
       </c>
       <c r="J2" t="n">
-        <v>2118.111</v>
+        <v>2118.843</v>
       </c>
       <c r="K2" t="n">
         <v>921.58</v>
@@ -11046,73 +11046,73 @@
         <v>995.8</v>
       </c>
       <c r="M2" t="n">
-        <v>9250.624</v>
+        <v>9249.897000000001</v>
       </c>
       <c r="N2" t="n">
         <v>80.268</v>
       </c>
       <c r="O2" t="n">
-        <v>5097.787</v>
+        <v>5098.514</v>
       </c>
       <c r="P2" t="n">
         <v>1813.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>3203.779</v>
+        <v>3204.506</v>
       </c>
       <c r="R2" t="n">
-        <v>661.298</v>
+        <v>687.044</v>
       </c>
       <c r="S2" t="n">
-        <v>3121.512</v>
+        <v>3143.22</v>
       </c>
       <c r="T2" t="n">
-        <v>35.728</v>
+        <v>35.734</v>
       </c>
       <c r="U2" t="n">
-        <v>5.24</v>
+        <v>5.276</v>
       </c>
       <c r="V2" t="n">
-        <v>17.046</v>
+        <v>17.051</v>
       </c>
       <c r="W2" t="n">
-        <v>9.151999999999999</v>
+        <v>9.137</v>
       </c>
       <c r="X2" t="n">
         <v>10.353</v>
       </c>
       <c r="Y2" t="n">
-        <v>21.304</v>
+        <v>21.309</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.845</v>
+        <v>14.85</v>
       </c>
       <c r="AA2" t="n">
         <v>6.979</v>
       </c>
       <c r="AB2" t="n">
-        <v>64.834</v>
+        <v>64.82899999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>12.712</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.596</v>
+        <v>16.626</v>
       </c>
       <c r="AE2" t="n">
-        <v>5.563</v>
+        <v>5.395</v>
       </c>
       <c r="AF2" t="n">
         <v>10.48</v>
       </c>
       <c r="AG2" t="n">
-        <v>27.933</v>
+        <v>27.964</v>
       </c>
       <c r="AH2" t="n">
         <v>-6.848</v>
       </c>
       <c r="AI2" t="n">
-        <v>14.135</v>
+        <v>14.126</v>
       </c>
     </row>
     <row r="3">
@@ -11136,19 +11136,19 @@
         <v>115.472</v>
       </c>
       <c r="F3" t="n">
-        <v>2758.354</v>
+        <v>2759.609</v>
       </c>
       <c r="G3" t="n">
-        <v>1383.592</v>
+        <v>1377.876</v>
       </c>
       <c r="H3" t="n">
         <v>1625.29</v>
       </c>
       <c r="I3" t="n">
-        <v>3458.781</v>
+        <v>3459.624</v>
       </c>
       <c r="J3" t="n">
-        <v>2435.828</v>
+        <v>2436.67</v>
       </c>
       <c r="K3" t="n">
         <v>1022.954</v>
@@ -11157,52 +11157,52 @@
         <v>1044.54</v>
       </c>
       <c r="M3" t="n">
-        <v>10270.557</v>
+        <v>10266.938</v>
       </c>
       <c r="N3" t="n">
         <v>82.536</v>
       </c>
       <c r="O3" t="n">
-        <v>5640.586</v>
+        <v>5644.204</v>
       </c>
       <c r="P3" t="n">
         <v>2052.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>3505.3</v>
+        <v>3508.919</v>
       </c>
       <c r="R3" t="n">
-        <v>732.754</v>
+        <v>745.41</v>
       </c>
       <c r="S3" t="n">
-        <v>3386.505</v>
+        <v>3399.931</v>
       </c>
       <c r="T3" t="n">
-        <v>35.635</v>
+        <v>35.658</v>
       </c>
       <c r="U3" t="n">
-        <v>5.91</v>
+        <v>5.933</v>
       </c>
       <c r="V3" t="n">
-        <v>17.426</v>
+        <v>17.434</v>
       </c>
       <c r="W3" t="n">
-        <v>8.741</v>
+        <v>8.705</v>
       </c>
       <c r="X3" t="n">
         <v>10.268</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.851</v>
+        <v>21.857</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.389</v>
+        <v>15.394</v>
       </c>
       <c r="AA3" t="n">
         <v>6.599</v>
       </c>
       <c r="AB3" t="n">
-        <v>64.886</v>
+        <v>64.863</v>
       </c>
       <c r="AC3" t="n">
         <v>12.969</v>
@@ -11250,7 +11250,7 @@
         <v>2374.408</v>
       </c>
       <c r="G4" t="n">
-        <v>1305.817</v>
+        <v>1303.73</v>
       </c>
       <c r="H4" t="n">
         <v>1477.12</v>
@@ -11268,37 +11268,37 @@
         <v>995.8</v>
       </c>
       <c r="M4" t="n">
-        <v>9125.416999999999</v>
+        <v>9123.329</v>
       </c>
       <c r="N4" t="n">
         <v>80.268</v>
       </c>
       <c r="O4" t="n">
-        <v>5222.995</v>
+        <v>5225.082</v>
       </c>
       <c r="P4" t="n">
         <v>1813.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>3328.987</v>
+        <v>3331.074</v>
       </c>
       <c r="R4" t="n">
-        <v>661.298</v>
+        <v>687.044</v>
       </c>
       <c r="S4" t="n">
-        <v>3224.182</v>
+        <v>3247.005</v>
       </c>
       <c r="T4" t="n">
-        <v>36.606</v>
+        <v>36.621</v>
       </c>
       <c r="U4" t="n">
-        <v>5.412</v>
+        <v>5.45</v>
       </c>
       <c r="V4" t="n">
         <v>16.641</v>
       </c>
       <c r="W4" t="n">
-        <v>9.151999999999999</v>
+        <v>9.137</v>
       </c>
       <c r="X4" t="n">
         <v>10.353</v>
@@ -11313,7 +11313,7 @@
         <v>6.979</v>
       </c>
       <c r="AB4" t="n">
-        <v>63.957</v>
+        <v>63.942</v>
       </c>
       <c r="AC4" t="n">
         <v>12.712</v>
@@ -11322,7 +11322,7 @@
         <v>13.826</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.563</v>
+        <v>5.395</v>
       </c>
       <c r="AF4" t="n">
         <v>10.48</v>
@@ -11334,7 +11334,7 @@
         <v>-6.848</v>
       </c>
       <c r="AI4" t="n">
-        <v>12.59</v>
+        <v>12.564</v>
       </c>
     </row>
     <row r="5">
@@ -11361,7 +11361,7 @@
         <v>2642.777</v>
       </c>
       <c r="G5" t="n">
-        <v>1383.592</v>
+        <v>1377.876</v>
       </c>
       <c r="H5" t="n">
         <v>1625.29</v>
@@ -11379,37 +11379,37 @@
         <v>1044.54</v>
       </c>
       <c r="M5" t="n">
-        <v>10077.448</v>
+        <v>10071.732</v>
       </c>
       <c r="N5" t="n">
         <v>82.536</v>
       </c>
       <c r="O5" t="n">
-        <v>5833.695</v>
+        <v>5839.411</v>
       </c>
       <c r="P5" t="n">
         <v>2052.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>3698.409</v>
+        <v>3704.125</v>
       </c>
       <c r="R5" t="n">
-        <v>732.754</v>
+        <v>745.41</v>
       </c>
       <c r="S5" t="n">
-        <v>3545.819</v>
+        <v>3560.977</v>
       </c>
       <c r="T5" t="n">
-        <v>36.855</v>
+        <v>36.892</v>
       </c>
       <c r="U5" t="n">
-        <v>6.188</v>
+        <v>6.214</v>
       </c>
       <c r="V5" t="n">
         <v>16.696</v>
       </c>
       <c r="W5" t="n">
-        <v>8.741</v>
+        <v>8.705</v>
       </c>
       <c r="X5" t="n">
         <v>10.268</v>
@@ -11424,7 +11424,7 @@
         <v>6.599</v>
       </c>
       <c r="AB5" t="n">
-        <v>63.666</v>
+        <v>63.63</v>
       </c>
       <c r="AC5" t="n">
         <v>12.969</v>
@@ -11469,19 +11469,19 @@
         <v>104.393</v>
       </c>
       <c r="F6" t="n">
-        <v>2413.076</v>
+        <v>2413.704</v>
       </c>
       <c r="G6" t="n">
-        <v>1304.967</v>
+        <v>1302.768</v>
       </c>
       <c r="H6" t="n">
         <v>1477.12</v>
       </c>
       <c r="I6" t="n">
-        <v>3039.691</v>
+        <v>3040.423</v>
       </c>
       <c r="J6" t="n">
-        <v>2118.111</v>
+        <v>2118.843</v>
       </c>
       <c r="K6" t="n">
         <v>921.58</v>
@@ -11490,73 +11490,73 @@
         <v>995.8</v>
       </c>
       <c r="M6" t="n">
-        <v>9230.654</v>
+        <v>9229.815000000001</v>
       </c>
       <c r="N6" t="n">
         <v>80.268</v>
       </c>
       <c r="O6" t="n">
-        <v>5014.42</v>
+        <v>5015.259</v>
       </c>
       <c r="P6" t="n">
         <v>1813.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>3120.413</v>
+        <v>3121.252</v>
       </c>
       <c r="R6" t="n">
-        <v>659.936</v>
+        <v>684.803</v>
       </c>
       <c r="S6" t="n">
-        <v>3052.034</v>
+        <v>3073.113</v>
       </c>
       <c r="T6" t="n">
-        <v>35.401</v>
+        <v>35.406</v>
       </c>
       <c r="U6" t="n">
-        <v>5.123</v>
+        <v>5.158</v>
       </c>
       <c r="V6" t="n">
-        <v>17.036</v>
+        <v>17.04</v>
       </c>
       <c r="W6" t="n">
-        <v>9.212999999999999</v>
+        <v>9.196999999999999</v>
       </c>
       <c r="X6" t="n">
         <v>10.428</v>
       </c>
       <c r="Y6" t="n">
-        <v>21.459</v>
+        <v>21.465</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.953</v>
+        <v>14.959</v>
       </c>
       <c r="AA6" t="n">
         <v>7.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>65.166</v>
+        <v>65.16</v>
       </c>
       <c r="AC6" t="n">
         <v>12.805</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.68</v>
+        <v>15.71</v>
       </c>
       <c r="AE6" t="n">
-        <v>5.495</v>
+        <v>5.317</v>
       </c>
       <c r="AF6" t="n">
         <v>10.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>27.933</v>
+        <v>27.964</v>
       </c>
       <c r="AH6" t="n">
         <v>-6.848</v>
       </c>
       <c r="AI6" t="n">
-        <v>13.888</v>
+        <v>13.878</v>
       </c>
     </row>
     <row r="7">
@@ -11580,19 +11580,19 @@
         <v>107.833</v>
       </c>
       <c r="F7" t="n">
-        <v>2617.741</v>
+        <v>2618.997</v>
       </c>
       <c r="G7" t="n">
-        <v>1375.962</v>
+        <v>1369.257</v>
       </c>
       <c r="H7" t="n">
         <v>1625.29</v>
       </c>
       <c r="I7" t="n">
-        <v>3458.781</v>
+        <v>3459.624</v>
       </c>
       <c r="J7" t="n">
-        <v>2435.828</v>
+        <v>2436.67</v>
       </c>
       <c r="K7" t="n">
         <v>1022.954</v>
@@ -11601,52 +11601,52 @@
         <v>1044.54</v>
       </c>
       <c r="M7" t="n">
-        <v>10122.314</v>
+        <v>10117.707</v>
       </c>
       <c r="N7" t="n">
         <v>82.536</v>
       </c>
       <c r="O7" t="n">
-        <v>4908.555</v>
+        <v>4913.163</v>
       </c>
       <c r="P7" t="n">
         <v>2052.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2773.27</v>
+        <v>2777.878</v>
       </c>
       <c r="R7" t="n">
-        <v>719.8819999999999</v>
+        <v>723.692</v>
       </c>
       <c r="S7" t="n">
-        <v>2771.96</v>
+        <v>2778.905</v>
       </c>
       <c r="T7" t="n">
-        <v>32.837</v>
+        <v>32.868</v>
       </c>
       <c r="U7" t="n">
-        <v>4.837</v>
+        <v>4.849</v>
       </c>
       <c r="V7" t="n">
-        <v>17.512</v>
+        <v>17.52</v>
       </c>
       <c r="W7" t="n">
-        <v>9.205</v>
+        <v>9.16</v>
       </c>
       <c r="X7" t="n">
         <v>10.873</v>
       </c>
       <c r="Y7" t="n">
-        <v>23.138</v>
+        <v>23.144</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.295</v>
+        <v>16.301</v>
       </c>
       <c r="AA7" t="n">
         <v>6.988</v>
       </c>
       <c r="AB7" t="n">
-        <v>67.715</v>
+        <v>67.685</v>
       </c>
       <c r="AC7" t="n">
         <v>13.732</v>
@@ -11691,19 +11691,19 @@
         <v>106.514</v>
       </c>
       <c r="F8" t="n">
-        <v>2452.869</v>
+        <v>2453.497</v>
       </c>
       <c r="G8" t="n">
-        <v>1306.819</v>
+        <v>1304.864</v>
       </c>
       <c r="H8" t="n">
         <v>1477.12</v>
       </c>
       <c r="I8" t="n">
-        <v>3039.691</v>
+        <v>3040.423</v>
       </c>
       <c r="J8" t="n">
-        <v>2118.111</v>
+        <v>2118.843</v>
       </c>
       <c r="K8" t="n">
         <v>921.58</v>
@@ -11712,73 +11712,73 @@
         <v>995.8</v>
       </c>
       <c r="M8" t="n">
-        <v>9272.299000000001</v>
+        <v>9271.704</v>
       </c>
       <c r="N8" t="n">
         <v>80.268</v>
       </c>
       <c r="O8" t="n">
-        <v>5199.905</v>
+        <v>5200.501</v>
       </c>
       <c r="P8" t="n">
         <v>1813.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>3305.898</v>
+        <v>3306.493</v>
       </c>
       <c r="R8" t="n">
-        <v>662.775</v>
+        <v>689.326</v>
       </c>
       <c r="S8" t="n">
-        <v>3206.459</v>
+        <v>3228.72</v>
       </c>
       <c r="T8" t="n">
-        <v>36.131</v>
+        <v>36.135</v>
       </c>
       <c r="U8" t="n">
-        <v>5.382</v>
+        <v>5.42</v>
       </c>
       <c r="V8" t="n">
-        <v>17.043</v>
+        <v>17.048</v>
       </c>
       <c r="W8" t="n">
-        <v>9.08</v>
+        <v>9.067</v>
       </c>
       <c r="X8" t="n">
         <v>10.264</v>
       </c>
       <c r="Y8" t="n">
-        <v>21.121</v>
+        <v>21.126</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.717</v>
+        <v>14.722</v>
       </c>
       <c r="AA8" t="n">
         <v>6.919</v>
       </c>
       <c r="AB8" t="n">
-        <v>64.42700000000001</v>
+        <v>64.423</v>
       </c>
       <c r="AC8" t="n">
         <v>12.602</v>
       </c>
       <c r="AD8" t="n">
-        <v>17.587</v>
+        <v>17.617</v>
       </c>
       <c r="AE8" t="n">
-        <v>5.644</v>
+        <v>5.486</v>
       </c>
       <c r="AF8" t="n">
         <v>10.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>27.933</v>
+        <v>27.964</v>
       </c>
       <c r="AH8" t="n">
         <v>-6.848</v>
       </c>
       <c r="AI8" t="n">
-        <v>14.402</v>
+        <v>14.395</v>
       </c>
     </row>
     <row r="9">
@@ -11802,19 +11802,19 @@
         <v>122.212</v>
       </c>
       <c r="F9" t="n">
-        <v>2883.631</v>
+        <v>2884.887</v>
       </c>
       <c r="G9" t="n">
-        <v>1390.425</v>
+        <v>1385.595</v>
       </c>
       <c r="H9" t="n">
         <v>1625.29</v>
       </c>
       <c r="I9" t="n">
-        <v>3458.781</v>
+        <v>3459.624</v>
       </c>
       <c r="J9" t="n">
-        <v>2435.828</v>
+        <v>2436.67</v>
       </c>
       <c r="K9" t="n">
         <v>1022.954</v>
@@ -11823,52 +11823,52 @@
         <v>1044.54</v>
       </c>
       <c r="M9" t="n">
-        <v>10402.667</v>
+        <v>10399.935</v>
       </c>
       <c r="N9" t="n">
         <v>82.536</v>
       </c>
       <c r="O9" t="n">
-        <v>6250.613</v>
+        <v>6253.345</v>
       </c>
       <c r="P9" t="n">
         <v>2052.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>4115.327</v>
+        <v>4118.059</v>
       </c>
       <c r="R9" t="n">
-        <v>744.3440000000001</v>
+        <v>764.271</v>
       </c>
       <c r="S9" t="n">
-        <v>3899.339</v>
+        <v>3918.032</v>
       </c>
       <c r="T9" t="n">
-        <v>37.721</v>
+        <v>37.737</v>
       </c>
       <c r="U9" t="n">
-        <v>6.805</v>
+        <v>6.837</v>
       </c>
       <c r="V9" t="n">
-        <v>17.402</v>
+        <v>17.41</v>
       </c>
       <c r="W9" t="n">
-        <v>8.391</v>
+        <v>8.362</v>
       </c>
       <c r="X9" t="n">
         <v>9.808</v>
       </c>
       <c r="Y9" t="n">
-        <v>20.873</v>
+        <v>20.878</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.7</v>
+        <v>14.705</v>
       </c>
       <c r="AA9" t="n">
         <v>6.304</v>
       </c>
       <c r="AB9" t="n">
-        <v>62.777</v>
+        <v>62.761</v>
       </c>
       <c r="AC9" t="n">
         <v>12.388</v>
@@ -11913,19 +11913,19 @@
         <v>105.415</v>
       </c>
       <c r="F10" t="n">
-        <v>2442.624</v>
+        <v>2442.974</v>
       </c>
       <c r="G10" t="n">
-        <v>1332.057</v>
+        <v>1330.857</v>
       </c>
       <c r="H10" t="n">
         <v>1490.48</v>
       </c>
       <c r="I10" t="n">
-        <v>3073.249</v>
+        <v>3073.658</v>
       </c>
       <c r="J10" t="n">
-        <v>2120.429</v>
+        <v>2120.838</v>
       </c>
       <c r="K10" t="n">
         <v>952.8200000000001</v>
@@ -11934,73 +11934,73 @@
         <v>1011.28</v>
       </c>
       <c r="M10" t="n">
-        <v>9349.690000000001</v>
+        <v>9349.249</v>
       </c>
       <c r="N10" t="n">
         <v>80.268</v>
       </c>
       <c r="O10" t="n">
-        <v>4998.721</v>
+        <v>4999.162</v>
       </c>
       <c r="P10" t="n">
         <v>1813.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>3104.714</v>
+        <v>3105.155</v>
       </c>
       <c r="R10" t="n">
-        <v>654.693</v>
+        <v>672.027</v>
       </c>
       <c r="S10" t="n">
-        <v>3034.861</v>
+        <v>3049.437</v>
       </c>
       <c r="T10" t="n">
-        <v>35.034</v>
+        <v>35.037</v>
       </c>
       <c r="U10" t="n">
-        <v>5.094</v>
+        <v>5.119</v>
       </c>
       <c r="V10" t="n">
-        <v>17.119</v>
+        <v>17.122</v>
       </c>
       <c r="W10" t="n">
-        <v>9.336</v>
+        <v>9.327</v>
       </c>
       <c r="X10" t="n">
         <v>10.446</v>
       </c>
       <c r="Y10" t="n">
-        <v>21.539</v>
+        <v>21.542</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.861</v>
+        <v>14.864</v>
       </c>
       <c r="AA10" t="n">
         <v>7.088</v>
       </c>
       <c r="AB10" t="n">
-        <v>65.52800000000001</v>
+        <v>65.52500000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>12.712</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.096</v>
+        <v>17.113</v>
       </c>
       <c r="AE10" t="n">
-        <v>7.685</v>
+        <v>7.587</v>
       </c>
       <c r="AF10" t="n">
         <v>11.479</v>
       </c>
       <c r="AG10" t="n">
-        <v>29.345</v>
+        <v>29.363</v>
       </c>
       <c r="AH10" t="n">
         <v>-5.399</v>
       </c>
       <c r="AI10" t="n">
-        <v>15.357</v>
+        <v>15.352</v>
       </c>
     </row>
     <row r="11">
@@ -12024,19 +12024,19 @@
         <v>115.472</v>
       </c>
       <c r="F11" t="n">
-        <v>2830.212</v>
+        <v>2830.913</v>
       </c>
       <c r="G11" t="n">
-        <v>1464.031</v>
+        <v>1460.774</v>
       </c>
       <c r="H11" t="n">
         <v>1699.528</v>
       </c>
       <c r="I11" t="n">
-        <v>3692.194</v>
+        <v>3692.693</v>
       </c>
       <c r="J11" t="n">
-        <v>2586.923</v>
+        <v>2587.422</v>
       </c>
       <c r="K11" t="n">
         <v>1105.271</v>
@@ -12045,52 +12045,52 @@
         <v>1091.102</v>
       </c>
       <c r="M11" t="n">
-        <v>10777.068</v>
+        <v>10775.011</v>
       </c>
       <c r="N11" t="n">
         <v>82.536</v>
       </c>
       <c r="O11" t="n">
-        <v>5134.074</v>
+        <v>5136.131</v>
       </c>
       <c r="P11" t="n">
         <v>2052.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2998.789</v>
+        <v>3000.846</v>
       </c>
       <c r="R11" t="n">
-        <v>702.181</v>
+        <v>710.644</v>
       </c>
       <c r="S11" t="n">
-        <v>2943.41</v>
+        <v>2952.089</v>
       </c>
       <c r="T11" t="n">
-        <v>32.435</v>
+        <v>32.448</v>
       </c>
       <c r="U11" t="n">
-        <v>5.136</v>
+        <v>5.152</v>
       </c>
       <c r="V11" t="n">
-        <v>17.88</v>
+        <v>17.885</v>
       </c>
       <c r="W11" t="n">
-        <v>9.249000000000001</v>
+        <v>9.228999999999999</v>
       </c>
       <c r="X11" t="n">
         <v>10.737</v>
       </c>
       <c r="Y11" t="n">
-        <v>23.326</v>
+        <v>23.329</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.343</v>
+        <v>16.346</v>
       </c>
       <c r="AA11" t="n">
         <v>6.893</v>
       </c>
       <c r="AB11" t="n">
-        <v>68.086</v>
+        <v>68.07299999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>12.969</v>
@@ -12135,19 +12135,19 @@
         <v>105.415</v>
       </c>
       <c r="F12" t="n">
-        <v>2424.361</v>
+        <v>2424.964</v>
       </c>
       <c r="G12" t="n">
-        <v>1283.976</v>
+        <v>1281.994</v>
       </c>
       <c r="H12" t="n">
         <v>1463.76</v>
       </c>
       <c r="I12" t="n">
-        <v>3002.434</v>
+        <v>3003.138</v>
       </c>
       <c r="J12" t="n">
-        <v>2112.094</v>
+        <v>2112.798</v>
       </c>
       <c r="K12" t="n">
         <v>890.34</v>
@@ -12156,73 +12156,73 @@
         <v>980.3200000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>9154.851000000001</v>
+        <v>9154.174999999999</v>
       </c>
       <c r="N12" t="n">
         <v>80.268</v>
       </c>
       <c r="O12" t="n">
-        <v>5193.56</v>
+        <v>5194.236</v>
       </c>
       <c r="P12" t="n">
         <v>1813.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>3299.553</v>
+        <v>3300.228</v>
       </c>
       <c r="R12" t="n">
-        <v>661.298</v>
+        <v>687.044</v>
       </c>
       <c r="S12" t="n">
-        <v>3200.046</v>
+        <v>3221.712</v>
       </c>
       <c r="T12" t="n">
-        <v>36.4</v>
+        <v>36.404</v>
       </c>
       <c r="U12" t="n">
-        <v>5.371</v>
+        <v>5.408</v>
       </c>
       <c r="V12" t="n">
-        <v>16.991</v>
+        <v>16.996</v>
       </c>
       <c r="W12" t="n">
-        <v>8.999000000000001</v>
+        <v>8.984999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>10.259</v>
       </c>
       <c r="Y12" t="n">
-        <v>21.043</v>
+        <v>21.048</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.803</v>
+        <v>14.808</v>
       </c>
       <c r="AA12" t="n">
         <v>6.871</v>
       </c>
       <c r="AB12" t="n">
-        <v>64.163</v>
+        <v>64.158</v>
       </c>
       <c r="AC12" t="n">
         <v>12.712</v>
       </c>
       <c r="AD12" t="n">
-        <v>16.221</v>
+        <v>16.249</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.798</v>
+        <v>3.637</v>
       </c>
       <c r="AF12" t="n">
         <v>9.481</v>
       </c>
       <c r="AG12" t="n">
-        <v>26.365</v>
+        <v>26.395</v>
       </c>
       <c r="AH12" t="n">
         <v>-8.295999999999999</v>
       </c>
       <c r="AI12" t="n">
-        <v>12.953</v>
+        <v>12.945</v>
       </c>
     </row>
     <row r="13">
@@ -12246,19 +12246,19 @@
         <v>115.472</v>
       </c>
       <c r="F13" t="n">
-        <v>2711.881</v>
+        <v>2713.087</v>
       </c>
       <c r="G13" t="n">
-        <v>1319.05</v>
+        <v>1313.663</v>
       </c>
       <c r="H13" t="n">
         <v>1566.586</v>
       </c>
       <c r="I13" t="n">
-        <v>3284.871</v>
+        <v>3285.645</v>
       </c>
       <c r="J13" t="n">
-        <v>2323.303</v>
+        <v>2324.078</v>
       </c>
       <c r="K13" t="n">
         <v>961.567</v>
@@ -12267,52 +12267,52 @@
         <v>1008.7</v>
       </c>
       <c r="M13" t="n">
-        <v>9891.087</v>
+        <v>9887.68</v>
       </c>
       <c r="N13" t="n">
         <v>82.536</v>
       </c>
       <c r="O13" t="n">
-        <v>6020.056</v>
+        <v>6023.462</v>
       </c>
       <c r="P13" t="n">
         <v>2052.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>3884.77</v>
+        <v>3888.177</v>
       </c>
       <c r="R13" t="n">
-        <v>732.754</v>
+        <v>745.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3699.568</v>
+        <v>3712.819</v>
       </c>
       <c r="T13" t="n">
-        <v>38.033</v>
+        <v>38.054</v>
       </c>
       <c r="U13" t="n">
-        <v>6.456</v>
+        <v>6.479</v>
       </c>
       <c r="V13" t="n">
-        <v>17.133</v>
+        <v>17.14</v>
       </c>
       <c r="W13" t="n">
-        <v>8.333</v>
+        <v>8.298999999999999</v>
       </c>
       <c r="X13" t="n">
         <v>9.897</v>
       </c>
       <c r="Y13" t="n">
-        <v>20.753</v>
+        <v>20.758</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.678</v>
+        <v>14.683</v>
       </c>
       <c r="AA13" t="n">
         <v>6.373</v>
       </c>
       <c r="AB13" t="n">
-        <v>62.489</v>
+        <v>62.467</v>
       </c>
       <c r="AC13" t="n">
         <v>12.969</v>
@@ -12357,19 +12357,19 @@
         <v>104.393</v>
       </c>
       <c r="F14" t="n">
-        <v>2422.798</v>
+        <v>2423.149</v>
       </c>
       <c r="G14" t="n">
-        <v>1331.34</v>
+        <v>1330.044</v>
       </c>
       <c r="H14" t="n">
         <v>1490.48</v>
       </c>
       <c r="I14" t="n">
-        <v>3073.249</v>
+        <v>3073.658</v>
       </c>
       <c r="J14" t="n">
-        <v>2120.429</v>
+        <v>2120.838</v>
       </c>
       <c r="K14" t="n">
         <v>952.8200000000001</v>
@@ -12378,73 +12378,73 @@
         <v>1011.28</v>
       </c>
       <c r="M14" t="n">
-        <v>9329.146000000001</v>
+        <v>9328.610000000001</v>
       </c>
       <c r="N14" t="n">
         <v>80.268</v>
       </c>
       <c r="O14" t="n">
-        <v>4915.928</v>
+        <v>4916.465</v>
       </c>
       <c r="P14" t="n">
         <v>1813.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>3021.921</v>
+        <v>3022.457</v>
       </c>
       <c r="R14" t="n">
-        <v>653.466</v>
+        <v>670.011</v>
       </c>
       <c r="S14" t="n">
-        <v>2965.965</v>
+        <v>2979.972</v>
       </c>
       <c r="T14" t="n">
-        <v>34.705</v>
+        <v>34.709</v>
       </c>
       <c r="U14" t="n">
-        <v>4.978</v>
+        <v>5.002</v>
       </c>
       <c r="V14" t="n">
-        <v>17.104</v>
+        <v>17.107</v>
       </c>
       <c r="W14" t="n">
-        <v>9.398999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="X14" t="n">
         <v>10.522</v>
       </c>
       <c r="Y14" t="n">
-        <v>21.696</v>
+        <v>21.699</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.97</v>
+        <v>14.973</v>
       </c>
       <c r="AA14" t="n">
         <v>7.139</v>
       </c>
       <c r="AB14" t="n">
-        <v>65.861</v>
+        <v>65.858</v>
       </c>
       <c r="AC14" t="n">
         <v>12.805</v>
       </c>
       <c r="AD14" t="n">
-        <v>16.146</v>
+        <v>16.162</v>
       </c>
       <c r="AE14" t="n">
-        <v>7.626</v>
+        <v>7.522</v>
       </c>
       <c r="AF14" t="n">
         <v>11.479</v>
       </c>
       <c r="AG14" t="n">
-        <v>29.345</v>
+        <v>29.363</v>
       </c>
       <c r="AH14" t="n">
         <v>-5.399</v>
       </c>
       <c r="AI14" t="n">
-        <v>15.104</v>
+        <v>15.097</v>
       </c>
     </row>
     <row r="15">
@@ -12468,19 +12468,19 @@
         <v>107.833</v>
       </c>
       <c r="F15" t="n">
-        <v>2684.325</v>
+        <v>2685.026</v>
       </c>
       <c r="G15" t="n">
-        <v>1457.469</v>
+        <v>1453.344</v>
       </c>
       <c r="H15" t="n">
         <v>1699.528</v>
       </c>
       <c r="I15" t="n">
-        <v>3692.194</v>
+        <v>3692.693</v>
       </c>
       <c r="J15" t="n">
-        <v>2586.923</v>
+        <v>2587.422</v>
       </c>
       <c r="K15" t="n">
         <v>1105.271</v>
@@ -12489,52 +12489,52 @@
         <v>1091.102</v>
       </c>
       <c r="M15" t="n">
-        <v>10624.619</v>
+        <v>10621.694</v>
       </c>
       <c r="N15" t="n">
         <v>82.536</v>
       </c>
       <c r="O15" t="n">
-        <v>4406.251</v>
+        <v>4409.176</v>
       </c>
       <c r="P15" t="n">
         <v>2052.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>2270.966</v>
+        <v>2273.891</v>
       </c>
       <c r="R15" t="n">
-        <v>691.0170000000001</v>
+        <v>691.097</v>
       </c>
       <c r="S15" t="n">
-        <v>2333.746</v>
+        <v>2336.225</v>
       </c>
       <c r="T15" t="n">
-        <v>29.477</v>
+        <v>29.496</v>
       </c>
       <c r="U15" t="n">
-        <v>4.073</v>
+        <v>4.077</v>
       </c>
       <c r="V15" t="n">
-        <v>17.957</v>
+        <v>17.962</v>
       </c>
       <c r="W15" t="n">
-        <v>9.75</v>
+        <v>9.722</v>
       </c>
       <c r="X15" t="n">
         <v>11.369</v>
       </c>
       <c r="Y15" t="n">
-        <v>24.7</v>
+        <v>24.703</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.306</v>
+        <v>17.309</v>
       </c>
       <c r="AA15" t="n">
         <v>7.299</v>
       </c>
       <c r="AB15" t="n">
-        <v>71.07599999999999</v>
+        <v>71.056</v>
       </c>
       <c r="AC15" t="n">
         <v>13.732</v>
@@ -12579,19 +12579,19 @@
         <v>106.514</v>
       </c>
       <c r="F16" t="n">
-        <v>2444.274</v>
+        <v>2444.877</v>
       </c>
       <c r="G16" t="n">
-        <v>1285.233</v>
+        <v>1283.351</v>
       </c>
       <c r="H16" t="n">
         <v>1463.76</v>
       </c>
       <c r="I16" t="n">
-        <v>3002.434</v>
+        <v>3003.138</v>
       </c>
       <c r="J16" t="n">
-        <v>2112.094</v>
+        <v>2112.798</v>
       </c>
       <c r="K16" t="n">
         <v>890.34</v>
@@ -12600,73 +12600,73 @@
         <v>980.3200000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>9176.021000000001</v>
+        <v>9175.446</v>
       </c>
       <c r="N16" t="n">
         <v>80.268</v>
       </c>
       <c r="O16" t="n">
-        <v>5296.183</v>
+        <v>5296.759</v>
       </c>
       <c r="P16" t="n">
         <v>1813.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>3402.176</v>
+        <v>3402.751</v>
       </c>
       <c r="R16" t="n">
-        <v>662.775</v>
+        <v>689.326</v>
       </c>
       <c r="S16" t="n">
-        <v>3285.407</v>
+        <v>3307.651</v>
       </c>
       <c r="T16" t="n">
-        <v>36.8</v>
+        <v>36.804</v>
       </c>
       <c r="U16" t="n">
-        <v>5.515</v>
+        <v>5.552</v>
       </c>
       <c r="V16" t="n">
-        <v>16.984</v>
+        <v>16.988</v>
       </c>
       <c r="W16" t="n">
-        <v>8.93</v>
+        <v>8.917</v>
       </c>
       <c r="X16" t="n">
         <v>10.171</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.862</v>
+        <v>20.867</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.676</v>
+        <v>14.68</v>
       </c>
       <c r="AA16" t="n">
         <v>6.812</v>
       </c>
       <c r="AB16" t="n">
-        <v>63.758</v>
+        <v>63.754</v>
       </c>
       <c r="AC16" t="n">
         <v>12.602</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.175</v>
+        <v>17.204</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.899</v>
+        <v>3.747</v>
       </c>
       <c r="AF16" t="n">
         <v>9.481</v>
       </c>
       <c r="AG16" t="n">
-        <v>26.365</v>
+        <v>26.395</v>
       </c>
       <c r="AH16" t="n">
         <v>-8.295999999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>13.214</v>
+        <v>13.207</v>
       </c>
     </row>
     <row r="17">
@@ -12690,19 +12690,19 @@
         <v>122.212</v>
       </c>
       <c r="F17" t="n">
-        <v>2832.507</v>
+        <v>2833.714</v>
       </c>
       <c r="G17" t="n">
-        <v>1327.48</v>
+        <v>1322.753</v>
       </c>
       <c r="H17" t="n">
         <v>1566.586</v>
       </c>
       <c r="I17" t="n">
-        <v>3284.871</v>
+        <v>3285.645</v>
       </c>
       <c r="J17" t="n">
-        <v>2323.303</v>
+        <v>2324.078</v>
       </c>
       <c r="K17" t="n">
         <v>961.567</v>
@@ -12711,52 +12711,52 @@
         <v>1008.7</v>
       </c>
       <c r="M17" t="n">
-        <v>10020.143</v>
+        <v>10017.396</v>
       </c>
       <c r="N17" t="n">
         <v>82.536</v>
       </c>
       <c r="O17" t="n">
-        <v>6633.137</v>
+        <v>6635.883</v>
       </c>
       <c r="P17" t="n">
         <v>2052.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>4497.851</v>
+        <v>4500.598</v>
       </c>
       <c r="R17" t="n">
-        <v>744.3440000000001</v>
+        <v>764.271</v>
       </c>
       <c r="S17" t="n">
-        <v>4214.921</v>
+        <v>4233.626</v>
       </c>
       <c r="T17" t="n">
-        <v>40.029</v>
+        <v>40.046</v>
       </c>
       <c r="U17" t="n">
-        <v>7.355</v>
+        <v>7.388</v>
       </c>
       <c r="V17" t="n">
-        <v>17.093</v>
+        <v>17.101</v>
       </c>
       <c r="W17" t="n">
-        <v>8.010999999999999</v>
+        <v>7.982</v>
       </c>
       <c r="X17" t="n">
         <v>9.454000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>19.823</v>
+        <v>19.828</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.021</v>
+        <v>14.025</v>
       </c>
       <c r="AA17" t="n">
         <v>6.087</v>
       </c>
       <c r="AB17" t="n">
-        <v>60.469</v>
+        <v>60.452</v>
       </c>
       <c r="AC17" t="n">
         <v>12.388</v>
@@ -12801,19 +12801,19 @@
         <v>125.021</v>
       </c>
       <c r="F18" t="n">
-        <v>2986.436</v>
+        <v>2987.795</v>
       </c>
       <c r="G18" t="n">
-        <v>1497.998</v>
+        <v>1491.81</v>
       </c>
       <c r="H18" t="n">
         <v>1759.681</v>
       </c>
       <c r="I18" t="n">
-        <v>3744.781</v>
+        <v>3745.693</v>
       </c>
       <c r="J18" t="n">
-        <v>2637.241</v>
+        <v>2638.153</v>
       </c>
       <c r="K18" t="n">
         <v>1107.54</v>
@@ -12822,55 +12822,55 @@
         <v>1130.911</v>
       </c>
       <c r="M18" t="n">
-        <v>11119.808</v>
+        <v>11115.89</v>
       </c>
       <c r="N18" t="n">
         <v>89.361</v>
       </c>
       <c r="O18" t="n">
-        <v>6106.994</v>
+        <v>6110.912</v>
       </c>
       <c r="P18" t="n">
         <v>2222.487</v>
       </c>
       <c r="Q18" t="n">
-        <v>3795.146</v>
+        <v>3799.064</v>
       </c>
       <c r="R18" t="n">
-        <v>793.3440000000001</v>
+        <v>807.047</v>
       </c>
       <c r="S18" t="n">
-        <v>3666.528</v>
+        <v>3681.065</v>
       </c>
       <c r="T18" t="n">
-        <v>35.635</v>
+        <v>35.658</v>
       </c>
       <c r="U18" t="n">
-        <v>6.398</v>
+        <v>6.424</v>
       </c>
       <c r="V18" t="n">
-        <v>18.867</v>
+        <v>17.434</v>
       </c>
       <c r="W18" t="n">
-        <v>9.464</v>
+        <v>8.705</v>
       </c>
       <c r="X18" t="n">
-        <v>11.117</v>
+        <v>10.268</v>
       </c>
       <c r="Y18" t="n">
-        <v>23.658</v>
+        <v>21.857</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.661</v>
+        <v>15.394</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.145</v>
+        <v>6.599</v>
       </c>
       <c r="AB18" t="n">
-        <v>70.251</v>
+        <v>64.863</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.041</v>
+        <v>12.969</v>
       </c>
       <c r="AD18" t="n">
         <v/>
@@ -12902,10 +12902,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="65" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52.37</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="5">
@@ -12958,86 +12958,96 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.48</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reconciled base: 3Q26 margin</t>
+          <t>reconciled base: 3Q26 margin at the GUIDE midpoint revenue (by construction = target)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.37</v>
+        <v>49.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reconciled base: 3Q26 total cash cost growth y/y %</t>
+          <t>reconciled base: 3Q26 margin at OUR revenue ($4,804M; the forecast)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.13</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reconciled base: cost gap assigned in 3Q26, USD m</t>
+          <t>reconciled base: 3Q26 total cash cost growth y/y %</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>96.31</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2H26 marketing growth % that lands the sentence (all else base)</t>
+          <t>reconciled base: cost gap assigned in 3Q26, USD m</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60.35</v>
+        <v>97.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3Q26 S&amp;M at that growth, USD m</t>
+          <t>2H26 marketing growth % that lands the sentence AT OUR revenue with no hosting step (evidence build)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>843.8</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3Q26 S&amp;M y/y % at that growth</t>
+          <t>3Q26 S&amp;M at that growth, USD m</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44.24</v>
+        <v>844.85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3Q26 total cash cost growth y/y % at that growth</t>
+          <t>3Q26 S&amp;M y/y % at that growth</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.93</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>3Q26 total cash cost growth y/y % at that growth</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>17.93</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>FY26 margin at that growth</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" t="n">
         <v>34.67</v>
       </c>
     </row>
@@ -13058,7 +13068,7 @@
     <col width="70" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -13134,7 +13144,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1H26 cost of revenue with the base rates and 1H26 drivers</t>
+          <t>1H26 cost of revenue with the base rates (1.70% x seasonal factors) and 1H26 drivers</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -13145,7 +13155,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>in sample (1.66% sits between FY25 1.76% and the 1H26 fit 1.62%)</t>
+          <t>in sample; the 1H26 fit itself is 1.68% annual-equivalent, FY25 1.76%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -13155,22 +13165,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1H26 ops &amp; support per booking, y/y %</t>
+          <t>1H26 ops &amp; support from the rule with v = 0.215 (exact calibration)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5.06</v>
+        <v>624.01</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.1</v>
+        <v>624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>calibration of the variable share v = 0.19; identity, not a test</t>
+          <t>calibration identity, not a test</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13251,7 +13261,7 @@
         <v>-0.669</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.152</v>
+        <v>-0.153</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -13275,10 +13285,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.52</v>
+        <v>0.526</v>
       </c>
       <c r="E3" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -13437,16 +13447,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.202</v>
+        <v>-0.195</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.046</v>
+        <v>-0.045</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.335000000000001</v>
+        <v>-8.077999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.308</v>
+        <v>-0.298</v>
       </c>
     </row>
     <row r="10">
@@ -13626,16 +13636,16 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.068</v>
+        <v>-0.077</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.015</v>
+        <v>-0.017</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.068</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="17">
@@ -13761,16 +13771,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.904</v>
+        <v>-3.286</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.036</v>
+        <v>-0.041</v>
       </c>
     </row>
     <row r="22">
@@ -13791,7 +13801,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.143</v>
+        <v>-0.144</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -13818,7 +13828,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.281</v>
+        <v>0.285</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -13845,7 +13855,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.044</v>
+        <v>-0.05</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -13914,13 +13924,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>640.47</v>
+        <v>640.78</v>
       </c>
       <c r="D2" t="n">
         <v>617.42</v>
       </c>
       <c r="E2" t="n">
-        <v>23.05</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="3">
@@ -13935,13 +13945,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>362.49</v>
+        <v>361.44</v>
       </c>
       <c r="D3" t="n">
         <v>364.81</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.32</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="4">
@@ -13977,13 +13987,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>777.58</v>
+        <v>778.3200000000001</v>
       </c>
       <c r="D5" t="n">
         <v>781.14</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.56</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="6">
@@ -14061,13 +14071,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>577.73</v>
+        <v>578.04</v>
       </c>
       <c r="D9" t="n">
         <v>543.88</v>
       </c>
       <c r="E9" t="n">
-        <v>33.84</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="10">
@@ -14082,13 +14092,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>319.33</v>
+        <v>318.29</v>
       </c>
       <c r="D10" t="n">
         <v>318.29</v>
       </c>
       <c r="E10" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -14166,13 +14176,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>898.14</v>
+        <v>898.87</v>
       </c>
       <c r="D14" t="n">
         <v>918.39</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.25</v>
+        <v>-19.52</v>
       </c>
     </row>
     <row r="15">
@@ -14187,13 +14197,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.26</v>
+        <v>28.28</v>
       </c>
       <c r="D15" t="n">
         <v>28.9</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.64</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="16">
@@ -14208,13 +14218,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>705.6900000000001</v>
+        <v>706</v>
       </c>
       <c r="D16" t="n">
         <v>644.01</v>
       </c>
       <c r="E16" t="n">
-        <v>61.68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -14229,13 +14239,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>319.78</v>
+        <v>319.09</v>
       </c>
       <c r="D17" t="n">
         <v>316.38</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="18">
@@ -14271,13 +14281,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>829.0700000000001</v>
+        <v>829.27</v>
       </c>
       <c r="D19" t="n">
         <v>857.97</v>
       </c>
       <c r="E19" t="n">
-        <v>-28.9</v>
+        <v>-28.7</v>
       </c>
     </row>
     <row r="20">
@@ -14313,13 +14323,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>555.87</v>
+        <v>556.05</v>
       </c>
       <c r="D21" t="n">
         <v>594.45</v>
       </c>
       <c r="E21" t="n">
-        <v>-38.58</v>
+        <v>-38.4</v>
       </c>
     </row>
     <row r="22">
@@ -14355,13 +14365,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>726.99</v>
+        <v>727.3</v>
       </c>
       <c r="D23" t="n">
         <v>688.17</v>
       </c>
       <c r="E23" t="n">
-        <v>38.82</v>
+        <v>39.13</v>
       </c>
     </row>
     <row r="24">
@@ -14376,13 +14386,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>341.88</v>
+        <v>340.97</v>
       </c>
       <c r="D24" t="n">
         <v>334.05</v>
       </c>
       <c r="E24" t="n">
-        <v>7.84</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="25">
@@ -14418,13 +14428,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>934.91</v>
+        <v>935.14</v>
       </c>
       <c r="D26" t="n">
         <v>993.4</v>
       </c>
       <c r="E26" t="n">
-        <v>-58.5</v>
+        <v>-58.27</v>
       </c>
     </row>
     <row r="27">
@@ -14460,13 +14470,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1373.46</v>
+        <v>1373.83</v>
       </c>
       <c r="D28" t="n">
         <v>1371.3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.16</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="29">
@@ -14481,13 +14491,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>34.09</v>
+        <v>34.1</v>
       </c>
       <c r="D29" t="n">
         <v>34.04</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="30">
@@ -14502,13 +14512,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>699.14</v>
+        <v>699.45</v>
       </c>
       <c r="D30" t="n">
         <v>671.63</v>
       </c>
       <c r="E30" t="n">
-        <v>27.51</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="31">
@@ -14523,13 +14533,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>383.87</v>
+        <v>381.76</v>
       </c>
       <c r="D31" t="n">
         <v>378.08</v>
       </c>
       <c r="E31" t="n">
-        <v>5.78</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="32">
@@ -14565,13 +14575,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>819.73</v>
+        <v>819.9299999999999</v>
       </c>
       <c r="D33" t="n">
         <v>967.09</v>
       </c>
       <c r="E33" t="n">
-        <v>-147.36</v>
+        <v>-147.16</v>
       </c>
     </row>
     <row r="34">
@@ -14607,13 +14617,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2742.43</v>
+        <v>2744.03</v>
       </c>
       <c r="D35" t="n">
         <v>2550.76</v>
       </c>
       <c r="E35" t="n">
-        <v>191.67</v>
+        <v>193.26</v>
       </c>
     </row>
     <row r="36">
@@ -14628,13 +14638,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>51.93</v>
+        <v>51.96</v>
       </c>
       <c r="D36" t="n">
         <v>48.3</v>
       </c>
       <c r="E36" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="37">
@@ -14649,13 +14659,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>626.54</v>
+        <v>626.85</v>
       </c>
       <c r="D37" t="n">
         <v>587.04</v>
       </c>
       <c r="E37" t="n">
-        <v>39.5</v>
+        <v>39.81</v>
       </c>
     </row>
     <row r="38">
@@ -14670,13 +14680,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>338.06</v>
+        <v>336.06</v>
       </c>
       <c r="D38" t="n">
         <v>329.44</v>
       </c>
       <c r="E38" t="n">
-        <v>8.619999999999999</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="39">
@@ -14712,13 +14722,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>875.0700000000001</v>
+        <v>875.28</v>
       </c>
       <c r="D40" t="n">
         <v>902.47</v>
       </c>
       <c r="E40" t="n">
-        <v>-27.4</v>
+        <v>-27.18</v>
       </c>
     </row>
     <row r="41">
@@ -14754,13 +14764,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>968.83</v>
+        <v>970.29</v>
       </c>
       <c r="D42" t="n">
         <v>966.8200000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>2.01</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="43">
@@ -14775,13 +14785,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27.95</v>
+        <v>28</v>
       </c>
       <c r="D43" t="n">
         <v>27.9</v>
       </c>
       <c r="E43" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/model/ABNB_margin_line_build.xlsx
+++ b/model/ABNB_margin_line_build.xlsx
@@ -15,7 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backcast" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivities" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vs_run23" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals_1Q23_2Q26" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Short_case" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Short_case_quarterly" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Short_case_revenue_path" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals_1Q23_2Q26" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,13 +493,1587 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_vs_team_path_pct</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nights_yoy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ops_cash</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ops_per_booking</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>chargebacks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>interest_income</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sm_pct_rev</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_cash_costs_pct_rev</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>margin_vs_base_pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3Q26</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4680.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-2.563</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>374.971</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9.442</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.551</v>
+      </c>
+      <c r="H2" t="n">
+        <v>174.359</v>
+      </c>
+      <c r="I2" t="n">
+        <v>16.627</v>
+      </c>
+      <c r="J2" t="n">
+        <v>51.523</v>
+      </c>
+      <c r="K2" t="n">
+        <v>48.918</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-1.449</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4Q26</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2965.868</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-6.678</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>329.176</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.387</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30.508</v>
+      </c>
+      <c r="H3" t="n">
+        <v>156.169</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25.561</v>
+      </c>
+      <c r="J3" t="n">
+        <v>77.107</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23.589</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-4.695</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1Q27</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2835.535</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-7.127</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>329.266</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7.297</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.258</v>
+      </c>
+      <c r="H4" t="n">
+        <v>167.126</v>
+      </c>
+      <c r="I4" t="n">
+        <v>29.246</v>
+      </c>
+      <c r="J4" t="n">
+        <v>88.004</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12.724</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-5.488</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2Q27</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3762.972</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-6.602</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>352.014</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.378</v>
+      </c>
+      <c r="G5" t="n">
+        <v>36.556</v>
+      </c>
+      <c r="H5" t="n">
+        <v>186.133</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24.851</v>
+      </c>
+      <c r="J5" t="n">
+        <v>70.557</v>
+      </c>
+      <c r="K5" t="n">
+        <v>29.992</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-4.107</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3Q27</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4988.174</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-5.54</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>409.419</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9.872</v>
+      </c>
+      <c r="G6" t="n">
+        <v>36.082</v>
+      </c>
+      <c r="H6" t="n">
+        <v>176.877</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16.437</v>
+      </c>
+      <c r="J6" t="n">
+        <v>51.317</v>
+      </c>
+      <c r="K6" t="n">
+        <v>49.097</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-2.866</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4Q27</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3326.831</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-4.009</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>360.088</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.738</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32.169</v>
+      </c>
+      <c r="H7" t="n">
+        <v>160.888</v>
+      </c>
+      <c r="I7" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="J7" t="n">
+        <v>75.881</v>
+      </c>
+      <c r="K7" t="n">
+        <v>24.739</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-3.257</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_musd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>gbv_busd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nights_mm</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nights_yoy_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>adr_reported_yoy_pct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_vs_base_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3Q26</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4680.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.361</v>
+      </c>
+      <c r="D2" t="n">
+        <v>144.956</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-2.563</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4Q26</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2965.868</v>
+      </c>
+      <c r="C3" t="n">
+        <v>21.452</v>
+      </c>
+      <c r="D3" t="n">
+        <v>127.995</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-6.678</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1Q27</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2835.535</v>
+      </c>
+      <c r="C4" t="n">
+        <v>30.276</v>
+      </c>
+      <c r="D4" t="n">
+        <v>162.448</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.302</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-7.127</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2Q27</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3762.972</v>
+      </c>
+      <c r="C5" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="D5" t="n">
+        <v>151.266</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-6.602</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3Q27</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4988.174</v>
+      </c>
+      <c r="C6" t="n">
+        <v>26.818</v>
+      </c>
+      <c r="D6" t="n">
+        <v>149.305</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-5.54</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4Q27</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3326.831</v>
+      </c>
+      <c r="C7" t="n">
+        <v>23.839</v>
+      </c>
+      <c r="D7" t="n">
+        <v>133.115</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.285</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-4.009</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>nights_m</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>gbv_busd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cor_cash</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ops_cash</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pd_cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>sm_cash</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ga_cash</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ga_cash_ex_lodging</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lodging_tax_reserves</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>sbc_total_is</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>adj_ebitda_reported</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>adj_ebitda_margin_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>interest_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>eps_diluted</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shares_diluted_m</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>funds_held_on_behalf</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1Q23</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1818</v>
+      </c>
+      <c r="C2" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>428</v>
+      </c>
+      <c r="F2" t="n">
+        <v>267</v>
+      </c>
+      <c r="G2" t="n">
+        <v>271</v>
+      </c>
+      <c r="H2" t="n">
+        <v>422</v>
+      </c>
+      <c r="I2" t="n">
+        <v>195</v>
+      </c>
+      <c r="J2" t="n">
+        <v>191</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" t="n">
+        <v>240</v>
+      </c>
+      <c r="N2" t="n">
+        <v>262</v>
+      </c>
+      <c r="O2" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="P2" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>117</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>670</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7760</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2Q23</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2484</v>
+      </c>
+      <c r="C3" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>432</v>
+      </c>
+      <c r="F3" t="n">
+        <v>298</v>
+      </c>
+      <c r="G3" t="n">
+        <v>260</v>
+      </c>
+      <c r="H3" t="n">
+        <v>450</v>
+      </c>
+      <c r="I3" t="n">
+        <v>217</v>
+      </c>
+      <c r="J3" t="n">
+        <v>219</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>304</v>
+      </c>
+      <c r="N3" t="n">
+        <v>819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="P3" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>650</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S3" t="n">
+        <v>665</v>
+      </c>
+      <c r="T3" t="n">
+        <v>9144</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3Q23</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3397</v>
+      </c>
+      <c r="C4" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>459</v>
+      </c>
+      <c r="F4" t="n">
+        <v>299</v>
+      </c>
+      <c r="G4" t="n">
+        <v>244</v>
+      </c>
+      <c r="H4" t="n">
+        <v>370</v>
+      </c>
+      <c r="I4" t="n">
+        <v>243</v>
+      </c>
+      <c r="J4" t="n">
+        <v>202</v>
+      </c>
+      <c r="K4" t="n">
+        <v>41</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>286</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1834</v>
+      </c>
+      <c r="O4" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="P4" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4374</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="S4" t="n">
+        <v>660</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5986</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4Q23</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2218</v>
+      </c>
+      <c r="C5" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>384</v>
+      </c>
+      <c r="F5" t="n">
+        <v>254</v>
+      </c>
+      <c r="G5" t="n">
+        <v>253</v>
+      </c>
+      <c r="H5" t="n">
+        <v>391</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1142</v>
+      </c>
+      <c r="J5" t="n">
+        <v>211</v>
+      </c>
+      <c r="K5" t="n">
+        <v>931</v>
+      </c>
+      <c r="L5" t="n">
+        <v>16</v>
+      </c>
+      <c r="M5" t="n">
+        <v>290</v>
+      </c>
+      <c r="N5" t="n">
+        <v>738</v>
+      </c>
+      <c r="O5" t="n">
+        <v>33.27</v>
+      </c>
+      <c r="P5" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-349</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="S5" t="n">
+        <v>640</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5869</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1Q24</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C6" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>480</v>
+      </c>
+      <c r="F6" t="n">
+        <v>266</v>
+      </c>
+      <c r="G6" t="n">
+        <v>290</v>
+      </c>
+      <c r="H6" t="n">
+        <v>479</v>
+      </c>
+      <c r="I6" t="n">
+        <v>231</v>
+      </c>
+      <c r="J6" t="n">
+        <v>223</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>14</v>
+      </c>
+      <c r="M6" t="n">
+        <v>295</v>
+      </c>
+      <c r="N6" t="n">
+        <v>424</v>
+      </c>
+      <c r="O6" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="P6" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>264</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="S6" t="n">
+        <v>654</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8737</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2Q24</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2748</v>
+      </c>
+      <c r="C7" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>506</v>
+      </c>
+      <c r="F7" t="n">
+        <v>314</v>
+      </c>
+      <c r="G7" t="n">
+        <v>280</v>
+      </c>
+      <c r="H7" t="n">
+        <v>527</v>
+      </c>
+      <c r="I7" t="n">
+        <v>242</v>
+      </c>
+      <c r="J7" t="n">
+        <v>242</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>14</v>
+      </c>
+      <c r="M7" t="n">
+        <v>382</v>
+      </c>
+      <c r="N7" t="n">
+        <v>894</v>
+      </c>
+      <c r="O7" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="P7" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>555</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="S7" t="n">
+        <v>649</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10342</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3Q24</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3732</v>
+      </c>
+      <c r="C8" t="n">
+        <v>122.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>465</v>
+      </c>
+      <c r="F8" t="n">
+        <v>347</v>
+      </c>
+      <c r="G8" t="n">
+        <v>294</v>
+      </c>
+      <c r="H8" t="n">
+        <v>471</v>
+      </c>
+      <c r="I8" t="n">
+        <v>268</v>
+      </c>
+      <c r="J8" t="n">
+        <v>210</v>
+      </c>
+      <c r="K8" t="n">
+        <v>58</v>
+      </c>
+      <c r="L8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M8" t="n">
+        <v>362</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1958</v>
+      </c>
+      <c r="O8" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="P8" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1368</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S8" t="n">
+        <v>642</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6573</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4Q24</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2480</v>
+      </c>
+      <c r="C9" t="n">
+        <v>111</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>427</v>
+      </c>
+      <c r="F9" t="n">
+        <v>265</v>
+      </c>
+      <c r="G9" t="n">
+        <v>306</v>
+      </c>
+      <c r="H9" t="n">
+        <v>501</v>
+      </c>
+      <c r="I9" t="n">
+        <v>183</v>
+      </c>
+      <c r="J9" t="n">
+        <v>226</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-43</v>
+      </c>
+      <c r="L9" t="n">
+        <v>22</v>
+      </c>
+      <c r="M9" t="n">
+        <v>368</v>
+      </c>
+      <c r="N9" t="n">
+        <v>765</v>
+      </c>
+      <c r="O9" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="P9" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>461</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="S9" t="n">
+        <v>636</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5931</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1Q25</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2272</v>
+      </c>
+      <c r="C10" t="n">
+        <v>143.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>506</v>
+      </c>
+      <c r="F10" t="n">
+        <v>282</v>
+      </c>
+      <c r="G10" t="n">
+        <v>338</v>
+      </c>
+      <c r="H10" t="n">
+        <v>519</v>
+      </c>
+      <c r="I10" t="n">
+        <v>231</v>
+      </c>
+      <c r="J10" t="n">
+        <v>235</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>358</v>
+      </c>
+      <c r="N10" t="n">
+        <v>417</v>
+      </c>
+      <c r="O10" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="P10" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>154</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>632</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9175</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2Q25</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3096</v>
+      </c>
+      <c r="C11" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>544</v>
+      </c>
+      <c r="F11" t="n">
+        <v>309</v>
+      </c>
+      <c r="G11" t="n">
+        <v>331</v>
+      </c>
+      <c r="H11" t="n">
+        <v>639</v>
+      </c>
+      <c r="I11" t="n">
+        <v>237</v>
+      </c>
+      <c r="J11" t="n">
+        <v>244</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>21</v>
+      </c>
+      <c r="M11" t="n">
+        <v>424</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1043</v>
+      </c>
+      <c r="O11" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="P11" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>642</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S11" t="n">
+        <v>626</v>
+      </c>
+      <c r="T11" t="n">
+        <v>11067</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3Q25</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4095</v>
+      </c>
+      <c r="C12" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>549</v>
+      </c>
+      <c r="F12" t="n">
+        <v>343</v>
+      </c>
+      <c r="G12" t="n">
+        <v>333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>585</v>
+      </c>
+      <c r="I12" t="n">
+        <v>261</v>
+      </c>
+      <c r="J12" t="n">
+        <v>257</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M12" t="n">
+        <v>399</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2051</v>
+      </c>
+      <c r="O12" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="P12" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1374</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>621</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7209</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4Q25</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2778</v>
+      </c>
+      <c r="C13" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>487</v>
+      </c>
+      <c r="F13" t="n">
+        <v>303</v>
+      </c>
+      <c r="G13" t="n">
+        <v>335</v>
+      </c>
+      <c r="H13" t="n">
+        <v>633</v>
+      </c>
+      <c r="I13" t="n">
+        <v>340</v>
+      </c>
+      <c r="J13" t="n">
+        <v>259</v>
+      </c>
+      <c r="K13" t="n">
+        <v>81</v>
+      </c>
+      <c r="L13" t="n">
+        <v>23</v>
+      </c>
+      <c r="M13" t="n">
+        <v>411</v>
+      </c>
+      <c r="N13" t="n">
+        <v>786</v>
+      </c>
+      <c r="O13" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="P13" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>341</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>614</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6959</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2678</v>
+      </c>
+      <c r="C14" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>581</v>
+      </c>
+      <c r="F14" t="n">
+        <v>301</v>
+      </c>
+      <c r="G14" t="n">
+        <v>375</v>
+      </c>
+      <c r="H14" t="n">
+        <v>696</v>
+      </c>
+      <c r="I14" t="n">
+        <v>229</v>
+      </c>
+      <c r="J14" t="n">
+        <v>226</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>22</v>
+      </c>
+      <c r="M14" t="n">
+        <v>410</v>
+      </c>
+      <c r="N14" t="n">
+        <v>519</v>
+      </c>
+      <c r="O14" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>155</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>160</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S14" t="n">
+        <v>608</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10550</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3608</v>
+      </c>
+      <c r="C15" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>633</v>
+      </c>
+      <c r="F15" t="n">
+        <v>323</v>
+      </c>
+      <c r="G15" t="n">
+        <v>374</v>
+      </c>
+      <c r="H15" t="n">
+        <v>808</v>
+      </c>
+      <c r="I15" t="n">
+        <v>225</v>
+      </c>
+      <c r="J15" t="n">
+        <v>227</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M15" t="n">
+        <v>487</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1261</v>
+      </c>
+      <c r="O15" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="P15" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>816</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S15" t="n">
+        <v>597</v>
+      </c>
+      <c r="T15" t="n">
+        <v>12224</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1509,93 +3086,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>below</t>
+          <t>overlay</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>da_per_q</t>
+          <t>rnpl_ops_uplift_pct</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>20.63397059990752</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>20.63397059990752</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>20.63397059990752</v>
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>USD m per quarter</t>
+          <t>% uplift on ops &amp; support per completed booking</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>M7 parameter sheet</t>
+          <t>Cancellations raise contacts, refunds and make-goods per completed stay: 2Q26 10-Q customer relations +$10M on higher make-good payouts and related case reserves, 1Q26 +$3M refunds and credits; short case 4%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>below</t>
+          <t>overlay</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sbc_growth</t>
+          <t>chargeback_add_per_booking</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13.17774076718567</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>13.17774076718567</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>13.17774076718567</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>% y/y on SBC[q-4]</t>
+          <t>USD per booking added</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>M7 (recency-weighted last-4 y/y); mgmt: SBC growth below FY25's</t>
+          <t>1H26 chargebacks +$25M y/y (+37%) after two years of declines; short case +$0.15</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>below</t>
+          <t>overlay</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>interest_income_beta</t>
+          <t>q4_marketing_cut_musd</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.8764975067193741</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8764975067193741</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8764975067193741</v>
+        <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>x 3m T-bill x avg earning base / 4</t>
+          <t>USD m cut from 4Q26 marketing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>M7 / WS04 rule (r 0.83, n 18)</t>
+          <t>Management protected the FY floor in 4Q24 by phasing brand marketing down; the short case reports the cut needed</t>
         </is>
       </c>
     </row>
@@ -1607,26 +3184,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>da_per_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.76</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="D36" t="n">
-        <v>3.76</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="E36" t="n">
-        <v>3.76</v>
+        <v>20.63397059990752</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>% (3Q26 QTD average, held)</t>
+          <t>USD m per quarter</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FRED DTB3 via M7</t>
+          <t>M7 parameter sheet</t>
         </is>
       </c>
     </row>
@@ -1638,26 +3215,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cash_plus_sti</t>
+          <t>sbc_growth</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12069</v>
+        <v>13.17774076718567</v>
       </c>
       <c r="D37" t="n">
-        <v>12069</v>
+        <v>13.17774076718567</v>
       </c>
       <c r="E37" t="n">
-        <v>12069</v>
+        <v>13.17774076718567</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>USD m, held flat</t>
+          <t>% y/y on SBC[q-4]</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>WS02 2Q26</t>
+          <t>M7 (recency-weighted last-4 y/y); mgmt: SBC growth below FY25's</t>
         </is>
       </c>
     </row>
@@ -1669,26 +3246,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>rnpl_share_shift_pts</t>
+          <t>interest_income_beta</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.8764975067193741</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>0.8764975067193741</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.8764975067193741</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>pts of GBV paid at check-in rather than at booking, vs 2025</t>
+          <t>x 3m T-bill x avg earning base / 4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No RNPL share series exists in the repo; sensitivity only: each 10 pts of GBV paid later cuts average funds held by ~10%</t>
+          <t>M7 / WS04 rule (r 0.83, n 18)</t>
         </is>
       </c>
     </row>
@@ -1700,26 +3277,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>interest_expense_per_q</t>
+          <t>tbill_3m</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37</v>
+        <v>3.76</v>
       </c>
       <c r="D39" t="n">
-        <v>37</v>
+        <v>3.76</v>
       </c>
       <c r="E39" t="n">
-        <v>37</v>
+        <v>3.76</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>USD m per quarter</t>
+          <t>% (3Q26 QTD average, held)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>M7: $2.5bn notes (~$119M a year, WS05 H10)</t>
+          <t>FRED DTB3 via M7</t>
         </is>
       </c>
     </row>
@@ -1731,26 +3308,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>other_income_per_q</t>
+          <t>cash_plus_sti</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.7</v>
+        <v>12069</v>
       </c>
       <c r="D40" t="n">
-        <v>3.7</v>
+        <v>12069</v>
       </c>
       <c r="E40" t="n">
-        <v>3.7</v>
+        <v>12069</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>USD m per quarter</t>
+          <t>USD m, held flat</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>M7 recency-weighted mean</t>
+          <t>WS02 2Q26</t>
         </is>
       </c>
     </row>
@@ -1762,26 +3339,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>etr_2h26</t>
+          <t>rnpl_share_shift_pts</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>% applied to 2H26 forecast quarters (1H26 printed 17.1%)</t>
+          <t>pts of GBV paid at check-in rather than at booking, vs 2025</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>M7; mgmt high teens (2Q26)</t>
+          <t>No RNPL share series exists in the repo; sensitivity only: each 10 pts of GBV paid later cuts average funds held by ~10%</t>
         </is>
       </c>
     </row>
@@ -1793,26 +3370,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>etr_fy27</t>
+          <t>interest_expense_per_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17.5</v>
+        <v>37</v>
       </c>
       <c r="D42" t="n">
-        <v>17.5</v>
+        <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>17.5</v>
+        <v>37</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m per quarter</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>M7; long-term mid-to-high teens under OBBBA (WS05 H09)</t>
+          <t>M7: $2.5bn notes (~$119M a year, WS05 H10)</t>
         </is>
       </c>
     </row>
@@ -1824,26 +3401,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>diluted_shares_2q26</t>
+          <t>other_income_per_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>597</v>
+        <v>3.7</v>
       </c>
       <c r="D43" t="n">
-        <v>597</v>
+        <v>3.7</v>
       </c>
       <c r="E43" t="n">
-        <v>597</v>
+        <v>3.7</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>USD m per quarter</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>WS02 2Q26</t>
+          <t>M7 recency-weighted mean</t>
         </is>
       </c>
     </row>
@@ -1855,24 +3432,117 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>etr_2h26</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D44" t="n">
+        <v>18</v>
+      </c>
+      <c r="E44" t="n">
+        <v>18</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>% applied to 2H26 forecast quarters (1H26 printed 17.1%)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>M7; mgmt high teens (2Q26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>etr_fy27</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>M7; long-term mid-to-high teens under OBBBA (WS05 H09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>diluted_shares_2q26</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>597</v>
+      </c>
+      <c r="D46" t="n">
+        <v>597</v>
+      </c>
+      <c r="E46" t="n">
+        <v>597</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>WS02 2Q26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>diluted_shares_delta_per_q</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C47" t="n">
         <v>-5.324186618094461</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D47" t="n">
         <v>-5.324186618094461</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E47" t="n">
         <v>-5.324186618094461</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>m per quarter</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>M7: -buyback/price + issuance; authorisation runs out ~1Q27 (WS05 H11)</t>
         </is>
@@ -14805,10 +16475,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -14824,1008 +16494,192 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>quarter</t>
+          <t>case</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>q3_ebitda</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>nights_m</t>
+          <t>q3_margin</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>gbv_busd</t>
+          <t>q3_revenue</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>cor_cash</t>
+          <t>q4_ebitda</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ops_cash</t>
+          <t>q4_margin</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>pd_cash</t>
+          <t>q4_revenue</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>sm_cash</t>
+          <t>fy26_ebitda</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>ga_cash</t>
+          <t>fy26_margin</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>ga_cash_ex_lodging</t>
+          <t>fy26_revenue</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>lodging_tax_reserves</t>
+          <t>fy27_ebitda</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>fy27_margin</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>sbc_total_is</t>
+          <t>fy27_revenue</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>adj_ebitda_reported</t>
+          <t>q3_eps</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>adj_ebitda_margin_pct</t>
+          <t>fy27_eps</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>interest_income</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>net_income</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>eps_diluted</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>shares_diluted_m</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>funds_held_on_behalf</t>
+          <t>q4_marketing_cut_musd</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1Q23</t>
+          <t>short_costs_at_budget</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1818</v>
+        <v>2289.815</v>
       </c>
       <c r="C2" t="n">
-        <v>121.1</v>
+        <v>48.918</v>
       </c>
       <c r="D2" t="n">
-        <v>20.4</v>
+        <v>4680.9</v>
       </c>
       <c r="E2" t="n">
-        <v>428</v>
+        <v>699.6079999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>267</v>
+        <v>23.589</v>
       </c>
       <c r="G2" t="n">
-        <v>271</v>
+        <v>2965.868</v>
       </c>
       <c r="H2" t="n">
-        <v>422</v>
+        <v>4769.423</v>
       </c>
       <c r="I2" t="n">
-        <v>195</v>
+        <v>34.232</v>
       </c>
       <c r="J2" t="n">
-        <v>191</v>
+        <v>13932.768</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>4761.435</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>31.927</v>
       </c>
       <c r="M2" t="n">
-        <v>240</v>
+        <v>14913.512</v>
       </c>
       <c r="N2" t="n">
-        <v>262</v>
+        <v>2.714</v>
       </c>
       <c r="O2" t="n">
-        <v>14.41</v>
+        <v>4.584</v>
       </c>
       <c r="P2" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>117</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>670</v>
-      </c>
-      <c r="T2" t="n">
-        <v>7760</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2Q23</t>
+          <t>short_with_q4_marketing_cut</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2484</v>
+        <v>2289.815</v>
       </c>
       <c r="C3" t="n">
-        <v>115.1</v>
+        <v>48.918</v>
       </c>
       <c r="D3" t="n">
-        <v>19.1</v>
+        <v>4680.9</v>
       </c>
       <c r="E3" t="n">
-        <v>432</v>
+        <v>876.317</v>
       </c>
       <c r="F3" t="n">
-        <v>298</v>
+        <v>29.547</v>
       </c>
       <c r="G3" t="n">
-        <v>260</v>
+        <v>2965.868</v>
       </c>
       <c r="H3" t="n">
-        <v>450</v>
+        <v>4946.133</v>
       </c>
       <c r="I3" t="n">
-        <v>217</v>
+        <v>35.5</v>
       </c>
       <c r="J3" t="n">
-        <v>219</v>
+        <v>13932.768</v>
       </c>
       <c r="K3" t="n">
-        <v>-2</v>
+        <v>4761.435</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>31.927</v>
       </c>
       <c r="M3" t="n">
-        <v>304</v>
+        <v>14913.512</v>
       </c>
       <c r="N3" t="n">
-        <v>819</v>
+        <v>2.714</v>
       </c>
       <c r="O3" t="n">
-        <v>32.97</v>
+        <v>4.584</v>
       </c>
       <c r="P3" t="n">
-        <v>191</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>650</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="S3" t="n">
-        <v>665</v>
-      </c>
-      <c r="T3" t="n">
-        <v>9144</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3Q23</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3397</v>
-      </c>
-      <c r="C4" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>459</v>
-      </c>
-      <c r="F4" t="n">
-        <v>299</v>
-      </c>
-      <c r="G4" t="n">
-        <v>244</v>
-      </c>
-      <c r="H4" t="n">
-        <v>370</v>
-      </c>
-      <c r="I4" t="n">
-        <v>243</v>
-      </c>
-      <c r="J4" t="n">
-        <v>202</v>
-      </c>
-      <c r="K4" t="n">
-        <v>41</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>286</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1834</v>
-      </c>
-      <c r="O4" t="n">
-        <v>53.99</v>
-      </c>
-      <c r="P4" t="n">
-        <v>192</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4374</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="S4" t="n">
-        <v>660</v>
-      </c>
-      <c r="T4" t="n">
-        <v>5986</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4Q23</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2218</v>
-      </c>
-      <c r="C5" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>384</v>
-      </c>
-      <c r="F5" t="n">
-        <v>254</v>
-      </c>
-      <c r="G5" t="n">
-        <v>253</v>
-      </c>
-      <c r="H5" t="n">
-        <v>391</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1142</v>
-      </c>
-      <c r="J5" t="n">
-        <v>211</v>
-      </c>
-      <c r="K5" t="n">
-        <v>931</v>
-      </c>
-      <c r="L5" t="n">
-        <v>16</v>
-      </c>
-      <c r="M5" t="n">
-        <v>290</v>
-      </c>
-      <c r="N5" t="n">
-        <v>738</v>
-      </c>
-      <c r="O5" t="n">
-        <v>33.27</v>
-      </c>
-      <c r="P5" t="n">
-        <v>192</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-349</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="S5" t="n">
-        <v>640</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5869</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1Q24</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2142</v>
-      </c>
-      <c r="C6" t="n">
-        <v>132.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>480</v>
-      </c>
-      <c r="F6" t="n">
-        <v>266</v>
-      </c>
-      <c r="G6" t="n">
-        <v>290</v>
-      </c>
-      <c r="H6" t="n">
-        <v>479</v>
-      </c>
-      <c r="I6" t="n">
-        <v>231</v>
-      </c>
-      <c r="J6" t="n">
-        <v>223</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>14</v>
-      </c>
-      <c r="M6" t="n">
-        <v>295</v>
-      </c>
-      <c r="N6" t="n">
-        <v>424</v>
-      </c>
-      <c r="O6" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="P6" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>264</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="S6" t="n">
-        <v>654</v>
-      </c>
-      <c r="T6" t="n">
-        <v>8737</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2Q24</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2748</v>
-      </c>
-      <c r="C7" t="n">
-        <v>125.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>506</v>
-      </c>
-      <c r="F7" t="n">
-        <v>314</v>
-      </c>
-      <c r="G7" t="n">
-        <v>280</v>
-      </c>
-      <c r="H7" t="n">
-        <v>527</v>
-      </c>
-      <c r="I7" t="n">
-        <v>242</v>
-      </c>
-      <c r="J7" t="n">
-        <v>242</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14</v>
-      </c>
-      <c r="M7" t="n">
-        <v>382</v>
-      </c>
-      <c r="N7" t="n">
-        <v>894</v>
-      </c>
-      <c r="O7" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="P7" t="n">
-        <v>226</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>555</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="S7" t="n">
-        <v>649</v>
-      </c>
-      <c r="T7" t="n">
-        <v>10342</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3Q24</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3732</v>
-      </c>
-      <c r="C8" t="n">
-        <v>122.8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>465</v>
-      </c>
-      <c r="F8" t="n">
-        <v>347</v>
-      </c>
-      <c r="G8" t="n">
-        <v>294</v>
-      </c>
-      <c r="H8" t="n">
-        <v>471</v>
-      </c>
-      <c r="I8" t="n">
-        <v>268</v>
-      </c>
-      <c r="J8" t="n">
-        <v>210</v>
-      </c>
-      <c r="K8" t="n">
-        <v>58</v>
-      </c>
-      <c r="L8" t="n">
-        <v>15</v>
-      </c>
-      <c r="M8" t="n">
-        <v>362</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1958</v>
-      </c>
-      <c r="O8" t="n">
-        <v>52.47</v>
-      </c>
-      <c r="P8" t="n">
-        <v>207</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1368</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S8" t="n">
-        <v>642</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6573</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>4Q24</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2480</v>
-      </c>
-      <c r="C9" t="n">
-        <v>111</v>
-      </c>
-      <c r="D9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>427</v>
-      </c>
-      <c r="F9" t="n">
-        <v>265</v>
-      </c>
-      <c r="G9" t="n">
-        <v>306</v>
-      </c>
-      <c r="H9" t="n">
-        <v>501</v>
-      </c>
-      <c r="I9" t="n">
-        <v>183</v>
-      </c>
-      <c r="J9" t="n">
-        <v>226</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-43</v>
-      </c>
-      <c r="L9" t="n">
-        <v>22</v>
-      </c>
-      <c r="M9" t="n">
-        <v>368</v>
-      </c>
-      <c r="N9" t="n">
-        <v>765</v>
-      </c>
-      <c r="O9" t="n">
-        <v>30.85</v>
-      </c>
-      <c r="P9" t="n">
-        <v>183</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>461</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="S9" t="n">
-        <v>636</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5931</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1Q25</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2272</v>
-      </c>
-      <c r="C10" t="n">
-        <v>143.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>506</v>
-      </c>
-      <c r="F10" t="n">
-        <v>282</v>
-      </c>
-      <c r="G10" t="n">
-        <v>338</v>
-      </c>
-      <c r="H10" t="n">
-        <v>519</v>
-      </c>
-      <c r="I10" t="n">
-        <v>231</v>
-      </c>
-      <c r="J10" t="n">
-        <v>235</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>25</v>
-      </c>
-      <c r="M10" t="n">
-        <v>358</v>
-      </c>
-      <c r="N10" t="n">
-        <v>417</v>
-      </c>
-      <c r="O10" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="P10" t="n">
-        <v>173</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>154</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>632</v>
-      </c>
-      <c r="T10" t="n">
-        <v>9175</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2Q25</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3096</v>
-      </c>
-      <c r="C11" t="n">
-        <v>134.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>544</v>
-      </c>
-      <c r="F11" t="n">
-        <v>309</v>
-      </c>
-      <c r="G11" t="n">
-        <v>331</v>
-      </c>
-      <c r="H11" t="n">
-        <v>639</v>
-      </c>
-      <c r="I11" t="n">
-        <v>237</v>
-      </c>
-      <c r="J11" t="n">
-        <v>244</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L11" t="n">
-        <v>21</v>
-      </c>
-      <c r="M11" t="n">
-        <v>424</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1043</v>
-      </c>
-      <c r="O11" t="n">
-        <v>33.69</v>
-      </c>
-      <c r="P11" t="n">
-        <v>190</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>642</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="S11" t="n">
-        <v>626</v>
-      </c>
-      <c r="T11" t="n">
-        <v>11067</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3Q25</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4095</v>
-      </c>
-      <c r="C12" t="n">
-        <v>133.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>549</v>
-      </c>
-      <c r="F12" t="n">
-        <v>343</v>
-      </c>
-      <c r="G12" t="n">
-        <v>333</v>
-      </c>
-      <c r="H12" t="n">
-        <v>585</v>
-      </c>
-      <c r="I12" t="n">
-        <v>261</v>
-      </c>
-      <c r="J12" t="n">
-        <v>257</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M12" t="n">
-        <v>399</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2051</v>
-      </c>
-      <c r="O12" t="n">
-        <v>50.09</v>
-      </c>
-      <c r="P12" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1374</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S12" t="n">
-        <v>621</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7209</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>4Q25</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2778</v>
-      </c>
-      <c r="C13" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>487</v>
-      </c>
-      <c r="F13" t="n">
-        <v>303</v>
-      </c>
-      <c r="G13" t="n">
-        <v>335</v>
-      </c>
-      <c r="H13" t="n">
-        <v>633</v>
-      </c>
-      <c r="I13" t="n">
-        <v>340</v>
-      </c>
-      <c r="J13" t="n">
-        <v>259</v>
-      </c>
-      <c r="K13" t="n">
-        <v>81</v>
-      </c>
-      <c r="L13" t="n">
-        <v>23</v>
-      </c>
-      <c r="M13" t="n">
-        <v>411</v>
-      </c>
-      <c r="N13" t="n">
-        <v>786</v>
-      </c>
-      <c r="O13" t="n">
-        <v>28.29</v>
-      </c>
-      <c r="P13" t="n">
-        <v>162</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>341</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="S13" t="n">
-        <v>614</v>
-      </c>
-      <c r="T13" t="n">
-        <v>6959</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1Q26</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2678</v>
-      </c>
-      <c r="C14" t="n">
-        <v>156.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>581</v>
-      </c>
-      <c r="F14" t="n">
-        <v>301</v>
-      </c>
-      <c r="G14" t="n">
-        <v>375</v>
-      </c>
-      <c r="H14" t="n">
-        <v>696</v>
-      </c>
-      <c r="I14" t="n">
-        <v>229</v>
-      </c>
-      <c r="J14" t="n">
-        <v>226</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>22</v>
-      </c>
-      <c r="M14" t="n">
-        <v>410</v>
-      </c>
-      <c r="N14" t="n">
-        <v>519</v>
-      </c>
-      <c r="O14" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="P14" t="n">
-        <v>155</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>160</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="S14" t="n">
-        <v>608</v>
-      </c>
-      <c r="T14" t="n">
-        <v>10550</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2Q26</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3608</v>
-      </c>
-      <c r="C15" t="n">
-        <v>148.3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>633</v>
-      </c>
-      <c r="F15" t="n">
-        <v>323</v>
-      </c>
-      <c r="G15" t="n">
-        <v>374</v>
-      </c>
-      <c r="H15" t="n">
-        <v>808</v>
-      </c>
-      <c r="I15" t="n">
-        <v>225</v>
-      </c>
-      <c r="J15" t="n">
-        <v>227</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>17</v>
-      </c>
-      <c r="M15" t="n">
-        <v>487</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1261</v>
-      </c>
-      <c r="O15" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="P15" t="n">
-        <v>183</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>816</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S15" t="n">
-        <v>597</v>
-      </c>
-      <c r="T15" t="n">
-        <v>12224</v>
+        <v>176.709</v>
       </c>
     </row>
   </sheetData>
